--- a/data/cox_xlsx/NKT.CO.xlsx
+++ b/data/cox_xlsx/NKT.CO.xlsx
@@ -12,14 +12,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="0YY3mIu+bR/w/ObSJ5hhglDxJQIoO4oGBOH6y7OBqcA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="i69u+P+qUCczw8Ie64ZrnR+Xr/tEW3jRaQzMcwmWEeQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="500">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -15728,104 +15728,120 @@
       <c r="H108" s="20">
         <v>51.17</v>
       </c>
-      <c r="I108" s="15"/>
-      <c r="J108" s="15"/>
-      <c r="K108" s="15"/>
-      <c r="L108" s="15"/>
-      <c r="M108" s="15"/>
-      <c r="N108" s="15"/>
-      <c r="O108" s="15"/>
-      <c r="P108" s="15"/>
-      <c r="Q108" s="15"/>
-      <c r="R108" s="15"/>
-      <c r="S108" s="15"/>
-      <c r="T108" s="15"/>
-      <c r="U108" s="15"/>
-      <c r="V108" s="15"/>
-      <c r="W108" s="15"/>
+      <c r="I108" s="20">
+        <v>81.24</v>
+      </c>
+      <c r="J108" s="20">
+        <v>70.88</v>
+      </c>
+      <c r="K108" s="20">
+        <v>95.34</v>
+      </c>
+      <c r="L108" s="16">
+        <v>111.36</v>
+      </c>
+      <c r="M108" s="16">
+        <v>325.97</v>
+      </c>
+      <c r="N108" s="16">
+        <v>536.85</v>
+      </c>
+      <c r="O108" s="16">
+        <v>1794.74</v>
+      </c>
+      <c r="P108" s="16">
+        <v>1252.14</v>
+      </c>
+      <c r="Q108" s="16">
+        <v>1000.23</v>
+      </c>
+      <c r="R108" s="16">
+        <v>1031.99</v>
+      </c>
+      <c r="S108" s="16">
+        <v>1846.54</v>
+      </c>
+      <c r="T108" s="16">
+        <v>1282.6</v>
+      </c>
+      <c r="U108" s="16">
+        <v>688.22</v>
+      </c>
+      <c r="V108" s="16">
+        <v>233.66</v>
+      </c>
+      <c r="W108" s="16">
+        <v>247.37</v>
+      </c>
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="B109" s="15"/>
-      <c r="C109" s="15"/>
-      <c r="D109" s="15"/>
+        <v>300</v>
+      </c>
+      <c r="B109" s="16">
+        <v>673.4</v>
+      </c>
+      <c r="C109" s="16">
+        <v>600.11</v>
+      </c>
+      <c r="D109" s="16">
+        <v>514.51</v>
+      </c>
       <c r="E109" s="15"/>
       <c r="F109" s="15"/>
       <c r="G109" s="15"/>
       <c r="H109" s="15"/>
-      <c r="I109" s="20">
-        <v>81.24</v>
-      </c>
-      <c r="J109" s="20">
-        <v>70.88</v>
-      </c>
-      <c r="K109" s="20">
-        <v>95.34</v>
-      </c>
-      <c r="L109" s="16">
-        <v>111.36</v>
-      </c>
-      <c r="M109" s="16">
-        <v>325.97</v>
-      </c>
-      <c r="N109" s="16">
-        <v>536.85</v>
-      </c>
-      <c r="O109" s="16">
-        <v>1794.74</v>
-      </c>
-      <c r="P109" s="16">
-        <v>1252.14</v>
-      </c>
-      <c r="Q109" s="16">
-        <v>1000.23</v>
-      </c>
-      <c r="R109" s="16">
-        <v>1031.99</v>
-      </c>
-      <c r="S109" s="16">
-        <v>1846.54</v>
-      </c>
-      <c r="T109" s="16">
-        <v>1282.6</v>
-      </c>
-      <c r="U109" s="16">
-        <v>688.22</v>
-      </c>
-      <c r="V109" s="16">
-        <v>233.66</v>
-      </c>
-      <c r="W109" s="16">
-        <v>247.37</v>
-      </c>
+      <c r="I109" s="15"/>
+      <c r="J109" s="15"/>
+      <c r="K109" s="15"/>
+      <c r="L109" s="15"/>
+      <c r="M109" s="15"/>
+      <c r="N109" s="15"/>
+      <c r="O109" s="15"/>
+      <c r="P109" s="15"/>
+      <c r="Q109" s="15"/>
+      <c r="R109" s="15"/>
+      <c r="S109" s="15"/>
+      <c r="T109" s="15"/>
+      <c r="U109" s="15"/>
+      <c r="V109" s="15"/>
+      <c r="W109" s="15"/>
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="B110" s="16">
-        <v>673.4</v>
-      </c>
-      <c r="C110" s="16">
-        <v>600.11</v>
-      </c>
-      <c r="D110" s="16">
-        <v>514.51</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="B110" s="15"/>
+      <c r="C110" s="15"/>
+      <c r="D110" s="15"/>
       <c r="E110" s="15"/>
       <c r="F110" s="15"/>
       <c r="G110" s="15"/>
       <c r="H110" s="15"/>
-      <c r="I110" s="15"/>
-      <c r="J110" s="15"/>
-      <c r="K110" s="15"/>
-      <c r="L110" s="15"/>
-      <c r="M110" s="15"/>
-      <c r="N110" s="15"/>
-      <c r="O110" s="15"/>
-      <c r="P110" s="15"/>
+      <c r="I110" s="16">
+        <v>5531.45</v>
+      </c>
+      <c r="J110" s="16">
+        <v>5731.84</v>
+      </c>
+      <c r="K110" s="16">
+        <v>2483.41</v>
+      </c>
+      <c r="L110" s="16">
+        <v>5320.33</v>
+      </c>
+      <c r="M110" s="16">
+        <v>4395.16</v>
+      </c>
+      <c r="N110" s="16">
+        <v>4235.86</v>
+      </c>
+      <c r="O110" s="16">
+        <v>3899.87</v>
+      </c>
+      <c r="P110" s="16">
+        <v>3957.79</v>
+      </c>
       <c r="Q110" s="15"/>
       <c r="R110" s="15"/>
       <c r="S110" s="15"/>
@@ -15836,7 +15852,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B111" s="15"/>
       <c r="C111" s="15"/>
@@ -15845,33 +15861,31 @@
       <c r="F111" s="15"/>
       <c r="G111" s="15"/>
       <c r="H111" s="15"/>
-      <c r="I111" s="16">
-        <v>5531.45</v>
-      </c>
-      <c r="J111" s="16">
-        <v>5731.84</v>
-      </c>
-      <c r="K111" s="16">
-        <v>2483.41</v>
-      </c>
-      <c r="L111" s="16">
-        <v>5320.33</v>
-      </c>
-      <c r="M111" s="16">
-        <v>4395.16</v>
-      </c>
-      <c r="N111" s="16">
-        <v>4235.86</v>
-      </c>
-      <c r="O111" s="16">
-        <v>3899.87</v>
-      </c>
-      <c r="P111" s="16">
-        <v>3957.79</v>
-      </c>
-      <c r="Q111" s="15"/>
-      <c r="R111" s="15"/>
-      <c r="S111" s="15"/>
+      <c r="I111" s="15"/>
+      <c r="J111" s="15"/>
+      <c r="K111" s="15"/>
+      <c r="L111" s="15"/>
+      <c r="M111" s="20">
+        <v>1.82</v>
+      </c>
+      <c r="N111" s="20">
+        <v>1.9</v>
+      </c>
+      <c r="O111" s="20">
+        <v>18.21</v>
+      </c>
+      <c r="P111" s="20">
+        <v>19.46</v>
+      </c>
+      <c r="Q111" s="20">
+        <v>2.93</v>
+      </c>
+      <c r="R111" s="16">
+        <v>160.31</v>
+      </c>
+      <c r="S111" s="16">
+        <v>174.44</v>
+      </c>
       <c r="T111" s="15"/>
       <c r="U111" s="15"/>
       <c r="V111" s="15"/>
@@ -15879,7 +15893,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B112" s="15"/>
       <c r="C112" s="15"/>
@@ -15888,39 +15902,55 @@
       <c r="F112" s="15"/>
       <c r="G112" s="15"/>
       <c r="H112" s="15"/>
-      <c r="I112" s="15"/>
-      <c r="J112" s="15"/>
-      <c r="K112" s="15"/>
-      <c r="L112" s="15"/>
-      <c r="M112" s="20">
-        <v>1.82</v>
-      </c>
-      <c r="N112" s="20">
-        <v>1.9</v>
-      </c>
-      <c r="O112" s="20">
-        <v>18.21</v>
-      </c>
-      <c r="P112" s="20">
-        <v>19.46</v>
-      </c>
-      <c r="Q112" s="20">
-        <v>2.93</v>
+      <c r="I112" s="20">
+        <v>53.5</v>
+      </c>
+      <c r="J112" s="20">
+        <v>15.75</v>
+      </c>
+      <c r="K112" s="20">
+        <v>38.14</v>
+      </c>
+      <c r="L112" s="16">
+        <v>142.08</v>
+      </c>
+      <c r="M112" s="16">
+        <v>226.42</v>
+      </c>
+      <c r="N112" s="16">
+        <v>213.31</v>
+      </c>
+      <c r="O112" s="16">
+        <v>240.98</v>
+      </c>
+      <c r="P112" s="16">
+        <v>211.78</v>
+      </c>
+      <c r="Q112" s="16">
+        <v>396.33</v>
       </c>
       <c r="R112" s="16">
-        <v>160.31</v>
+        <v>279.6</v>
       </c>
       <c r="S112" s="16">
-        <v>174.44</v>
-      </c>
-      <c r="T112" s="15"/>
-      <c r="U112" s="15"/>
-      <c r="V112" s="15"/>
-      <c r="W112" s="15"/>
+        <v>365.19</v>
+      </c>
+      <c r="T112" s="16">
+        <v>412.39</v>
+      </c>
+      <c r="U112" s="16">
+        <v>349.63</v>
+      </c>
+      <c r="V112" s="16">
+        <v>168.34</v>
+      </c>
+      <c r="W112" s="16">
+        <v>141.97</v>
+      </c>
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
@@ -15929,55 +15959,43 @@
       <c r="F113" s="15"/>
       <c r="G113" s="15"/>
       <c r="H113" s="15"/>
-      <c r="I113" s="20">
-        <v>53.5</v>
-      </c>
-      <c r="J113" s="20">
-        <v>15.75</v>
-      </c>
-      <c r="K113" s="20">
-        <v>38.14</v>
-      </c>
-      <c r="L113" s="16">
-        <v>142.08</v>
-      </c>
-      <c r="M113" s="16">
-        <v>226.42</v>
-      </c>
-      <c r="N113" s="16">
-        <v>213.31</v>
-      </c>
-      <c r="O113" s="16">
-        <v>240.98</v>
+      <c r="I113" s="16">
+        <v>644.0</v>
+      </c>
+      <c r="J113" s="16">
+        <v>820.1</v>
+      </c>
+      <c r="K113" s="15"/>
+      <c r="L113" s="15"/>
+      <c r="M113" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="N113" s="20">
+        <v>52.66</v>
+      </c>
+      <c r="O113" s="20">
+        <v>23.43</v>
       </c>
       <c r="P113" s="16">
-        <v>211.78</v>
-      </c>
-      <c r="Q113" s="16">
-        <v>396.33</v>
-      </c>
-      <c r="R113" s="16">
-        <v>279.6</v>
+        <v>173.17</v>
+      </c>
+      <c r="Q113" s="20">
+        <v>41.49</v>
+      </c>
+      <c r="R113" s="20">
+        <v>24.97</v>
       </c>
       <c r="S113" s="16">
-        <v>365.19</v>
-      </c>
-      <c r="T113" s="16">
-        <v>412.39</v>
-      </c>
-      <c r="U113" s="16">
-        <v>349.63</v>
-      </c>
-      <c r="V113" s="16">
-        <v>168.34</v>
-      </c>
-      <c r="W113" s="16">
-        <v>141.97</v>
-      </c>
+        <v>310.78</v>
+      </c>
+      <c r="T113" s="15"/>
+      <c r="U113" s="15"/>
+      <c r="V113" s="15"/>
+      <c r="W113" s="15"/>
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B114" s="15"/>
       <c r="C114" s="15"/>
@@ -15986,43 +16004,55 @@
       <c r="F114" s="15"/>
       <c r="G114" s="15"/>
       <c r="H114" s="15"/>
-      <c r="I114" s="16">
-        <v>644.0</v>
-      </c>
-      <c r="J114" s="16">
-        <v>820.1</v>
-      </c>
-      <c r="K114" s="15"/>
-      <c r="L114" s="15"/>
-      <c r="M114" s="15">
-        <v>0.0</v>
+      <c r="I114" s="20">
+        <v>12.88</v>
+      </c>
+      <c r="J114" s="20">
+        <v>13.78</v>
+      </c>
+      <c r="K114" s="20">
+        <v>16.34</v>
+      </c>
+      <c r="L114" s="20">
+        <v>26.88</v>
+      </c>
+      <c r="M114" s="20">
+        <v>41.64</v>
       </c>
       <c r="N114" s="20">
-        <v>52.66</v>
+        <v>42.37</v>
       </c>
       <c r="O114" s="20">
-        <v>23.43</v>
-      </c>
-      <c r="P114" s="16">
-        <v>173.17</v>
+        <v>35.04</v>
+      </c>
+      <c r="P114" s="20">
+        <v>34.76</v>
       </c>
       <c r="Q114" s="20">
-        <v>41.49</v>
+        <v>35.33</v>
       </c>
       <c r="R114" s="20">
-        <v>24.97</v>
-      </c>
-      <c r="S114" s="16">
-        <v>310.78</v>
-      </c>
-      <c r="T114" s="15"/>
-      <c r="U114" s="15"/>
-      <c r="V114" s="15"/>
-      <c r="W114" s="15"/>
+        <v>57.86</v>
+      </c>
+      <c r="S114" s="20">
+        <v>96.81</v>
+      </c>
+      <c r="T114" s="16">
+        <v>102.25</v>
+      </c>
+      <c r="U114" s="20">
+        <v>0.33</v>
+      </c>
+      <c r="V114" s="20">
+        <v>8.35</v>
+      </c>
+      <c r="W114" s="20">
+        <v>4.21</v>
+      </c>
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B115" s="15"/>
       <c r="C115" s="15"/>
@@ -16031,55 +16061,41 @@
       <c r="F115" s="15"/>
       <c r="G115" s="15"/>
       <c r="H115" s="15"/>
-      <c r="I115" s="20">
-        <v>12.88</v>
-      </c>
-      <c r="J115" s="20">
-        <v>13.78</v>
-      </c>
-      <c r="K115" s="20">
-        <v>16.34</v>
-      </c>
-      <c r="L115" s="20">
-        <v>26.88</v>
-      </c>
-      <c r="M115" s="20">
-        <v>41.64</v>
-      </c>
-      <c r="N115" s="20">
-        <v>42.37</v>
-      </c>
-      <c r="O115" s="20">
-        <v>35.04</v>
-      </c>
-      <c r="P115" s="20">
-        <v>34.76</v>
-      </c>
-      <c r="Q115" s="20">
-        <v>35.33</v>
-      </c>
-      <c r="R115" s="20">
-        <v>57.86</v>
-      </c>
-      <c r="S115" s="20">
-        <v>96.81</v>
-      </c>
-      <c r="T115" s="16">
-        <v>102.25</v>
-      </c>
-      <c r="U115" s="20">
-        <v>0.33</v>
-      </c>
-      <c r="V115" s="20">
-        <v>8.35</v>
-      </c>
-      <c r="W115" s="20">
-        <v>4.21</v>
-      </c>
+      <c r="I115" s="16">
+        <v>1404.91</v>
+      </c>
+      <c r="J115" s="16">
+        <v>1479.72</v>
+      </c>
+      <c r="K115" s="16">
+        <v>651.04</v>
+      </c>
+      <c r="L115" s="16">
+        <v>845.76</v>
+      </c>
+      <c r="M115" s="16">
+        <v>1385.82</v>
+      </c>
+      <c r="N115" s="16">
+        <v>1211.76</v>
+      </c>
+      <c r="O115" s="16">
+        <v>1137.27</v>
+      </c>
+      <c r="P115" s="16">
+        <v>1241.73</v>
+      </c>
+      <c r="Q115" s="15"/>
+      <c r="R115" s="15"/>
+      <c r="S115" s="15"/>
+      <c r="T115" s="15"/>
+      <c r="U115" s="15"/>
+      <c r="V115" s="15"/>
+      <c r="W115" s="15"/>
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
@@ -16089,28 +16105,28 @@
       <c r="G116" s="15"/>
       <c r="H116" s="15"/>
       <c r="I116" s="16">
-        <v>1404.91</v>
+        <v>730.2</v>
       </c>
       <c r="J116" s="16">
-        <v>1479.72</v>
+        <v>397.74</v>
       </c>
       <c r="K116" s="16">
-        <v>651.04</v>
+        <v>279.67</v>
       </c>
       <c r="L116" s="16">
-        <v>845.76</v>
+        <v>331.2</v>
       </c>
       <c r="M116" s="16">
-        <v>1385.82</v>
-      </c>
-      <c r="N116" s="16">
-        <v>1211.76</v>
+        <v>114.97</v>
+      </c>
+      <c r="N116" s="20">
+        <v>48.41</v>
       </c>
       <c r="O116" s="16">
-        <v>1137.27</v>
+        <v>338.83</v>
       </c>
       <c r="P116" s="16">
-        <v>1241.73</v>
+        <v>227.18</v>
       </c>
       <c r="Q116" s="15"/>
       <c r="R116" s="15"/>
@@ -16122,7 +16138,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B117" s="15"/>
       <c r="C117" s="15"/>
@@ -16131,30 +16147,16 @@
       <c r="F117" s="15"/>
       <c r="G117" s="15"/>
       <c r="H117" s="15"/>
-      <c r="I117" s="16">
-        <v>730.2</v>
-      </c>
-      <c r="J117" s="16">
-        <v>397.74</v>
-      </c>
-      <c r="K117" s="16">
-        <v>279.67</v>
-      </c>
-      <c r="L117" s="16">
-        <v>331.2</v>
-      </c>
-      <c r="M117" s="16">
-        <v>114.97</v>
-      </c>
-      <c r="N117" s="20">
-        <v>48.41</v>
-      </c>
-      <c r="O117" s="16">
-        <v>338.83</v>
-      </c>
-      <c r="P117" s="16">
-        <v>227.18</v>
-      </c>
+      <c r="I117" s="20">
+        <v>6.94</v>
+      </c>
+      <c r="J117" s="15"/>
+      <c r="K117" s="15"/>
+      <c r="L117" s="15"/>
+      <c r="M117" s="15"/>
+      <c r="N117" s="15"/>
+      <c r="O117" s="15"/>
+      <c r="P117" s="15"/>
       <c r="Q117" s="15"/>
       <c r="R117" s="15"/>
       <c r="S117" s="15"/>
@@ -16165,7 +16167,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
@@ -16174,12 +16176,14 @@
       <c r="F118" s="15"/>
       <c r="G118" s="15"/>
       <c r="H118" s="15"/>
-      <c r="I118" s="20">
-        <v>6.94</v>
-      </c>
+      <c r="I118" s="15"/>
       <c r="J118" s="15"/>
-      <c r="K118" s="15"/>
-      <c r="L118" s="15"/>
+      <c r="K118" s="22">
+        <v>-202.49</v>
+      </c>
+      <c r="L118" s="16">
+        <v>1916.17</v>
+      </c>
       <c r="M118" s="15"/>
       <c r="N118" s="15"/>
       <c r="O118" s="15"/>
@@ -16194,309 +16198,319 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="B119" s="15"/>
-      <c r="C119" s="15"/>
-      <c r="D119" s="15"/>
-      <c r="E119" s="15"/>
-      <c r="F119" s="15"/>
-      <c r="G119" s="15"/>
-      <c r="H119" s="15"/>
-      <c r="I119" s="15"/>
-      <c r="J119" s="15"/>
-      <c r="K119" s="22">
-        <v>-202.49</v>
+        <v>310</v>
+      </c>
+      <c r="B119" s="16">
+        <v>6544.96</v>
+      </c>
+      <c r="C119" s="16">
+        <v>6283.55</v>
+      </c>
+      <c r="D119" s="16">
+        <v>4071.35</v>
+      </c>
+      <c r="E119" s="16">
+        <v>3679.98</v>
+      </c>
+      <c r="F119" s="16">
+        <v>3421.92</v>
+      </c>
+      <c r="G119" s="16">
+        <v>2862.09</v>
+      </c>
+      <c r="H119" s="16">
+        <v>2817.36</v>
+      </c>
+      <c r="I119" s="16">
+        <v>2679.04</v>
+      </c>
+      <c r="J119" s="16">
+        <v>3004.73</v>
+      </c>
+      <c r="K119" s="16">
+        <v>1700.7</v>
       </c>
       <c r="L119" s="16">
-        <v>1916.17</v>
-      </c>
-      <c r="M119" s="15"/>
-      <c r="N119" s="15"/>
-      <c r="O119" s="15"/>
-      <c r="P119" s="15"/>
-      <c r="Q119" s="15"/>
-      <c r="R119" s="15"/>
-      <c r="S119" s="15"/>
-      <c r="T119" s="15"/>
-      <c r="U119" s="15"/>
-      <c r="V119" s="15"/>
-      <c r="W119" s="15"/>
+        <v>2058.25</v>
+      </c>
+      <c r="M119" s="16">
+        <v>2624.49</v>
+      </c>
+      <c r="N119" s="16">
+        <v>2665.45</v>
+      </c>
+      <c r="O119" s="16">
+        <v>2106.11</v>
+      </c>
+      <c r="P119" s="16">
+        <v>2049.71</v>
+      </c>
+      <c r="Q119" s="16">
+        <v>1658.89</v>
+      </c>
+      <c r="R119" s="16">
+        <v>1129.76</v>
+      </c>
+      <c r="S119" s="16">
+        <v>1320.35</v>
+      </c>
+      <c r="T119" s="16">
+        <v>1197.8</v>
+      </c>
+      <c r="U119" s="16">
+        <v>886.76</v>
+      </c>
+      <c r="V119" s="16">
+        <v>819.53</v>
+      </c>
+      <c r="W119" s="16">
+        <v>783.01</v>
+      </c>
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="B120" s="16">
-        <v>6544.96</v>
-      </c>
-      <c r="C120" s="16">
-        <v>6283.55</v>
-      </c>
-      <c r="D120" s="16">
-        <v>4071.35</v>
-      </c>
-      <c r="E120" s="16">
-        <v>3679.98</v>
-      </c>
-      <c r="F120" s="16">
-        <v>3421.92</v>
-      </c>
-      <c r="G120" s="16">
-        <v>2862.09</v>
-      </c>
-      <c r="H120" s="16">
-        <v>2817.36</v>
-      </c>
-      <c r="I120" s="16">
-        <v>2679.04</v>
-      </c>
-      <c r="J120" s="16">
-        <v>3004.73</v>
-      </c>
-      <c r="K120" s="16">
-        <v>1700.7</v>
-      </c>
-      <c r="L120" s="16">
-        <v>2058.25</v>
-      </c>
-      <c r="M120" s="16">
-        <v>2624.49</v>
-      </c>
-      <c r="N120" s="16">
-        <v>2665.45</v>
-      </c>
-      <c r="O120" s="16">
-        <v>2106.11</v>
-      </c>
-      <c r="P120" s="16">
-        <v>2049.71</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="B120" s="15"/>
+      <c r="C120" s="15"/>
+      <c r="D120" s="15"/>
+      <c r="E120" s="15"/>
+      <c r="F120" s="15"/>
+      <c r="G120" s="15"/>
+      <c r="H120" s="15"/>
+      <c r="I120" s="15"/>
+      <c r="J120" s="15"/>
+      <c r="K120" s="15"/>
+      <c r="L120" s="15"/>
+      <c r="M120" s="15"/>
+      <c r="N120" s="15"/>
+      <c r="O120" s="15"/>
+      <c r="P120" s="15"/>
       <c r="Q120" s="16">
-        <v>1658.89</v>
+        <v>1266.85</v>
       </c>
       <c r="R120" s="16">
-        <v>1129.76</v>
+        <v>1419.5</v>
       </c>
       <c r="S120" s="16">
-        <v>1320.35</v>
+        <v>1644.44</v>
       </c>
       <c r="T120" s="16">
-        <v>1197.8</v>
+        <v>1068.32</v>
       </c>
       <c r="U120" s="16">
-        <v>886.76</v>
+        <v>941.5</v>
       </c>
       <c r="V120" s="16">
-        <v>819.53</v>
+        <v>782.37</v>
       </c>
       <c r="W120" s="16">
-        <v>783.01</v>
+        <v>785.45</v>
       </c>
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="B121" s="15"/>
-      <c r="C121" s="15"/>
-      <c r="D121" s="15"/>
-      <c r="E121" s="15"/>
-      <c r="F121" s="15"/>
-      <c r="G121" s="15"/>
-      <c r="H121" s="15"/>
-      <c r="I121" s="15"/>
-      <c r="J121" s="15"/>
-      <c r="K121" s="15"/>
-      <c r="L121" s="15"/>
-      <c r="M121" s="15"/>
-      <c r="N121" s="15"/>
-      <c r="O121" s="15"/>
-      <c r="P121" s="15"/>
-      <c r="Q121" s="16">
-        <v>1266.85</v>
-      </c>
-      <c r="R121" s="16">
-        <v>1419.5</v>
+        <v>312</v>
+      </c>
+      <c r="B121" s="16">
+        <v>968.75</v>
+      </c>
+      <c r="C121" s="16">
+        <v>706.02</v>
+      </c>
+      <c r="D121" s="16">
+        <v>302.0</v>
+      </c>
+      <c r="E121" s="16">
+        <v>100.65</v>
+      </c>
+      <c r="F121" s="16">
+        <v>105.12</v>
+      </c>
+      <c r="G121" s="20">
+        <v>22.0</v>
+      </c>
+      <c r="H121" s="20">
+        <v>18.7</v>
+      </c>
+      <c r="I121" s="20">
+        <v>7.93</v>
+      </c>
+      <c r="J121" s="16">
+        <v>115.19</v>
+      </c>
+      <c r="K121" s="20">
+        <v>66.28</v>
+      </c>
+      <c r="L121" s="20">
+        <v>63.36</v>
+      </c>
+      <c r="M121" s="20">
+        <v>64.34</v>
+      </c>
+      <c r="N121" s="20">
+        <v>21.46</v>
+      </c>
+      <c r="O121" s="20">
+        <v>66.15</v>
+      </c>
+      <c r="P121" s="20">
+        <v>48.5</v>
+      </c>
+      <c r="Q121" s="20">
+        <v>38.25</v>
+      </c>
+      <c r="R121" s="20">
+        <v>83.61</v>
       </c>
       <c r="S121" s="16">
-        <v>1644.44</v>
-      </c>
-      <c r="T121" s="16">
-        <v>1068.32</v>
-      </c>
-      <c r="U121" s="16">
-        <v>941.5</v>
-      </c>
-      <c r="V121" s="16">
-        <v>782.37</v>
-      </c>
-      <c r="W121" s="16">
-        <v>785.45</v>
+        <v>142.08</v>
+      </c>
+      <c r="T121" s="20">
+        <v>51.07</v>
+      </c>
+      <c r="U121" s="20">
+        <v>14.9</v>
+      </c>
+      <c r="V121" s="20">
+        <v>46.48</v>
+      </c>
+      <c r="W121" s="20">
+        <v>32.58</v>
       </c>
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B122" s="16">
-        <v>968.75</v>
+        <v>425.3</v>
       </c>
       <c r="C122" s="16">
-        <v>706.02</v>
+        <v>329.47</v>
       </c>
       <c r="D122" s="16">
-        <v>302.0</v>
+        <v>335.55</v>
       </c>
       <c r="E122" s="16">
-        <v>100.65</v>
+        <v>237.99</v>
       </c>
       <c r="F122" s="16">
-        <v>105.12</v>
-      </c>
-      <c r="G122" s="20">
-        <v>22.0</v>
-      </c>
-      <c r="H122" s="20">
-        <v>18.7</v>
-      </c>
-      <c r="I122" s="20">
-        <v>7.93</v>
+        <v>633.73</v>
+      </c>
+      <c r="G122" s="16">
+        <v>136.19</v>
+      </c>
+      <c r="H122" s="16">
+        <v>205.67</v>
+      </c>
+      <c r="I122" s="16">
+        <v>130.78</v>
       </c>
       <c r="J122" s="16">
-        <v>115.19</v>
-      </c>
-      <c r="K122" s="20">
-        <v>66.28</v>
-      </c>
-      <c r="L122" s="20">
-        <v>63.36</v>
-      </c>
-      <c r="M122" s="20">
-        <v>64.34</v>
-      </c>
-      <c r="N122" s="20">
-        <v>21.46</v>
-      </c>
-      <c r="O122" s="20">
-        <v>66.15</v>
-      </c>
-      <c r="P122" s="20">
-        <v>48.5</v>
-      </c>
-      <c r="Q122" s="20">
-        <v>38.25</v>
-      </c>
-      <c r="R122" s="20">
-        <v>83.61</v>
+        <v>132.91</v>
+      </c>
+      <c r="K122" s="16">
+        <v>143.47</v>
+      </c>
+      <c r="L122" s="16">
+        <v>386.88</v>
+      </c>
+      <c r="M122" s="16">
+        <v>277.41</v>
+      </c>
+      <c r="N122" s="16">
+        <v>198.55</v>
+      </c>
+      <c r="O122" s="16">
+        <v>139.39</v>
+      </c>
+      <c r="P122" s="16">
+        <v>159.85</v>
+      </c>
+      <c r="Q122" s="16">
+        <v>166.7</v>
+      </c>
+      <c r="R122" s="16">
+        <v>144.82</v>
       </c>
       <c r="S122" s="16">
-        <v>142.08</v>
-      </c>
-      <c r="T122" s="20">
-        <v>51.07</v>
-      </c>
-      <c r="U122" s="20">
-        <v>14.9</v>
-      </c>
-      <c r="V122" s="20">
-        <v>46.48</v>
-      </c>
-      <c r="W122" s="20">
-        <v>32.58</v>
-      </c>
+        <v>181.22</v>
+      </c>
+      <c r="T122" s="16">
+        <v>140.66</v>
+      </c>
+      <c r="U122" s="16">
+        <v>154.4</v>
+      </c>
+      <c r="V122" s="15"/>
+      <c r="W122" s="15"/>
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B123" s="16">
-        <v>425.3</v>
+        <v>3260.67</v>
       </c>
       <c r="C123" s="16">
-        <v>329.47</v>
+        <v>3424.18</v>
       </c>
       <c r="D123" s="16">
-        <v>335.55</v>
+        <v>1621.83</v>
       </c>
       <c r="E123" s="16">
-        <v>237.99</v>
+        <v>2345.33</v>
       </c>
       <c r="F123" s="16">
-        <v>633.73</v>
+        <v>1705.96</v>
       </c>
       <c r="G123" s="16">
-        <v>136.19</v>
+        <v>1760.0</v>
       </c>
       <c r="H123" s="16">
-        <v>205.67</v>
-      </c>
-      <c r="I123" s="16">
-        <v>130.78</v>
-      </c>
-      <c r="J123" s="16">
-        <v>132.91</v>
-      </c>
-      <c r="K123" s="16">
-        <v>143.47</v>
-      </c>
-      <c r="L123" s="16">
-        <v>386.88</v>
-      </c>
-      <c r="M123" s="16">
-        <v>277.41</v>
-      </c>
-      <c r="N123" s="16">
-        <v>198.55</v>
-      </c>
-      <c r="O123" s="16">
-        <v>139.39</v>
-      </c>
-      <c r="P123" s="16">
-        <v>159.85</v>
-      </c>
-      <c r="Q123" s="16">
-        <v>166.7</v>
-      </c>
-      <c r="R123" s="16">
-        <v>144.82</v>
-      </c>
-      <c r="S123" s="16">
-        <v>181.22</v>
-      </c>
-      <c r="T123" s="16">
-        <v>140.66</v>
-      </c>
-      <c r="U123" s="16">
-        <v>154.4</v>
-      </c>
+        <v>1367.84</v>
+      </c>
+      <c r="I123" s="15"/>
+      <c r="J123" s="15"/>
+      <c r="K123" s="15"/>
+      <c r="L123" s="15"/>
+      <c r="M123" s="15"/>
+      <c r="N123" s="15"/>
+      <c r="O123" s="15"/>
+      <c r="P123" s="15"/>
+      <c r="Q123" s="15"/>
+      <c r="R123" s="15"/>
+      <c r="S123" s="15"/>
+      <c r="T123" s="15"/>
+      <c r="U123" s="15"/>
       <c r="V123" s="15"/>
       <c r="W123" s="15"/>
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="B124" s="16">
-        <v>3260.67</v>
+        <v>315</v>
+      </c>
+      <c r="B124" s="15">
+        <v>11199.68</v>
       </c>
       <c r="C124" s="16">
-        <v>3424.18</v>
+        <v>7366.11</v>
       </c>
       <c r="D124" s="16">
-        <v>1621.83</v>
+        <v>7974.93</v>
       </c>
       <c r="E124" s="16">
-        <v>2345.33</v>
+        <v>7104.14</v>
       </c>
       <c r="F124" s="16">
-        <v>1705.96</v>
+        <v>4598.27</v>
       </c>
       <c r="G124" s="16">
-        <v>1760.0</v>
+        <v>3106.19</v>
       </c>
       <c r="H124" s="16">
-        <v>1367.84</v>
+        <v>1833.3</v>
       </c>
       <c r="I124" s="15"/>
       <c r="J124" s="15"/>
@@ -16516,33 +16530,25 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="B125" s="15">
-        <v>11199.68</v>
-      </c>
-      <c r="C125" s="16">
-        <v>7366.11</v>
-      </c>
-      <c r="D125" s="16">
-        <v>7974.93</v>
-      </c>
-      <c r="E125" s="16">
-        <v>7104.14</v>
-      </c>
-      <c r="F125" s="16">
-        <v>4598.27</v>
-      </c>
-      <c r="G125" s="16">
-        <v>3106.19</v>
-      </c>
-      <c r="H125" s="16">
-        <v>1833.3</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="B125" s="15"/>
+      <c r="C125" s="15"/>
+      <c r="D125" s="15"/>
+      <c r="E125" s="15"/>
+      <c r="F125" s="15"/>
+      <c r="G125" s="15"/>
+      <c r="H125" s="15"/>
       <c r="I125" s="15"/>
-      <c r="J125" s="15"/>
-      <c r="K125" s="15"/>
-      <c r="L125" s="15"/>
+      <c r="J125" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="K125" s="16">
+        <v>2788.5</v>
+      </c>
+      <c r="L125" s="15">
+        <v>0.0</v>
+      </c>
       <c r="M125" s="15"/>
       <c r="N125" s="15"/>
       <c r="O125" s="15"/>
@@ -16557,12 +16563,18 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B126" s="15"/>
-      <c r="C126" s="15"/>
-      <c r="D126" s="15"/>
-      <c r="E126" s="15"/>
+      <c r="C126" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="D126" s="16">
+        <v>425.03</v>
+      </c>
+      <c r="E126" s="16">
+        <v>373.24</v>
+      </c>
       <c r="F126" s="15"/>
       <c r="G126" s="15"/>
       <c r="H126" s="15"/>
@@ -16571,7 +16583,7 @@
         <v>0.0</v>
       </c>
       <c r="K126" s="16">
-        <v>2788.5</v>
+        <v>223.37</v>
       </c>
       <c r="L126" s="15">
         <v>0.0</v>
@@ -16589,194 +16601,196 @@
       <c r="W126" s="15"/>
     </row>
     <row r="127" ht="15.0" customHeight="1">
-      <c r="A127" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="B127" s="15"/>
-      <c r="C127" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="D127" s="16">
-        <v>425.03</v>
-      </c>
-      <c r="E127" s="16">
-        <v>373.24</v>
-      </c>
-      <c r="F127" s="15"/>
-      <c r="G127" s="15"/>
-      <c r="H127" s="15"/>
-      <c r="I127" s="15"/>
-      <c r="J127" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K127" s="16">
-        <v>223.37</v>
-      </c>
-      <c r="L127" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="M127" s="15"/>
-      <c r="N127" s="15"/>
-      <c r="O127" s="15"/>
-      <c r="P127" s="15"/>
-      <c r="Q127" s="15"/>
-      <c r="R127" s="15"/>
-      <c r="S127" s="15"/>
-      <c r="T127" s="15"/>
-      <c r="U127" s="15"/>
-      <c r="V127" s="15"/>
-      <c r="W127" s="15"/>
+      <c r="A127" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="B127" s="18">
+        <v>23332.66</v>
+      </c>
+      <c r="C127" s="18">
+        <v>18909.49</v>
+      </c>
+      <c r="D127" s="18">
+        <v>15368.24</v>
+      </c>
+      <c r="E127" s="18">
+        <v>13997.55</v>
+      </c>
+      <c r="F127" s="18">
+        <v>10640.2</v>
+      </c>
+      <c r="G127" s="19">
+        <v>8020.57</v>
+      </c>
+      <c r="H127" s="19">
+        <v>6353.09</v>
+      </c>
+      <c r="I127" s="19">
+        <v>5751.41</v>
+      </c>
+      <c r="J127" s="19">
+        <v>6050.82</v>
+      </c>
+      <c r="K127" s="19">
+        <v>5800.37</v>
+      </c>
+      <c r="L127" s="19">
+        <v>5881.94</v>
+      </c>
+      <c r="M127" s="19">
+        <v>5062.88</v>
+      </c>
+      <c r="N127" s="19">
+        <v>4992.72</v>
+      </c>
+      <c r="O127" s="19">
+        <v>5900.15</v>
+      </c>
+      <c r="P127" s="19">
+        <v>5418.28</v>
+      </c>
+      <c r="Q127" s="19">
+        <v>4607.0</v>
+      </c>
+      <c r="R127" s="19">
+        <v>4332.42</v>
+      </c>
+      <c r="S127" s="19">
+        <v>6081.85</v>
+      </c>
+      <c r="T127" s="19">
+        <v>4255.09</v>
+      </c>
+      <c r="U127" s="19">
+        <v>3035.73</v>
+      </c>
+      <c r="V127" s="19">
+        <v>2058.72</v>
+      </c>
+      <c r="W127" s="19">
+        <v>1994.6</v>
+      </c>
     </row>
     <row r="128" ht="15.0" customHeight="1">
-      <c r="A128" s="17" t="s">
-        <v>318</v>
-      </c>
-      <c r="B128" s="18">
-        <v>23332.66</v>
-      </c>
-      <c r="C128" s="18">
-        <v>18909.49</v>
-      </c>
-      <c r="D128" s="18">
-        <v>15368.24</v>
-      </c>
-      <c r="E128" s="18">
-        <v>13997.55</v>
-      </c>
-      <c r="F128" s="18">
-        <v>10640.2</v>
-      </c>
-      <c r="G128" s="19">
-        <v>8020.57</v>
-      </c>
-      <c r="H128" s="19">
-        <v>6353.09</v>
-      </c>
-      <c r="I128" s="19">
-        <v>5751.41</v>
-      </c>
-      <c r="J128" s="19">
-        <v>6050.82</v>
-      </c>
-      <c r="K128" s="19">
-        <v>5800.37</v>
-      </c>
-      <c r="L128" s="19">
-        <v>5881.94</v>
-      </c>
-      <c r="M128" s="19">
-        <v>5062.88</v>
-      </c>
-      <c r="N128" s="19">
-        <v>4992.72</v>
-      </c>
-      <c r="O128" s="19">
-        <v>5900.15</v>
-      </c>
-      <c r="P128" s="19">
-        <v>5418.28</v>
-      </c>
-      <c r="Q128" s="19">
-        <v>4607.0</v>
-      </c>
-      <c r="R128" s="19">
-        <v>4332.42</v>
-      </c>
-      <c r="S128" s="19">
-        <v>6081.85</v>
-      </c>
-      <c r="T128" s="19">
-        <v>4255.09</v>
-      </c>
-      <c r="U128" s="19">
-        <v>3035.73</v>
-      </c>
-      <c r="V128" s="19">
-        <v>2058.72</v>
-      </c>
-      <c r="W128" s="19">
-        <v>1994.6</v>
+      <c r="A128" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="B128" s="15"/>
+      <c r="C128" s="15"/>
+      <c r="D128" s="15"/>
+      <c r="E128" s="15"/>
+      <c r="F128" s="15"/>
+      <c r="G128" s="15"/>
+      <c r="H128" s="15"/>
+      <c r="I128" s="16">
+        <v>2659.22</v>
+      </c>
+      <c r="J128" s="16">
+        <v>3276.46</v>
+      </c>
+      <c r="K128" s="16">
+        <v>753.65</v>
+      </c>
+      <c r="L128" s="16">
+        <v>1381.44</v>
+      </c>
+      <c r="M128" s="16">
+        <v>1602.64</v>
+      </c>
+      <c r="N128" s="16">
+        <v>2345.83</v>
+      </c>
+      <c r="O128" s="16">
+        <v>535.61</v>
+      </c>
+      <c r="P128" s="16">
+        <v>3702.2</v>
+      </c>
+      <c r="Q128" s="16">
+        <v>3607.92</v>
+      </c>
+      <c r="R128" s="16">
+        <v>2170.11</v>
+      </c>
+      <c r="S128" s="16">
+        <v>1715.68</v>
+      </c>
+      <c r="T128" s="16">
+        <v>1429.0</v>
+      </c>
+      <c r="U128" s="16">
+        <v>1629.82</v>
+      </c>
+      <c r="V128" s="16">
+        <v>1051.47</v>
+      </c>
+      <c r="W128" s="16">
+        <v>814.49</v>
       </c>
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="B129" s="15"/>
-      <c r="C129" s="15"/>
-      <c r="D129" s="15"/>
-      <c r="E129" s="15"/>
-      <c r="F129" s="15"/>
-      <c r="G129" s="15"/>
-      <c r="H129" s="15"/>
-      <c r="I129" s="16">
-        <v>2659.22</v>
-      </c>
-      <c r="J129" s="16">
-        <v>3276.46</v>
-      </c>
-      <c r="K129" s="16">
-        <v>753.65</v>
-      </c>
-      <c r="L129" s="16">
-        <v>1381.44</v>
-      </c>
-      <c r="M129" s="16">
-        <v>1602.64</v>
-      </c>
-      <c r="N129" s="16">
-        <v>2345.83</v>
-      </c>
-      <c r="O129" s="16">
-        <v>535.61</v>
-      </c>
-      <c r="P129" s="16">
-        <v>3702.2</v>
-      </c>
-      <c r="Q129" s="16">
-        <v>3607.92</v>
-      </c>
-      <c r="R129" s="16">
-        <v>2170.11</v>
-      </c>
-      <c r="S129" s="16">
-        <v>1715.68</v>
-      </c>
-      <c r="T129" s="16">
-        <v>1429.0</v>
-      </c>
-      <c r="U129" s="16">
-        <v>1629.82</v>
-      </c>
-      <c r="V129" s="16">
-        <v>1051.47</v>
-      </c>
-      <c r="W129" s="16">
-        <v>814.49</v>
-      </c>
+      <c r="C129" s="16">
+        <v>2600.5</v>
+      </c>
+      <c r="D129" s="16">
+        <v>2192.27</v>
+      </c>
+      <c r="E129" s="16">
+        <v>1896.6</v>
+      </c>
+      <c r="F129" s="16">
+        <v>1966.26</v>
+      </c>
+      <c r="G129" s="16">
+        <v>2101.52</v>
+      </c>
+      <c r="H129" s="16">
+        <v>2342.06</v>
+      </c>
+      <c r="I129" s="15"/>
+      <c r="J129" s="15"/>
+      <c r="K129" s="15"/>
+      <c r="L129" s="15"/>
+      <c r="M129" s="15"/>
+      <c r="N129" s="15"/>
+      <c r="O129" s="15"/>
+      <c r="P129" s="15"/>
+      <c r="Q129" s="15"/>
+      <c r="R129" s="15"/>
+      <c r="S129" s="15"/>
+      <c r="T129" s="15"/>
+      <c r="U129" s="15"/>
+      <c r="V129" s="15"/>
+      <c r="W129" s="15"/>
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="B130" s="15"/>
+        <v>320</v>
+      </c>
+      <c r="B130" s="16">
+        <v>1228.66</v>
+      </c>
       <c r="C130" s="16">
-        <v>2600.5</v>
+        <v>1400.27</v>
       </c>
       <c r="D130" s="16">
-        <v>2192.27</v>
+        <v>984.28</v>
       </c>
       <c r="E130" s="16">
-        <v>1896.6</v>
+        <v>336.55</v>
       </c>
       <c r="F130" s="16">
-        <v>1966.26</v>
+        <v>425.49</v>
       </c>
       <c r="G130" s="16">
-        <v>2101.52</v>
+        <v>408.57</v>
       </c>
       <c r="H130" s="16">
-        <v>2342.06</v>
+        <v>310.96</v>
       </c>
       <c r="I130" s="15"/>
       <c r="J130" s="15"/>
@@ -16796,28 +16810,28 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="B131" s="16">
-        <v>1228.66</v>
+        <v>1476.75</v>
       </c>
       <c r="C131" s="16">
-        <v>1400.27</v>
+        <v>1200.23</v>
       </c>
       <c r="D131" s="16">
-        <v>984.28</v>
+        <v>1207.98</v>
       </c>
       <c r="E131" s="16">
-        <v>336.55</v>
+        <v>1560.06</v>
       </c>
       <c r="F131" s="16">
-        <v>425.49</v>
+        <v>1540.77</v>
       </c>
       <c r="G131" s="16">
-        <v>408.57</v>
+        <v>1692.95</v>
       </c>
       <c r="H131" s="16">
-        <v>310.96</v>
+        <v>2031.1</v>
       </c>
       <c r="I131" s="15"/>
       <c r="J131" s="15"/>
@@ -16837,304 +16851,290 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>299</v>
+        <v>125</v>
       </c>
       <c r="B132" s="16">
-        <v>1476.75</v>
+        <v>637.96</v>
       </c>
       <c r="C132" s="16">
-        <v>1200.23</v>
+        <v>400.08</v>
       </c>
       <c r="D132" s="16">
-        <v>1207.98</v>
+        <v>402.66</v>
       </c>
       <c r="E132" s="16">
-        <v>1560.06</v>
+        <v>575.59</v>
       </c>
       <c r="F132" s="16">
-        <v>1540.77</v>
+        <v>718.82</v>
       </c>
       <c r="G132" s="16">
-        <v>1692.95</v>
+        <v>428.48</v>
       </c>
       <c r="H132" s="16">
-        <v>2031.1</v>
-      </c>
-      <c r="I132" s="15"/>
-      <c r="J132" s="15"/>
-      <c r="K132" s="15"/>
-      <c r="L132" s="15"/>
-      <c r="M132" s="15"/>
-      <c r="N132" s="15"/>
-      <c r="O132" s="15"/>
-      <c r="P132" s="15"/>
-      <c r="Q132" s="15"/>
-      <c r="R132" s="15"/>
-      <c r="S132" s="15"/>
-      <c r="T132" s="15"/>
-      <c r="U132" s="15"/>
-      <c r="V132" s="15"/>
-      <c r="W132" s="15"/>
+        <v>312.93</v>
+      </c>
+      <c r="I132" s="16">
+        <v>458.73</v>
+      </c>
+      <c r="J132" s="16">
+        <v>589.72</v>
+      </c>
+      <c r="K132" s="20">
+        <v>72.64</v>
+      </c>
+      <c r="L132" s="16">
+        <v>411.84</v>
+      </c>
+      <c r="M132" s="16">
+        <v>403.91</v>
+      </c>
+      <c r="N132" s="16">
+        <v>386.59</v>
+      </c>
+      <c r="O132" s="16">
+        <v>270.12</v>
+      </c>
+      <c r="P132" s="16">
+        <v>221.35</v>
+      </c>
+      <c r="Q132" s="16">
+        <v>186.14</v>
+      </c>
+      <c r="R132" s="16">
+        <v>172.13</v>
+      </c>
+      <c r="S132" s="16">
+        <v>160.22</v>
+      </c>
+      <c r="T132" s="16">
+        <v>100.86</v>
+      </c>
+      <c r="U132" s="20">
+        <v>7.61</v>
+      </c>
+      <c r="V132" s="20">
+        <v>7.28</v>
+      </c>
+      <c r="W132" s="20">
+        <v>8.2</v>
+      </c>
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>125</v>
+        <v>313</v>
       </c>
       <c r="B133" s="16">
-        <v>637.96</v>
+        <v>472.56</v>
       </c>
       <c r="C133" s="16">
-        <v>400.08</v>
+        <v>411.84</v>
       </c>
       <c r="D133" s="16">
-        <v>402.66</v>
-      </c>
-      <c r="E133" s="16">
-        <v>575.59</v>
-      </c>
-      <c r="F133" s="16">
-        <v>718.82</v>
-      </c>
-      <c r="G133" s="16">
-        <v>428.48</v>
+        <v>123.04</v>
+      </c>
+      <c r="E133" s="20">
+        <v>73.39</v>
+      </c>
+      <c r="F133" s="20">
+        <v>68.08</v>
+      </c>
+      <c r="G133" s="20">
+        <v>95.33</v>
       </c>
       <c r="H133" s="16">
-        <v>312.93</v>
+        <v>143.67</v>
       </c>
       <c r="I133" s="16">
-        <v>458.73</v>
+        <v>183.29</v>
       </c>
       <c r="J133" s="16">
-        <v>589.72</v>
-      </c>
-      <c r="K133" s="20">
-        <v>72.64</v>
+        <v>280.59</v>
+      </c>
+      <c r="K133" s="16">
+        <v>116.23</v>
       </c>
       <c r="L133" s="16">
-        <v>411.84</v>
+        <v>188.16</v>
       </c>
       <c r="M133" s="16">
-        <v>403.91</v>
-      </c>
-      <c r="N133" s="16">
-        <v>386.59</v>
-      </c>
-      <c r="O133" s="16">
-        <v>270.12</v>
+        <v>122.86</v>
+      </c>
+      <c r="N133" s="20">
+        <v>77.7</v>
+      </c>
+      <c r="O133" s="20">
+        <v>85.45</v>
       </c>
       <c r="P133" s="16">
-        <v>221.35</v>
+        <v>103.44</v>
       </c>
       <c r="Q133" s="16">
-        <v>186.14</v>
+        <v>117.58</v>
       </c>
       <c r="R133" s="16">
-        <v>172.13</v>
+        <v>124.86</v>
       </c>
       <c r="S133" s="16">
-        <v>160.22</v>
-      </c>
-      <c r="T133" s="16">
-        <v>100.86</v>
+        <v>118.6</v>
+      </c>
+      <c r="T133" s="20">
+        <v>98.84</v>
       </c>
       <c r="U133" s="20">
-        <v>7.61</v>
-      </c>
-      <c r="V133" s="20">
-        <v>7.28</v>
+        <v>23.84</v>
+      </c>
+      <c r="V133" s="16">
+        <v>264.29</v>
       </c>
       <c r="W133" s="20">
-        <v>8.2</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B134" s="16">
-        <v>472.56</v>
+        <v>129.95</v>
       </c>
       <c r="C134" s="16">
-        <v>411.84</v>
+        <v>600.11</v>
       </c>
       <c r="D134" s="16">
-        <v>123.04</v>
-      </c>
-      <c r="E134" s="20">
-        <v>73.39</v>
-      </c>
-      <c r="F134" s="20">
-        <v>68.08</v>
-      </c>
-      <c r="G134" s="20">
-        <v>95.33</v>
-      </c>
-      <c r="H134" s="16">
-        <v>143.67</v>
-      </c>
-      <c r="I134" s="16">
-        <v>183.29</v>
-      </c>
-      <c r="J134" s="16">
-        <v>280.59</v>
-      </c>
-      <c r="K134" s="16">
-        <v>116.23</v>
-      </c>
-      <c r="L134" s="16">
-        <v>188.16</v>
-      </c>
-      <c r="M134" s="16">
-        <v>122.86</v>
-      </c>
-      <c r="N134" s="20">
-        <v>77.7</v>
-      </c>
-      <c r="O134" s="20">
-        <v>85.45</v>
-      </c>
-      <c r="P134" s="16">
-        <v>103.44</v>
-      </c>
-      <c r="Q134" s="16">
-        <v>117.58</v>
-      </c>
-      <c r="R134" s="16">
-        <v>124.86</v>
-      </c>
-      <c r="S134" s="16">
-        <v>118.6</v>
-      </c>
-      <c r="T134" s="20">
-        <v>98.84</v>
-      </c>
-      <c r="U134" s="20">
-        <v>23.84</v>
-      </c>
-      <c r="V134" s="16">
-        <v>264.29</v>
-      </c>
-      <c r="W134" s="20">
-        <v>15.41</v>
-      </c>
+        <v>536.88</v>
+      </c>
+      <c r="E134" s="15"/>
+      <c r="F134" s="15"/>
+      <c r="G134" s="15"/>
+      <c r="H134" s="15"/>
+      <c r="I134" s="15"/>
+      <c r="J134" s="15"/>
+      <c r="K134" s="15"/>
+      <c r="L134" s="15"/>
+      <c r="M134" s="15"/>
+      <c r="N134" s="15"/>
+      <c r="O134" s="15"/>
+      <c r="P134" s="15"/>
+      <c r="Q134" s="15"/>
+      <c r="R134" s="15"/>
+      <c r="S134" s="15"/>
+      <c r="T134" s="15"/>
+      <c r="U134" s="15"/>
+      <c r="V134" s="15"/>
+      <c r="W134" s="15"/>
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B135" s="16">
-        <v>129.95</v>
+        <v>425.3</v>
       </c>
       <c r="C135" s="16">
-        <v>600.11</v>
+        <v>494.21</v>
       </c>
       <c r="D135" s="16">
-        <v>536.88</v>
-      </c>
-      <c r="E135" s="15"/>
-      <c r="F135" s="15"/>
-      <c r="G135" s="15"/>
-      <c r="H135" s="15"/>
-      <c r="I135" s="15"/>
-      <c r="J135" s="15"/>
-      <c r="K135" s="15"/>
-      <c r="L135" s="15"/>
-      <c r="M135" s="15"/>
-      <c r="N135" s="15"/>
-      <c r="O135" s="15"/>
-      <c r="P135" s="15"/>
-      <c r="Q135" s="15"/>
-      <c r="R135" s="15"/>
-      <c r="S135" s="15"/>
-      <c r="T135" s="15"/>
-      <c r="U135" s="15"/>
-      <c r="V135" s="15"/>
-      <c r="W135" s="15"/>
+        <v>447.4</v>
+      </c>
+      <c r="E135" s="16">
+        <v>433.0</v>
+      </c>
+      <c r="F135" s="16">
+        <v>538.62</v>
+      </c>
+      <c r="G135" s="16">
+        <v>596.09</v>
+      </c>
+      <c r="H135" s="16">
+        <v>547.14</v>
+      </c>
+      <c r="I135" s="16">
+        <v>494.39</v>
+      </c>
+      <c r="J135" s="16">
+        <v>516.87</v>
+      </c>
+      <c r="K135" s="16">
+        <v>482.15</v>
+      </c>
+      <c r="L135" s="16">
+        <v>528.0</v>
+      </c>
+      <c r="M135" s="16">
+        <v>532.47</v>
+      </c>
+      <c r="N135" s="16">
+        <v>382.68</v>
+      </c>
+      <c r="O135" s="16">
+        <v>295.12</v>
+      </c>
+      <c r="P135" s="16">
+        <v>308.56</v>
+      </c>
+      <c r="Q135" s="16">
+        <v>306.03</v>
+      </c>
+      <c r="R135" s="16">
+        <v>317.39</v>
+      </c>
+      <c r="S135" s="16">
+        <v>365.45</v>
+      </c>
+      <c r="T135" s="16">
+        <v>304.93</v>
+      </c>
+      <c r="U135" s="16">
+        <v>318.17</v>
+      </c>
+      <c r="V135" s="16">
+        <v>304.12</v>
+      </c>
+      <c r="W135" s="16">
+        <v>308.55</v>
+      </c>
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>322</v>
-      </c>
-      <c r="B136" s="16">
-        <v>425.3</v>
-      </c>
-      <c r="C136" s="16">
-        <v>494.21</v>
+        <v>315</v>
+      </c>
+      <c r="B136" s="15">
+        <v>12487.41</v>
+      </c>
+      <c r="C136" s="15">
+        <v>11955.22</v>
       </c>
       <c r="D136" s="16">
-        <v>447.4</v>
-      </c>
-      <c r="E136" s="16">
-        <v>433.0</v>
-      </c>
-      <c r="F136" s="16">
-        <v>538.62</v>
-      </c>
-      <c r="G136" s="16">
-        <v>596.09</v>
-      </c>
-      <c r="H136" s="16">
-        <v>547.14</v>
-      </c>
-      <c r="I136" s="16">
-        <v>494.39</v>
-      </c>
-      <c r="J136" s="16">
-        <v>516.87</v>
-      </c>
-      <c r="K136" s="16">
-        <v>482.15</v>
-      </c>
-      <c r="L136" s="16">
-        <v>528.0</v>
-      </c>
-      <c r="M136" s="16">
-        <v>532.47</v>
-      </c>
-      <c r="N136" s="16">
-        <v>382.68</v>
-      </c>
-      <c r="O136" s="16">
-        <v>295.12</v>
-      </c>
-      <c r="P136" s="16">
-        <v>308.56</v>
-      </c>
-      <c r="Q136" s="16">
-        <v>306.03</v>
-      </c>
-      <c r="R136" s="16">
-        <v>317.39</v>
-      </c>
-      <c r="S136" s="16">
-        <v>365.45</v>
-      </c>
-      <c r="T136" s="16">
-        <v>304.93</v>
-      </c>
-      <c r="U136" s="16">
-        <v>318.17</v>
-      </c>
-      <c r="V136" s="16">
-        <v>304.12</v>
-      </c>
-      <c r="W136" s="16">
-        <v>308.55</v>
-      </c>
+        <v>3623.95</v>
+      </c>
+      <c r="E136" s="15"/>
+      <c r="F136" s="15"/>
+      <c r="G136" s="15"/>
+      <c r="H136" s="15"/>
+      <c r="I136" s="15"/>
+      <c r="J136" s="15"/>
+      <c r="K136" s="15"/>
+      <c r="L136" s="15"/>
+      <c r="M136" s="15"/>
+      <c r="N136" s="15"/>
+      <c r="O136" s="15"/>
+      <c r="P136" s="15"/>
+      <c r="Q136" s="15"/>
+      <c r="R136" s="15"/>
+      <c r="S136" s="15"/>
+      <c r="T136" s="15"/>
+      <c r="U136" s="15"/>
+      <c r="V136" s="15"/>
+      <c r="W136" s="15"/>
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>315</v>
-      </c>
-      <c r="B137" s="15">
-        <v>12487.41</v>
-      </c>
-      <c r="C137" s="15">
-        <v>11955.22</v>
-      </c>
-      <c r="D137" s="16">
-        <v>3623.95</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="B137" s="15"/>
+      <c r="C137" s="15"/>
+      <c r="D137" s="15"/>
       <c r="E137" s="15"/>
       <c r="F137" s="15"/>
       <c r="G137" s="15"/>
@@ -17153,18 +17153,26 @@
       <c r="T137" s="15"/>
       <c r="U137" s="15"/>
       <c r="V137" s="15"/>
-      <c r="W137" s="15"/>
+      <c r="W137" s="16">
+        <v>315.75</v>
+      </c>
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B138" s="15"/>
       <c r="C138" s="15"/>
       <c r="D138" s="15"/>
-      <c r="E138" s="15"/>
-      <c r="F138" s="15"/>
-      <c r="G138" s="15"/>
+      <c r="E138" s="16">
+        <v>552.52</v>
+      </c>
+      <c r="F138" s="16">
+        <v>625.72</v>
+      </c>
+      <c r="G138" s="16">
+        <v>702.95</v>
+      </c>
       <c r="H138" s="15"/>
       <c r="I138" s="15"/>
       <c r="J138" s="15"/>
@@ -17180,25 +17188,23 @@
       <c r="T138" s="15"/>
       <c r="U138" s="15"/>
       <c r="V138" s="15"/>
-      <c r="W138" s="16">
-        <v>315.75</v>
-      </c>
+      <c r="W138" s="15"/>
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B139" s="15"/>
       <c r="C139" s="15"/>
       <c r="D139" s="15"/>
-      <c r="E139" s="16">
-        <v>552.52</v>
-      </c>
-      <c r="F139" s="16">
-        <v>625.72</v>
-      </c>
-      <c r="G139" s="16">
-        <v>702.95</v>
+      <c r="E139" s="20">
+        <v>46.13</v>
+      </c>
+      <c r="F139" s="20">
+        <v>19.02</v>
+      </c>
+      <c r="G139" s="20">
+        <v>11.52</v>
       </c>
       <c r="H139" s="15"/>
       <c r="I139" s="15"/>
@@ -17218,373 +17224,399 @@
       <c r="W139" s="15"/>
     </row>
     <row r="140" ht="15.0" customHeight="1">
-      <c r="A140" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="B140" s="15"/>
-      <c r="C140" s="15"/>
-      <c r="D140" s="15"/>
-      <c r="E140" s="20">
-        <v>46.13</v>
-      </c>
-      <c r="F140" s="20">
-        <v>19.02</v>
-      </c>
-      <c r="G140" s="20">
-        <v>11.52</v>
-      </c>
-      <c r="H140" s="15"/>
-      <c r="I140" s="15"/>
-      <c r="J140" s="15"/>
-      <c r="K140" s="15"/>
-      <c r="L140" s="15"/>
-      <c r="M140" s="15"/>
-      <c r="N140" s="15"/>
-      <c r="O140" s="15"/>
-      <c r="P140" s="15"/>
-      <c r="Q140" s="15"/>
-      <c r="R140" s="15"/>
-      <c r="S140" s="15"/>
-      <c r="T140" s="15"/>
-      <c r="U140" s="15"/>
-      <c r="V140" s="15"/>
-      <c r="W140" s="15"/>
+      <c r="A140" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="B140" s="18">
+        <v>16858.59</v>
+      </c>
+      <c r="C140" s="18">
+        <v>16461.97</v>
+      </c>
+      <c r="D140" s="19">
+        <v>7326.2</v>
+      </c>
+      <c r="E140" s="19">
+        <v>3024.71</v>
+      </c>
+      <c r="F140" s="19">
+        <v>3310.8</v>
+      </c>
+      <c r="G140" s="19">
+        <v>3232.95</v>
+      </c>
+      <c r="H140" s="19">
+        <v>3345.8</v>
+      </c>
+      <c r="I140" s="19">
+        <v>3795.63</v>
+      </c>
+      <c r="J140" s="19">
+        <v>4663.64</v>
+      </c>
+      <c r="K140" s="19">
+        <v>1424.67</v>
+      </c>
+      <c r="L140" s="19">
+        <v>2509.45</v>
+      </c>
+      <c r="M140" s="19">
+        <v>2661.89</v>
+      </c>
+      <c r="N140" s="19">
+        <v>3192.8</v>
+      </c>
+      <c r="O140" s="19">
+        <v>1186.29</v>
+      </c>
+      <c r="P140" s="19">
+        <v>4335.56</v>
+      </c>
+      <c r="Q140" s="19">
+        <v>4217.67</v>
+      </c>
+      <c r="R140" s="19">
+        <v>2784.49</v>
+      </c>
+      <c r="S140" s="19">
+        <v>2359.94</v>
+      </c>
+      <c r="T140" s="19">
+        <v>1933.64</v>
+      </c>
+      <c r="U140" s="19">
+        <v>1979.45</v>
+      </c>
+      <c r="V140" s="19">
+        <v>1627.17</v>
+      </c>
+      <c r="W140" s="19">
+        <v>1462.39</v>
+      </c>
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="17" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B141" s="18">
-        <v>16858.59</v>
+        <v>40191.25</v>
       </c>
       <c r="C141" s="18">
-        <v>16461.97</v>
-      </c>
-      <c r="D141" s="19">
-        <v>7326.2</v>
-      </c>
-      <c r="E141" s="19">
-        <v>3024.71</v>
-      </c>
-      <c r="F141" s="19">
-        <v>3310.8</v>
-      </c>
-      <c r="G141" s="19">
-        <v>3232.95</v>
+        <v>35371.46</v>
+      </c>
+      <c r="D141" s="18">
+        <v>22694.45</v>
+      </c>
+      <c r="E141" s="18">
+        <v>17022.26</v>
+      </c>
+      <c r="F141" s="18">
+        <v>13951.0</v>
+      </c>
+      <c r="G141" s="18">
+        <v>11253.52</v>
       </c>
       <c r="H141" s="19">
-        <v>3345.8</v>
+        <v>9698.89</v>
       </c>
       <c r="I141" s="19">
-        <v>3795.63</v>
-      </c>
-      <c r="J141" s="19">
-        <v>4663.64</v>
+        <v>9547.04</v>
+      </c>
+      <c r="J141" s="18">
+        <v>10714.46</v>
       </c>
       <c r="K141" s="19">
-        <v>1424.67</v>
+        <v>7225.04</v>
       </c>
       <c r="L141" s="19">
-        <v>2509.45</v>
+        <v>8391.38</v>
       </c>
       <c r="M141" s="19">
-        <v>2661.89</v>
+        <v>7724.76</v>
       </c>
       <c r="N141" s="19">
-        <v>3192.8</v>
+        <v>8185.51</v>
       </c>
       <c r="O141" s="19">
-        <v>1186.29</v>
+        <v>7086.45</v>
       </c>
       <c r="P141" s="19">
-        <v>4335.56</v>
+        <v>9753.84</v>
       </c>
       <c r="Q141" s="19">
-        <v>4217.67</v>
+        <v>8824.67</v>
       </c>
       <c r="R141" s="19">
-        <v>2784.49</v>
+        <v>7116.92</v>
       </c>
       <c r="S141" s="19">
-        <v>2359.94</v>
+        <v>8441.79</v>
       </c>
       <c r="T141" s="19">
-        <v>1933.64</v>
+        <v>6188.73</v>
       </c>
       <c r="U141" s="19">
-        <v>1979.45</v>
+        <v>5015.18</v>
       </c>
       <c r="V141" s="19">
-        <v>1627.17</v>
+        <v>3685.89</v>
       </c>
       <c r="W141" s="19">
-        <v>1462.39</v>
+        <v>3456.99</v>
       </c>
     </row>
     <row r="142" ht="15.0" customHeight="1">
-      <c r="A142" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="B142" s="18">
-        <v>40191.25</v>
-      </c>
-      <c r="C142" s="18">
-        <v>35371.46</v>
-      </c>
-      <c r="D142" s="18">
-        <v>22694.45</v>
-      </c>
-      <c r="E142" s="18">
-        <v>17022.26</v>
-      </c>
-      <c r="F142" s="18">
-        <v>13951.0</v>
-      </c>
-      <c r="G142" s="18">
-        <v>11253.52</v>
-      </c>
-      <c r="H142" s="19">
-        <v>9698.89</v>
-      </c>
-      <c r="I142" s="19">
-        <v>9547.04</v>
-      </c>
-      <c r="J142" s="18">
-        <v>10714.46</v>
-      </c>
-      <c r="K142" s="19">
-        <v>7225.04</v>
-      </c>
-      <c r="L142" s="19">
-        <v>8391.38</v>
-      </c>
-      <c r="M142" s="19">
-        <v>7724.76</v>
-      </c>
-      <c r="N142" s="19">
-        <v>8185.51</v>
-      </c>
-      <c r="O142" s="19">
-        <v>7086.45</v>
-      </c>
-      <c r="P142" s="19">
-        <v>9753.84</v>
-      </c>
-      <c r="Q142" s="19">
-        <v>8824.67</v>
-      </c>
-      <c r="R142" s="19">
-        <v>7116.92</v>
-      </c>
-      <c r="S142" s="19">
-        <v>8441.79</v>
-      </c>
-      <c r="T142" s="19">
-        <v>6188.73</v>
-      </c>
-      <c r="U142" s="19">
-        <v>5015.18</v>
-      </c>
-      <c r="V142" s="19">
-        <v>3685.89</v>
-      </c>
-      <c r="W142" s="19">
-        <v>3456.99</v>
+      <c r="A142" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="B142" s="16">
+        <v>1701.22</v>
+      </c>
+      <c r="C142" s="16">
+        <v>1694.44</v>
+      </c>
+      <c r="D142" s="16">
+        <v>1610.65</v>
+      </c>
+      <c r="E142" s="16">
+        <v>1209.88</v>
+      </c>
+      <c r="F142" s="16">
+        <v>1155.32</v>
+      </c>
+      <c r="G142" s="16">
+        <v>1208.95</v>
+      </c>
+      <c r="H142" s="16">
+        <v>720.33</v>
+      </c>
+      <c r="I142" s="16">
+        <v>721.28</v>
+      </c>
+      <c r="J142" s="16">
+        <v>716.73</v>
+      </c>
+      <c r="K142" s="16">
+        <v>653.77</v>
+      </c>
+      <c r="L142" s="16">
+        <v>623.04</v>
+      </c>
+      <c r="M142" s="16">
+        <v>581.16</v>
+      </c>
+      <c r="N142" s="16">
+        <v>535.06</v>
+      </c>
+      <c r="O142" s="16">
+        <v>470.34</v>
+      </c>
+      <c r="P142" s="16">
+        <v>494.11</v>
+      </c>
+      <c r="Q142" s="16">
+        <v>496.25</v>
+      </c>
+      <c r="R142" s="16">
+        <v>528.87</v>
+      </c>
+      <c r="S142" s="16">
+        <v>618.95</v>
+      </c>
+      <c r="T142" s="16">
+        <v>503.04</v>
+      </c>
+      <c r="U142" s="16">
+        <v>518.7</v>
+      </c>
+      <c r="V142" s="16">
+        <v>524.72</v>
+      </c>
+      <c r="W142" s="16">
+        <v>543.06</v>
       </c>
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="B143" s="16">
-        <v>1701.22</v>
-      </c>
-      <c r="C143" s="16">
-        <v>1694.44</v>
-      </c>
-      <c r="D143" s="16">
-        <v>1610.65</v>
-      </c>
-      <c r="E143" s="16">
-        <v>1209.88</v>
-      </c>
-      <c r="F143" s="16">
-        <v>1155.32</v>
-      </c>
-      <c r="G143" s="16">
-        <v>1208.95</v>
-      </c>
-      <c r="H143" s="16">
-        <v>720.33</v>
-      </c>
-      <c r="I143" s="16">
-        <v>721.28</v>
-      </c>
-      <c r="J143" s="16">
-        <v>716.73</v>
-      </c>
-      <c r="K143" s="16">
-        <v>653.77</v>
-      </c>
-      <c r="L143" s="16">
-        <v>623.04</v>
-      </c>
-      <c r="M143" s="16">
-        <v>581.16</v>
-      </c>
-      <c r="N143" s="16">
-        <v>535.06</v>
-      </c>
-      <c r="O143" s="16">
-        <v>470.34</v>
-      </c>
-      <c r="P143" s="16">
-        <v>494.11</v>
-      </c>
-      <c r="Q143" s="16">
-        <v>496.25</v>
-      </c>
-      <c r="R143" s="16">
-        <v>528.87</v>
-      </c>
-      <c r="S143" s="16">
-        <v>618.95</v>
-      </c>
-      <c r="T143" s="16">
-        <v>503.04</v>
-      </c>
-      <c r="U143" s="16">
-        <v>518.7</v>
-      </c>
-      <c r="V143" s="16">
-        <v>524.72</v>
-      </c>
-      <c r="W143" s="16">
-        <v>543.06</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="B143" s="15">
+        <v>21714.14</v>
+      </c>
+      <c r="C143" s="15">
+        <v>18485.88</v>
+      </c>
+      <c r="D143" s="15">
+        <v>13958.93</v>
+      </c>
+      <c r="E143" s="15"/>
+      <c r="F143" s="15"/>
+      <c r="G143" s="15"/>
+      <c r="H143" s="15"/>
+      <c r="I143" s="15"/>
+      <c r="J143" s="15"/>
+      <c r="K143" s="15"/>
+      <c r="L143" s="15"/>
+      <c r="M143" s="15"/>
+      <c r="N143" s="15"/>
+      <c r="O143" s="15"/>
+      <c r="P143" s="15"/>
+      <c r="Q143" s="15"/>
+      <c r="R143" s="15"/>
+      <c r="S143" s="15"/>
+      <c r="T143" s="15"/>
+      <c r="U143" s="15"/>
+      <c r="V143" s="15"/>
+      <c r="W143" s="15"/>
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>329</v>
-      </c>
-      <c r="B144" s="15">
-        <v>21714.14</v>
-      </c>
-      <c r="C144" s="15">
-        <v>18485.88</v>
-      </c>
-      <c r="D144" s="15">
-        <v>13958.93</v>
-      </c>
-      <c r="E144" s="15"/>
-      <c r="F144" s="15"/>
-      <c r="G144" s="15"/>
-      <c r="H144" s="15"/>
-      <c r="I144" s="15"/>
-      <c r="J144" s="15"/>
-      <c r="K144" s="15"/>
-      <c r="L144" s="15"/>
-      <c r="M144" s="15"/>
-      <c r="N144" s="15"/>
-      <c r="O144" s="15"/>
+        <v>330</v>
+      </c>
+      <c r="B144" s="16">
+        <v>661.58</v>
+      </c>
+      <c r="C144" s="22">
+        <v>-200.04</v>
+      </c>
+      <c r="D144" s="16">
+        <v>313.18</v>
+      </c>
+      <c r="E144" s="16">
+        <v>721.32</v>
+      </c>
+      <c r="F144" s="16">
+        <v>1476.69</v>
+      </c>
+      <c r="G144" s="16">
+        <v>661.05</v>
+      </c>
+      <c r="H144" s="22">
+        <v>-332.61</v>
+      </c>
+      <c r="I144" s="22">
+        <v>-286.33</v>
+      </c>
+      <c r="J144" s="21">
+        <v>-50.21</v>
+      </c>
+      <c r="K144" s="16">
+        <v>271.5</v>
+      </c>
+      <c r="L144" s="16">
+        <v>303.36</v>
+      </c>
+      <c r="M144" s="16">
+        <v>233.34</v>
+      </c>
+      <c r="N144" s="20">
+        <v>23.37</v>
+      </c>
+      <c r="O144" s="16">
+        <v>127.58</v>
+      </c>
       <c r="P144" s="15"/>
       <c r="Q144" s="15"/>
-      <c r="R144" s="15"/>
-      <c r="S144" s="15"/>
-      <c r="T144" s="15"/>
-      <c r="U144" s="15"/>
+      <c r="R144" s="21">
+        <v>-30.99</v>
+      </c>
+      <c r="S144" s="21">
+        <v>-96.29</v>
+      </c>
+      <c r="T144" s="22">
+        <v>-119.16</v>
+      </c>
+      <c r="U144" s="20">
+        <v>17.0</v>
+      </c>
       <c r="V144" s="15"/>
       <c r="W144" s="15"/>
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="B145" s="16">
-        <v>661.58</v>
-      </c>
-      <c r="C145" s="22">
-        <v>-200.04</v>
-      </c>
-      <c r="D145" s="16">
-        <v>313.18</v>
-      </c>
-      <c r="E145" s="16">
-        <v>721.32</v>
-      </c>
-      <c r="F145" s="16">
-        <v>1476.69</v>
-      </c>
-      <c r="G145" s="16">
-        <v>661.05</v>
-      </c>
-      <c r="H145" s="22">
-        <v>-332.61</v>
-      </c>
-      <c r="I145" s="22">
-        <v>-286.33</v>
-      </c>
-      <c r="J145" s="21">
-        <v>-50.21</v>
-      </c>
-      <c r="K145" s="16">
-        <v>271.5</v>
-      </c>
-      <c r="L145" s="16">
-        <v>303.36</v>
-      </c>
-      <c r="M145" s="16">
-        <v>233.34</v>
-      </c>
-      <c r="N145" s="20">
-        <v>23.37</v>
-      </c>
-      <c r="O145" s="16">
-        <v>127.58</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="B145" s="22">
+        <v>-236.28</v>
+      </c>
+      <c r="C145" s="21">
+        <v>-35.3</v>
+      </c>
+      <c r="D145" s="21">
+        <v>-44.74</v>
+      </c>
+      <c r="E145" s="15"/>
+      <c r="F145" s="15"/>
+      <c r="G145" s="15"/>
+      <c r="H145" s="15"/>
+      <c r="I145" s="15"/>
+      <c r="J145" s="15"/>
+      <c r="K145" s="15"/>
+      <c r="L145" s="15"/>
+      <c r="M145" s="15"/>
+      <c r="N145" s="15"/>
+      <c r="O145" s="15"/>
       <c r="P145" s="15"/>
       <c r="Q145" s="15"/>
-      <c r="R145" s="21">
-        <v>-30.99</v>
-      </c>
-      <c r="S145" s="21">
-        <v>-96.29</v>
-      </c>
-      <c r="T145" s="22">
-        <v>-119.16</v>
-      </c>
-      <c r="U145" s="20">
-        <v>17.0</v>
-      </c>
+      <c r="R145" s="15"/>
+      <c r="S145" s="15"/>
+      <c r="T145" s="15"/>
+      <c r="U145" s="15"/>
       <c r="V145" s="15"/>
       <c r="W145" s="15"/>
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B146" s="22">
-        <v>-236.28</v>
-      </c>
-      <c r="C146" s="21">
-        <v>-35.3</v>
-      </c>
-      <c r="D146" s="21">
-        <v>-44.74</v>
-      </c>
-      <c r="E146" s="15"/>
-      <c r="F146" s="15"/>
-      <c r="G146" s="15"/>
-      <c r="H146" s="15"/>
-      <c r="I146" s="15"/>
-      <c r="J146" s="15"/>
-      <c r="K146" s="15"/>
-      <c r="L146" s="15"/>
-      <c r="M146" s="15"/>
-      <c r="N146" s="15"/>
-      <c r="O146" s="15"/>
-      <c r="P146" s="15"/>
-      <c r="Q146" s="15"/>
+        <v>-354.42</v>
+      </c>
+      <c r="C146" s="22">
+        <v>-929.59</v>
+      </c>
+      <c r="D146" s="22">
+        <v>-626.36</v>
+      </c>
+      <c r="E146" s="22">
+        <v>-664.7</v>
+      </c>
+      <c r="F146" s="22">
+        <v>-186.21</v>
+      </c>
+      <c r="G146" s="21">
+        <v>-95.33</v>
+      </c>
+      <c r="H146" s="22">
+        <v>-335.56</v>
+      </c>
+      <c r="I146" s="22">
+        <v>-273.45</v>
+      </c>
+      <c r="J146" s="20">
+        <v>39.38</v>
+      </c>
+      <c r="K146" s="16">
+        <v>218.83</v>
+      </c>
+      <c r="L146" s="16">
+        <v>328.32</v>
+      </c>
+      <c r="M146" s="16">
+        <v>182.35</v>
+      </c>
+      <c r="N146" s="20">
+        <v>16.43</v>
+      </c>
+      <c r="O146" s="16">
+        <v>140.67</v>
+      </c>
+      <c r="P146" s="16">
+        <v>128.0</v>
+      </c>
+      <c r="Q146" s="16">
+        <v>122.18</v>
+      </c>
       <c r="R146" s="15"/>
       <c r="S146" s="15"/>
       <c r="T146" s="15"/>
@@ -17594,55 +17626,55 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="B147" s="22">
-        <v>-354.42</v>
-      </c>
-      <c r="C147" s="22">
-        <v>-929.59</v>
-      </c>
-      <c r="D147" s="22">
-        <v>-626.36</v>
-      </c>
-      <c r="E147" s="22">
-        <v>-664.7</v>
-      </c>
-      <c r="F147" s="22">
-        <v>-186.21</v>
-      </c>
-      <c r="G147" s="21">
-        <v>-95.33</v>
-      </c>
-      <c r="H147" s="22">
-        <v>-335.56</v>
-      </c>
-      <c r="I147" s="22">
-        <v>-273.45</v>
-      </c>
-      <c r="J147" s="20">
-        <v>39.38</v>
-      </c>
-      <c r="K147" s="16">
-        <v>218.83</v>
-      </c>
-      <c r="L147" s="16">
-        <v>328.32</v>
-      </c>
-      <c r="M147" s="16">
-        <v>182.35</v>
+        <v>333</v>
+      </c>
+      <c r="B147" s="16">
+        <v>1252.28</v>
+      </c>
+      <c r="C147" s="16">
+        <v>764.85</v>
+      </c>
+      <c r="D147" s="16">
+        <v>995.47</v>
+      </c>
+      <c r="E147" s="16">
+        <v>1382.87</v>
+      </c>
+      <c r="F147" s="16">
+        <v>1659.9</v>
+      </c>
+      <c r="G147" s="16">
+        <v>753.24</v>
+      </c>
+      <c r="H147" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="I147" s="21">
+        <v>-15.85</v>
+      </c>
+      <c r="J147" s="21">
+        <v>-92.54</v>
+      </c>
+      <c r="K147" s="20">
+        <v>37.23</v>
+      </c>
+      <c r="L147" s="21">
+        <v>-38.4</v>
+      </c>
+      <c r="M147" s="20">
+        <v>43.1</v>
       </c>
       <c r="N147" s="20">
-        <v>16.43</v>
-      </c>
-      <c r="O147" s="16">
-        <v>140.67</v>
-      </c>
-      <c r="P147" s="16">
-        <v>128.0</v>
-      </c>
-      <c r="Q147" s="16">
-        <v>122.18</v>
+        <v>2.01</v>
+      </c>
+      <c r="O147" s="21">
+        <v>-16.64</v>
+      </c>
+      <c r="P147" s="21">
+        <v>-87.1</v>
+      </c>
+      <c r="Q147" s="20">
+        <v>58.32</v>
       </c>
       <c r="R147" s="15"/>
       <c r="S147" s="15"/>
@@ -17653,56 +17685,26 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="B148" s="16">
-        <v>1252.28</v>
-      </c>
-      <c r="C148" s="16">
-        <v>764.85</v>
-      </c>
-      <c r="D148" s="16">
-        <v>995.47</v>
-      </c>
-      <c r="E148" s="16">
-        <v>1382.87</v>
-      </c>
-      <c r="F148" s="16">
-        <v>1659.9</v>
-      </c>
-      <c r="G148" s="16">
-        <v>753.24</v>
-      </c>
-      <c r="H148" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="I148" s="21">
-        <v>-15.85</v>
-      </c>
-      <c r="J148" s="21">
-        <v>-92.54</v>
-      </c>
-      <c r="K148" s="20">
-        <v>37.23</v>
-      </c>
-      <c r="L148" s="21">
-        <v>-38.4</v>
-      </c>
-      <c r="M148" s="20">
-        <v>43.1</v>
-      </c>
-      <c r="N148" s="20">
-        <v>2.01</v>
-      </c>
-      <c r="O148" s="21">
-        <v>-16.64</v>
-      </c>
-      <c r="P148" s="21">
-        <v>-87.1</v>
-      </c>
-      <c r="Q148" s="20">
-        <v>58.32</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="B148" s="15"/>
+      <c r="C148" s="15"/>
+      <c r="D148" s="21">
+        <v>-11.19</v>
+      </c>
+      <c r="E148" s="15"/>
+      <c r="F148" s="15"/>
+      <c r="G148" s="15"/>
+      <c r="H148" s="15"/>
+      <c r="I148" s="15"/>
+      <c r="J148" s="15"/>
+      <c r="K148" s="15"/>
+      <c r="L148" s="15"/>
+      <c r="M148" s="15"/>
+      <c r="N148" s="15"/>
+      <c r="O148" s="15"/>
+      <c r="P148" s="15"/>
+      <c r="Q148" s="15"/>
       <c r="R148" s="15"/>
       <c r="S148" s="15"/>
       <c r="T148" s="15"/>
@@ -17712,26 +17714,50 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
-      <c r="D149" s="21">
-        <v>-11.19</v>
-      </c>
-      <c r="E149" s="15"/>
-      <c r="F149" s="15"/>
-      <c r="G149" s="15"/>
-      <c r="H149" s="15"/>
-      <c r="I149" s="15"/>
-      <c r="J149" s="15"/>
-      <c r="K149" s="15"/>
-      <c r="L149" s="15"/>
-      <c r="M149" s="15"/>
-      <c r="N149" s="15"/>
-      <c r="O149" s="15"/>
-      <c r="P149" s="15"/>
-      <c r="Q149" s="15"/>
+      <c r="D149" s="15"/>
+      <c r="E149" s="20">
+        <v>3.15</v>
+      </c>
+      <c r="F149" s="20">
+        <v>3.0</v>
+      </c>
+      <c r="G149" s="20">
+        <v>3.14</v>
+      </c>
+      <c r="H149" s="20">
+        <v>2.95</v>
+      </c>
+      <c r="I149" s="20">
+        <v>2.97</v>
+      </c>
+      <c r="J149" s="20">
+        <v>2.95</v>
+      </c>
+      <c r="K149" s="20">
+        <v>15.44</v>
+      </c>
+      <c r="L149" s="20">
+        <v>13.44</v>
+      </c>
+      <c r="M149" s="20">
+        <v>7.89</v>
+      </c>
+      <c r="N149" s="20">
+        <v>4.92</v>
+      </c>
+      <c r="O149" s="20">
+        <v>3.54</v>
+      </c>
+      <c r="P149" s="20">
+        <v>2.91</v>
+      </c>
+      <c r="Q149" s="20">
+        <v>0.21</v>
+      </c>
       <c r="R149" s="15"/>
       <c r="S149" s="15"/>
       <c r="T149" s="15"/>
@@ -17741,125 +17767,103 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
       <c r="D150" s="15"/>
-      <c r="E150" s="20">
-        <v>3.15</v>
-      </c>
-      <c r="F150" s="20">
-        <v>3.0</v>
-      </c>
-      <c r="G150" s="20">
-        <v>3.14</v>
-      </c>
-      <c r="H150" s="20">
-        <v>2.95</v>
-      </c>
-      <c r="I150" s="20">
-        <v>2.97</v>
-      </c>
-      <c r="J150" s="20">
-        <v>2.95</v>
-      </c>
-      <c r="K150" s="20">
-        <v>15.44</v>
-      </c>
-      <c r="L150" s="20">
-        <v>13.44</v>
-      </c>
-      <c r="M150" s="20">
-        <v>7.89</v>
-      </c>
-      <c r="N150" s="20">
-        <v>4.92</v>
-      </c>
-      <c r="O150" s="20">
-        <v>3.54</v>
-      </c>
-      <c r="P150" s="20">
-        <v>2.91</v>
-      </c>
-      <c r="Q150" s="20">
-        <v>0.21</v>
-      </c>
-      <c r="R150" s="15"/>
-      <c r="S150" s="15"/>
-      <c r="T150" s="15"/>
-      <c r="U150" s="15"/>
-      <c r="V150" s="15"/>
-      <c r="W150" s="15"/>
+      <c r="E150" s="16">
+        <v>8449.27</v>
+      </c>
+      <c r="F150" s="16">
+        <v>7454.55</v>
+      </c>
+      <c r="G150" s="16">
+        <v>7810.0</v>
+      </c>
+      <c r="H150" s="16">
+        <v>6022.44</v>
+      </c>
+      <c r="I150" s="16">
+        <v>6928.44</v>
+      </c>
+      <c r="J150" s="16">
+        <v>7370.07</v>
+      </c>
+      <c r="K150" s="16">
+        <v>7713.55</v>
+      </c>
+      <c r="L150" s="16">
+        <v>6711.38</v>
+      </c>
+      <c r="M150" s="16">
+        <v>6316.24</v>
+      </c>
+      <c r="N150" s="16">
+        <v>5683.4</v>
+      </c>
+      <c r="O150" s="16">
+        <v>4854.43</v>
+      </c>
+      <c r="P150" s="16">
+        <v>3637.37</v>
+      </c>
+      <c r="Q150" s="16">
+        <v>3564.24</v>
+      </c>
+      <c r="R150" s="16">
+        <v>3555.39</v>
+      </c>
+      <c r="S150" s="16">
+        <v>3948.8</v>
+      </c>
+      <c r="T150" s="16">
+        <v>2793.21</v>
+      </c>
+      <c r="U150" s="16">
+        <v>2280.41</v>
+      </c>
+      <c r="V150" s="16">
+        <v>1879.14</v>
+      </c>
+      <c r="W150" s="16">
+        <v>2200.85</v>
+      </c>
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
       <c r="D151" s="15"/>
-      <c r="E151" s="16">
-        <v>8449.27</v>
-      </c>
-      <c r="F151" s="16">
-        <v>7454.55</v>
-      </c>
-      <c r="G151" s="16">
-        <v>7810.0</v>
-      </c>
-      <c r="H151" s="16">
-        <v>6022.44</v>
-      </c>
-      <c r="I151" s="16">
-        <v>6928.44</v>
-      </c>
-      <c r="J151" s="16">
-        <v>7370.07</v>
-      </c>
-      <c r="K151" s="16">
-        <v>7713.55</v>
-      </c>
-      <c r="L151" s="16">
-        <v>6711.38</v>
-      </c>
-      <c r="M151" s="16">
-        <v>6316.24</v>
-      </c>
-      <c r="N151" s="16">
-        <v>5683.4</v>
-      </c>
-      <c r="O151" s="16">
-        <v>4854.43</v>
-      </c>
-      <c r="P151" s="16">
-        <v>3637.37</v>
-      </c>
-      <c r="Q151" s="16">
-        <v>3564.24</v>
-      </c>
-      <c r="R151" s="16">
-        <v>3555.39</v>
-      </c>
-      <c r="S151" s="16">
-        <v>3948.8</v>
-      </c>
-      <c r="T151" s="16">
-        <v>2793.21</v>
-      </c>
-      <c r="U151" s="16">
-        <v>2280.41</v>
-      </c>
+      <c r="E151" s="15"/>
+      <c r="F151" s="15"/>
+      <c r="G151" s="15"/>
+      <c r="H151" s="15"/>
+      <c r="I151" s="15"/>
+      <c r="J151" s="15"/>
+      <c r="K151" s="15"/>
+      <c r="L151" s="15"/>
+      <c r="M151" s="15"/>
+      <c r="N151" s="15"/>
+      <c r="O151" s="15"/>
+      <c r="P151" s="15"/>
+      <c r="Q151" s="15"/>
+      <c r="R151" s="15"/>
+      <c r="S151" s="15"/>
+      <c r="T151" s="15"/>
+      <c r="U151" s="15"/>
       <c r="V151" s="16">
-        <v>1879.14</v>
-      </c>
-      <c r="W151" s="16">
-        <v>2200.85</v>
+        <v>142.32</v>
+      </c>
+      <c r="W151" s="20">
+        <v>2.11</v>
       </c>
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -17868,516 +17872,556 @@
       <c r="F152" s="15"/>
       <c r="G152" s="15"/>
       <c r="H152" s="15"/>
-      <c r="I152" s="15"/>
-      <c r="J152" s="15"/>
-      <c r="K152" s="15"/>
-      <c r="L152" s="15"/>
-      <c r="M152" s="15"/>
-      <c r="N152" s="15"/>
-      <c r="O152" s="15"/>
-      <c r="P152" s="15"/>
-      <c r="Q152" s="15"/>
-      <c r="R152" s="15"/>
-      <c r="S152" s="15"/>
-      <c r="T152" s="15"/>
-      <c r="U152" s="15"/>
+      <c r="I152" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="J152" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="K152" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="L152" s="16">
+        <v>124.8</v>
+      </c>
+      <c r="M152" s="16">
+        <v>116.18</v>
+      </c>
+      <c r="N152" s="20">
+        <v>93.69</v>
+      </c>
+      <c r="O152" s="16">
+        <v>188.12</v>
+      </c>
+      <c r="P152" s="20">
+        <v>49.43</v>
+      </c>
+      <c r="Q152" s="20">
+        <v>49.65</v>
+      </c>
+      <c r="R152" s="20">
+        <v>92.53</v>
+      </c>
+      <c r="S152" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="T152" s="16">
+        <v>276.63</v>
+      </c>
+      <c r="U152" s="16">
+        <v>259.35</v>
+      </c>
       <c r="V152" s="16">
-        <v>142.32</v>
-      </c>
-      <c r="W152" s="20">
-        <v>2.11</v>
+        <v>314.83</v>
+      </c>
+      <c r="W152" s="16">
+        <v>217.23</v>
       </c>
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="B153" s="15"/>
-      <c r="C153" s="15"/>
-      <c r="D153" s="15"/>
-      <c r="E153" s="15"/>
-      <c r="F153" s="15"/>
-      <c r="G153" s="15"/>
-      <c r="H153" s="15"/>
-      <c r="I153" s="15">
+        <v>339</v>
+      </c>
+      <c r="B153" s="16">
+        <v>1831.17</v>
+      </c>
+      <c r="C153" s="16">
+        <v>1823.88</v>
+      </c>
+      <c r="D153" s="16">
+        <v>1733.68</v>
+      </c>
+      <c r="E153" s="16">
+        <v>1610.38</v>
+      </c>
+      <c r="F153" s="16">
+        <v>1525.75</v>
+      </c>
+      <c r="G153" s="16">
+        <v>1596.57</v>
+      </c>
+      <c r="H153" s="16">
+        <v>1499.71</v>
+      </c>
+      <c r="I153" s="16">
+        <v>1509.93</v>
+      </c>
+      <c r="J153" s="15"/>
+      <c r="K153" s="15"/>
+      <c r="L153" s="15"/>
+      <c r="M153" s="15"/>
+      <c r="N153" s="15"/>
+      <c r="O153" s="15"/>
+      <c r="P153" s="15"/>
+      <c r="Q153" s="15"/>
+      <c r="R153" s="15"/>
+      <c r="S153" s="15"/>
+      <c r="T153" s="15"/>
+      <c r="U153" s="15"/>
+      <c r="V153" s="15"/>
+      <c r="W153" s="15"/>
+    </row>
+    <row r="154" ht="15.0" customHeight="1">
+      <c r="A154" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="B154" s="18">
+        <v>25908.12</v>
+      </c>
+      <c r="C154" s="18">
+        <v>21804.16</v>
+      </c>
+      <c r="D154" s="18">
+        <v>17616.44</v>
+      </c>
+      <c r="E154" s="18">
+        <v>11990.86</v>
+      </c>
+      <c r="F154" s="18">
+        <v>11612.32</v>
+      </c>
+      <c r="G154" s="18">
+        <v>11276.57</v>
+      </c>
+      <c r="H154" s="19">
+        <v>7909.87</v>
+      </c>
+      <c r="I154" s="19">
+        <v>8873.31</v>
+      </c>
+      <c r="J154" s="19">
+        <v>8036.58</v>
+      </c>
+      <c r="K154" s="19">
+        <v>8638.82</v>
+      </c>
+      <c r="L154" s="19">
+        <v>7762.58</v>
+      </c>
+      <c r="M154" s="19">
+        <v>7246.92</v>
+      </c>
+      <c r="N154" s="19">
+        <v>6335.51</v>
+      </c>
+      <c r="O154" s="19">
+        <v>5640.47</v>
+      </c>
+      <c r="P154" s="19">
+        <v>4224.73</v>
+      </c>
+      <c r="Q154" s="19">
+        <v>4290.84</v>
+      </c>
+      <c r="R154" s="19">
+        <v>4145.8</v>
+      </c>
+      <c r="S154" s="19">
+        <v>4471.46</v>
+      </c>
+      <c r="T154" s="19">
+        <v>3453.72</v>
+      </c>
+      <c r="U154" s="19">
+        <v>3075.46</v>
+      </c>
+      <c r="V154" s="19">
+        <v>2861.01</v>
+      </c>
+      <c r="W154" s="19">
+        <v>2963.25</v>
+      </c>
+    </row>
+    <row r="155" ht="15.0" customHeight="1">
+      <c r="A155" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="B155" s="15"/>
+      <c r="C155" s="15"/>
+      <c r="D155" s="15"/>
+      <c r="E155" s="15"/>
+      <c r="F155" s="15"/>
+      <c r="G155" s="15"/>
+      <c r="H155" s="15"/>
+      <c r="I155" s="15"/>
+      <c r="J155" s="15"/>
+      <c r="K155" s="15">
         <v>0.0</v>
       </c>
-      <c r="J153" s="15">
+      <c r="L155" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="M155" s="20">
+        <v>7.04</v>
+      </c>
+      <c r="N155" s="20">
+        <v>7.38</v>
+      </c>
+      <c r="O155" s="20">
+        <v>6.99</v>
+      </c>
+      <c r="P155" s="20">
+        <v>6.97</v>
+      </c>
+      <c r="Q155" s="20">
+        <v>7.32</v>
+      </c>
+      <c r="R155" s="20">
+        <v>23.41</v>
+      </c>
+      <c r="S155" s="20">
+        <v>48.93</v>
+      </c>
+      <c r="T155" s="20">
+        <v>38.73</v>
+      </c>
+      <c r="U155" s="20">
+        <v>20.86</v>
+      </c>
+      <c r="V155" s="20">
+        <v>67.57</v>
+      </c>
+      <c r="W155" s="20">
+        <v>84.67</v>
+      </c>
+    </row>
+    <row r="156" ht="15.0" customHeight="1">
+      <c r="A156" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="B156" s="18"/>
+      <c r="C156" s="18"/>
+      <c r="D156" s="18"/>
+      <c r="E156" s="18"/>
+      <c r="F156" s="18"/>
+      <c r="G156" s="18"/>
+      <c r="H156" s="18"/>
+      <c r="I156" s="18"/>
+      <c r="J156" s="18"/>
+      <c r="K156" s="18">
         <v>0.0</v>
       </c>
-      <c r="K153" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L153" s="16">
-        <v>124.8</v>
-      </c>
-      <c r="M153" s="16">
-        <v>116.18</v>
-      </c>
-      <c r="N153" s="20">
-        <v>93.69</v>
-      </c>
-      <c r="O153" s="16">
-        <v>188.12</v>
-      </c>
-      <c r="P153" s="20">
-        <v>49.43</v>
-      </c>
-      <c r="Q153" s="20">
-        <v>49.65</v>
-      </c>
-      <c r="R153" s="20">
-        <v>92.53</v>
-      </c>
-      <c r="S153" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="T153" s="16">
-        <v>276.63</v>
-      </c>
-      <c r="U153" s="16">
-        <v>259.35</v>
-      </c>
-      <c r="V153" s="16">
-        <v>314.83</v>
-      </c>
-      <c r="W153" s="16">
-        <v>217.23</v>
-      </c>
-    </row>
-    <row r="154" ht="15.0" customHeight="1">
-      <c r="A154" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="B154" s="16">
-        <v>1831.17</v>
-      </c>
-      <c r="C154" s="16">
-        <v>1823.88</v>
-      </c>
-      <c r="D154" s="16">
-        <v>1733.68</v>
-      </c>
-      <c r="E154" s="16">
-        <v>1610.38</v>
-      </c>
-      <c r="F154" s="16">
-        <v>1525.75</v>
-      </c>
-      <c r="G154" s="16">
-        <v>1596.57</v>
-      </c>
-      <c r="H154" s="16">
-        <v>1499.71</v>
-      </c>
-      <c r="I154" s="16">
-        <v>1509.93</v>
-      </c>
-      <c r="J154" s="15"/>
-      <c r="K154" s="15"/>
-      <c r="L154" s="15"/>
-      <c r="M154" s="15"/>
-      <c r="N154" s="15"/>
-      <c r="O154" s="15"/>
-      <c r="P154" s="15"/>
-      <c r="Q154" s="15"/>
-      <c r="R154" s="15"/>
-      <c r="S154" s="15"/>
-      <c r="T154" s="15"/>
-      <c r="U154" s="15"/>
-      <c r="V154" s="15"/>
-      <c r="W154" s="15"/>
-    </row>
-    <row r="155" ht="15.0" customHeight="1">
-      <c r="A155" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="B155" s="18">
+      <c r="L156" s="24">
+        <v>8.64</v>
+      </c>
+      <c r="M156" s="24">
+        <v>7.04</v>
+      </c>
+      <c r="N156" s="24">
+        <v>7.38</v>
+      </c>
+      <c r="O156" s="24">
+        <v>6.99</v>
+      </c>
+      <c r="P156" s="24">
+        <v>6.97</v>
+      </c>
+      <c r="Q156" s="24">
+        <v>7.32</v>
+      </c>
+      <c r="R156" s="24">
+        <v>23.41</v>
+      </c>
+      <c r="S156" s="24">
+        <v>48.93</v>
+      </c>
+      <c r="T156" s="24">
+        <v>38.73</v>
+      </c>
+      <c r="U156" s="24">
+        <v>20.86</v>
+      </c>
+      <c r="V156" s="24">
+        <v>67.57</v>
+      </c>
+      <c r="W156" s="24">
+        <v>84.67</v>
+      </c>
+    </row>
+    <row r="157" ht="15.0" customHeight="1">
+      <c r="A157" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="B157" s="15"/>
+      <c r="C157" s="15"/>
+      <c r="D157" s="15"/>
+      <c r="E157" s="20">
+        <v>1.05</v>
+      </c>
+      <c r="F157" s="15"/>
+      <c r="G157" s="15"/>
+      <c r="H157" s="15"/>
+      <c r="I157" s="15"/>
+      <c r="J157" s="15"/>
+      <c r="K157" s="15"/>
+      <c r="L157" s="15"/>
+      <c r="M157" s="15"/>
+      <c r="N157" s="15"/>
+      <c r="O157" s="15"/>
+      <c r="P157" s="15"/>
+      <c r="Q157" s="15"/>
+      <c r="R157" s="15"/>
+      <c r="S157" s="15"/>
+      <c r="T157" s="15"/>
+      <c r="U157" s="15"/>
+      <c r="V157" s="15"/>
+      <c r="W157" s="15"/>
+    </row>
+    <row r="158" ht="15.0" customHeight="1">
+      <c r="A158" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="B158" s="18">
         <v>25908.12</v>
       </c>
-      <c r="C155" s="18">
+      <c r="C158" s="18">
         <v>21804.16</v>
       </c>
-      <c r="D155" s="18">
+      <c r="D158" s="18">
         <v>17616.44</v>
       </c>
-      <c r="E155" s="18">
-        <v>11990.86</v>
-      </c>
-      <c r="F155" s="18">
+      <c r="E158" s="18">
+        <v>11991.91</v>
+      </c>
+      <c r="F158" s="18">
         <v>11612.32</v>
       </c>
-      <c r="G155" s="18">
+      <c r="G158" s="18">
         <v>11276.57</v>
       </c>
-      <c r="H155" s="19">
+      <c r="H158" s="19">
         <v>7909.87</v>
       </c>
-      <c r="I155" s="19">
+      <c r="I158" s="19">
         <v>8873.31</v>
       </c>
-      <c r="J155" s="19">
+      <c r="J158" s="19">
         <v>8036.58</v>
       </c>
-      <c r="K155" s="19">
+      <c r="K158" s="19">
         <v>8638.82</v>
       </c>
-      <c r="L155" s="19">
-        <v>7762.58</v>
-      </c>
-      <c r="M155" s="19">
-        <v>7246.92</v>
-      </c>
-      <c r="N155" s="19">
-        <v>6335.51</v>
-      </c>
-      <c r="O155" s="19">
-        <v>5640.47</v>
-      </c>
-      <c r="P155" s="19">
-        <v>4224.73</v>
-      </c>
-      <c r="Q155" s="19">
-        <v>4290.84</v>
-      </c>
-      <c r="R155" s="19">
-        <v>4145.8</v>
-      </c>
-      <c r="S155" s="19">
-        <v>4471.46</v>
-      </c>
-      <c r="T155" s="19">
-        <v>3453.72</v>
-      </c>
-      <c r="U155" s="19">
-        <v>3075.46</v>
-      </c>
-      <c r="V155" s="19">
-        <v>2861.01</v>
-      </c>
-      <c r="W155" s="19">
-        <v>2963.25</v>
-      </c>
-    </row>
-    <row r="156" ht="15.0" customHeight="1">
-      <c r="A156" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="B156" s="15"/>
-      <c r="C156" s="15"/>
-      <c r="D156" s="15"/>
-      <c r="E156" s="15"/>
-      <c r="F156" s="15"/>
-      <c r="G156" s="15"/>
-      <c r="H156" s="15"/>
-      <c r="I156" s="15"/>
-      <c r="J156" s="15"/>
-      <c r="K156" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L156" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="M156" s="20">
-        <v>7.04</v>
-      </c>
-      <c r="N156" s="20">
-        <v>7.38</v>
-      </c>
-      <c r="O156" s="20">
-        <v>6.99</v>
-      </c>
-      <c r="P156" s="20">
-        <v>6.97</v>
-      </c>
-      <c r="Q156" s="20">
-        <v>7.32</v>
-      </c>
-      <c r="R156" s="20">
-        <v>23.41</v>
-      </c>
-      <c r="S156" s="20">
-        <v>48.93</v>
-      </c>
-      <c r="T156" s="20">
-        <v>38.73</v>
-      </c>
-      <c r="U156" s="20">
-        <v>20.86</v>
-      </c>
-      <c r="V156" s="20">
-        <v>67.57</v>
-      </c>
-      <c r="W156" s="20">
-        <v>84.67</v>
-      </c>
-    </row>
-    <row r="157" ht="15.0" customHeight="1">
-      <c r="A157" s="17" t="s">
-        <v>342</v>
-      </c>
-      <c r="B157" s="18"/>
-      <c r="C157" s="18"/>
-      <c r="D157" s="18"/>
-      <c r="E157" s="18"/>
-      <c r="F157" s="18"/>
-      <c r="G157" s="18"/>
-      <c r="H157" s="18"/>
-      <c r="I157" s="18"/>
-      <c r="J157" s="18"/>
-      <c r="K157" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="L157" s="24">
-        <v>8.64</v>
-      </c>
-      <c r="M157" s="24">
-        <v>7.04</v>
-      </c>
-      <c r="N157" s="24">
-        <v>7.38</v>
-      </c>
-      <c r="O157" s="24">
-        <v>6.99</v>
-      </c>
-      <c r="P157" s="24">
-        <v>6.97</v>
-      </c>
-      <c r="Q157" s="24">
-        <v>7.32</v>
-      </c>
-      <c r="R157" s="24">
-        <v>23.41</v>
-      </c>
-      <c r="S157" s="24">
-        <v>48.93</v>
-      </c>
-      <c r="T157" s="24">
-        <v>38.73</v>
-      </c>
-      <c r="U157" s="24">
-        <v>20.86</v>
-      </c>
-      <c r="V157" s="24">
-        <v>67.57</v>
-      </c>
-      <c r="W157" s="24">
-        <v>84.67</v>
-      </c>
-    </row>
-    <row r="158" ht="15.0" customHeight="1">
-      <c r="A158" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="B158" s="15"/>
-      <c r="C158" s="15"/>
-      <c r="D158" s="15"/>
-      <c r="E158" s="20">
-        <v>1.05</v>
-      </c>
-      <c r="F158" s="15"/>
-      <c r="G158" s="15"/>
-      <c r="H158" s="15"/>
-      <c r="I158" s="15"/>
-      <c r="J158" s="15"/>
-      <c r="K158" s="15"/>
-      <c r="L158" s="15"/>
-      <c r="M158" s="15"/>
-      <c r="N158" s="15"/>
-      <c r="O158" s="15"/>
-      <c r="P158" s="15"/>
-      <c r="Q158" s="15"/>
-      <c r="R158" s="15"/>
-      <c r="S158" s="15"/>
-      <c r="T158" s="15"/>
-      <c r="U158" s="15"/>
-      <c r="V158" s="15"/>
-      <c r="W158" s="15"/>
+      <c r="L158" s="19">
+        <v>7771.22</v>
+      </c>
+      <c r="M158" s="19">
+        <v>7253.96</v>
+      </c>
+      <c r="N158" s="19">
+        <v>6342.88</v>
+      </c>
+      <c r="O158" s="19">
+        <v>5647.46</v>
+      </c>
+      <c r="P158" s="19">
+        <v>4231.7</v>
+      </c>
+      <c r="Q158" s="19">
+        <v>4298.15</v>
+      </c>
+      <c r="R158" s="19">
+        <v>4169.21</v>
+      </c>
+      <c r="S158" s="19">
+        <v>4520.39</v>
+      </c>
+      <c r="T158" s="19">
+        <v>3492.44</v>
+      </c>
+      <c r="U158" s="19">
+        <v>3096.31</v>
+      </c>
+      <c r="V158" s="19">
+        <v>2928.58</v>
+      </c>
+      <c r="W158" s="19">
+        <v>3047.92</v>
+      </c>
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="17" t="s">
-        <v>344</v>
-      </c>
-      <c r="B159" s="18">
-        <v>25908.12</v>
-      </c>
-      <c r="C159" s="18">
-        <v>21804.16</v>
-      </c>
-      <c r="D159" s="18">
-        <v>17616.44</v>
-      </c>
-      <c r="E159" s="18">
-        <v>11991.91</v>
-      </c>
-      <c r="F159" s="18">
-        <v>11612.32</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="B159" s="18"/>
+      <c r="C159" s="18"/>
+      <c r="D159" s="18"/>
+      <c r="E159" s="18"/>
+      <c r="F159" s="18"/>
       <c r="G159" s="18">
-        <v>11276.57</v>
-      </c>
-      <c r="H159" s="19">
-        <v>7909.87</v>
-      </c>
-      <c r="I159" s="19">
-        <v>8873.31</v>
-      </c>
-      <c r="J159" s="19">
-        <v>8036.58</v>
-      </c>
-      <c r="K159" s="19">
-        <v>8638.82</v>
-      </c>
-      <c r="L159" s="19">
-        <v>7771.22</v>
-      </c>
-      <c r="M159" s="19">
-        <v>7253.96</v>
-      </c>
-      <c r="N159" s="19">
-        <v>6342.88</v>
-      </c>
-      <c r="O159" s="19">
-        <v>5647.46</v>
-      </c>
-      <c r="P159" s="19">
-        <v>4231.7</v>
-      </c>
-      <c r="Q159" s="19">
-        <v>4298.15</v>
-      </c>
-      <c r="R159" s="19">
-        <v>4169.21</v>
-      </c>
-      <c r="S159" s="19">
-        <v>4520.39</v>
+        <v>22530.08</v>
+      </c>
+      <c r="H159" s="18">
+        <v>17608.76</v>
+      </c>
+      <c r="I159" s="18">
+        <v>18420.35</v>
+      </c>
+      <c r="J159" s="18">
+        <v>18751.04</v>
+      </c>
+      <c r="K159" s="18">
+        <v>15863.86</v>
+      </c>
+      <c r="L159" s="18">
+        <v>16162.6</v>
+      </c>
+      <c r="M159" s="18">
+        <v>14978.72</v>
+      </c>
+      <c r="N159" s="18">
+        <v>14528.4</v>
+      </c>
+      <c r="O159" s="18">
+        <v>12733.91</v>
+      </c>
+      <c r="P159" s="18">
+        <v>13985.54</v>
+      </c>
+      <c r="Q159" s="18">
+        <v>13122.83</v>
+      </c>
+      <c r="R159" s="18">
+        <v>11286.13</v>
+      </c>
+      <c r="S159" s="18">
+        <v>12962.18</v>
       </c>
       <c r="T159" s="19">
-        <v>3492.44</v>
+        <v>9681.17</v>
       </c>
       <c r="U159" s="19">
-        <v>3096.31</v>
+        <v>8111.49</v>
       </c>
       <c r="V159" s="19">
-        <v>2928.58</v>
+        <v>6614.46</v>
       </c>
       <c r="W159" s="19">
-        <v>3047.92</v>
+        <v>6504.91</v>
       </c>
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="B160" s="18"/>
-      <c r="C160" s="18"/>
-      <c r="D160" s="18"/>
-      <c r="E160" s="18"/>
-      <c r="F160" s="18"/>
-      <c r="G160" s="18">
-        <v>22530.08</v>
-      </c>
-      <c r="H160" s="18">
-        <v>17608.76</v>
-      </c>
-      <c r="I160" s="18">
-        <v>18420.35</v>
-      </c>
-      <c r="J160" s="18">
-        <v>18751.04</v>
-      </c>
-      <c r="K160" s="18">
-        <v>15863.86</v>
-      </c>
-      <c r="L160" s="18">
-        <v>16162.6</v>
-      </c>
-      <c r="M160" s="18">
-        <v>14978.72</v>
-      </c>
-      <c r="N160" s="18">
-        <v>14528.4</v>
-      </c>
-      <c r="O160" s="18">
-        <v>12733.91</v>
-      </c>
-      <c r="P160" s="18">
-        <v>13985.54</v>
-      </c>
-      <c r="Q160" s="18">
-        <v>13122.83</v>
-      </c>
-      <c r="R160" s="18">
-        <v>11286.13</v>
-      </c>
-      <c r="S160" s="18">
-        <v>12962.18</v>
-      </c>
-      <c r="T160" s="19">
-        <v>9681.17</v>
-      </c>
-      <c r="U160" s="19">
-        <v>8111.49</v>
-      </c>
-      <c r="V160" s="19">
-        <v>6614.46</v>
-      </c>
-      <c r="W160" s="19">
-        <v>6504.91</v>
-      </c>
+      <c r="B160" s="18">
+        <v>66099.37</v>
+      </c>
+      <c r="C160" s="18">
+        <v>57175.63</v>
+      </c>
+      <c r="D160" s="18">
+        <v>40310.88</v>
+      </c>
+      <c r="E160" s="18">
+        <v>29014.16</v>
+      </c>
+      <c r="F160" s="18">
+        <v>25563.32</v>
+      </c>
+      <c r="G160" s="18"/>
+      <c r="H160" s="18"/>
+      <c r="I160" s="18"/>
+      <c r="J160" s="18"/>
+      <c r="K160" s="18"/>
+      <c r="L160" s="18"/>
+      <c r="M160" s="18"/>
+      <c r="N160" s="18"/>
+      <c r="O160" s="18"/>
+      <c r="P160" s="18"/>
+      <c r="Q160" s="18"/>
+      <c r="R160" s="18"/>
+      <c r="S160" s="18"/>
+      <c r="T160" s="18"/>
+      <c r="U160" s="18"/>
+      <c r="V160" s="18"/>
+      <c r="W160" s="18"/>
     </row>
     <row r="161" ht="15.0" customHeight="1">
-      <c r="A161" s="17" t="s">
-        <v>345</v>
-      </c>
-      <c r="B161" s="18">
-        <v>66099.37</v>
-      </c>
-      <c r="C161" s="18">
-        <v>57175.63</v>
-      </c>
-      <c r="D161" s="18">
-        <v>40310.88</v>
-      </c>
-      <c r="E161" s="18">
-        <v>29014.16</v>
-      </c>
-      <c r="F161" s="18">
-        <v>25563.32</v>
-      </c>
-      <c r="G161" s="18"/>
-      <c r="H161" s="18"/>
-      <c r="I161" s="18"/>
-      <c r="J161" s="18"/>
-      <c r="K161" s="18"/>
-      <c r="L161" s="18"/>
-      <c r="M161" s="18"/>
-      <c r="N161" s="18"/>
-      <c r="O161" s="18"/>
-      <c r="P161" s="18"/>
-      <c r="Q161" s="18"/>
-      <c r="R161" s="18"/>
-      <c r="S161" s="18"/>
-      <c r="T161" s="18"/>
-      <c r="U161" s="18"/>
-      <c r="V161" s="18"/>
-      <c r="W161" s="18"/>
+      <c r="A161" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="B161" s="20">
+        <v>53.72</v>
+      </c>
+      <c r="C161" s="20">
+        <v>53.72</v>
+      </c>
+      <c r="D161" s="20">
+        <v>53.72</v>
+      </c>
+      <c r="E161" s="20">
+        <v>46.82</v>
+      </c>
+      <c r="F161" s="20">
+        <v>46.81</v>
+      </c>
+      <c r="G161" s="20">
+        <v>46.81</v>
+      </c>
+      <c r="H161" s="20">
+        <v>33.63</v>
+      </c>
+      <c r="I161" s="20">
+        <v>33.46</v>
+      </c>
+      <c r="J161" s="20">
+        <v>33.46</v>
+      </c>
+      <c r="K161" s="20">
+        <v>33.11</v>
+      </c>
+      <c r="L161" s="20">
+        <v>29.84</v>
+      </c>
+      <c r="M161" s="20">
+        <v>29.53</v>
+      </c>
+      <c r="N161" s="20">
+        <v>29.52</v>
+      </c>
+      <c r="O161" s="20">
+        <v>29.47</v>
+      </c>
+      <c r="P161" s="20">
+        <v>29.28</v>
+      </c>
+      <c r="Q161" s="20">
+        <v>29.28</v>
+      </c>
+      <c r="R161" s="20">
+        <v>29.26</v>
+      </c>
+      <c r="S161" s="20">
+        <v>29.26</v>
+      </c>
+      <c r="T161" s="20">
+        <v>29.16</v>
+      </c>
+      <c r="U161" s="20">
+        <v>28.99</v>
+      </c>
+      <c r="V161" s="20">
+        <v>30.22</v>
+      </c>
+      <c r="W161" s="20">
+        <v>30.22</v>
+      </c>
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B162" s="20">
-        <v>53.72</v>
+        <v>53.45</v>
       </c>
       <c r="C162" s="20">
-        <v>53.72</v>
+        <v>53.67</v>
       </c>
       <c r="D162" s="20">
-        <v>53.72</v>
+        <v>53.63</v>
       </c>
       <c r="E162" s="20">
-        <v>46.82</v>
+        <v>46.81</v>
       </c>
       <c r="F162" s="20">
         <v>46.81</v>
@@ -18398,37 +18442,37 @@
         <v>33.11</v>
       </c>
       <c r="L162" s="20">
-        <v>29.84</v>
+        <v>29.74</v>
       </c>
       <c r="M162" s="20">
-        <v>29.53</v>
+        <v>29.43</v>
       </c>
       <c r="N162" s="20">
-        <v>29.52</v>
+        <v>29.43</v>
       </c>
       <c r="O162" s="20">
-        <v>29.47</v>
+        <v>29.37</v>
       </c>
       <c r="P162" s="20">
-        <v>29.28</v>
+        <v>29.19</v>
       </c>
       <c r="Q162" s="20">
-        <v>29.28</v>
+        <v>29.18</v>
       </c>
       <c r="R162" s="20">
-        <v>29.26</v>
+        <v>29.16</v>
       </c>
       <c r="S162" s="20">
-        <v>29.26</v>
+        <v>29.16</v>
       </c>
       <c r="T162" s="20">
-        <v>29.16</v>
+        <v>29.06</v>
       </c>
       <c r="U162" s="20">
-        <v>28.99</v>
+        <v>28.9</v>
       </c>
       <c r="V162" s="20">
-        <v>30.22</v>
+        <v>28.86</v>
       </c>
       <c r="W162" s="20">
         <v>30.22</v>
@@ -18436,167 +18480,133 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B163" s="20">
-        <v>53.45</v>
+        <v>0.27</v>
       </c>
       <c r="C163" s="20">
-        <v>53.67</v>
+        <v>0.05</v>
       </c>
       <c r="D163" s="20">
-        <v>53.63</v>
+        <v>0.09</v>
       </c>
       <c r="E163" s="20">
-        <v>46.81</v>
-      </c>
-      <c r="F163" s="20">
-        <v>46.81</v>
-      </c>
-      <c r="G163" s="20">
-        <v>46.81</v>
-      </c>
-      <c r="H163" s="20">
-        <v>33.63</v>
-      </c>
-      <c r="I163" s="20">
-        <v>33.46</v>
-      </c>
-      <c r="J163" s="20">
-        <v>33.46</v>
-      </c>
-      <c r="K163" s="20">
-        <v>33.11</v>
+        <v>0.02</v>
+      </c>
+      <c r="F163" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="G163" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="H163" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="I163" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="J163" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="K163" s="15">
+        <v>0.0</v>
       </c>
       <c r="L163" s="20">
-        <v>29.74</v>
+        <v>0.09</v>
       </c>
       <c r="M163" s="20">
-        <v>29.43</v>
+        <v>0.09</v>
       </c>
       <c r="N163" s="20">
-        <v>29.43</v>
+        <v>0.09</v>
       </c>
       <c r="O163" s="20">
-        <v>29.37</v>
+        <v>0.09</v>
       </c>
       <c r="P163" s="20">
-        <v>29.19</v>
+        <v>0.1</v>
       </c>
       <c r="Q163" s="20">
-        <v>29.18</v>
+        <v>0.1</v>
       </c>
       <c r="R163" s="20">
-        <v>29.16</v>
+        <v>0.1</v>
       </c>
       <c r="S163" s="20">
-        <v>29.16</v>
+        <v>0.1</v>
       </c>
       <c r="T163" s="20">
-        <v>29.06</v>
+        <v>0.1</v>
       </c>
       <c r="U163" s="20">
-        <v>28.9</v>
+        <v>0.1</v>
       </c>
       <c r="V163" s="20">
-        <v>28.86</v>
-      </c>
-      <c r="W163" s="20">
-        <v>30.22</v>
+        <v>1.36</v>
+      </c>
+      <c r="W163" s="15">
+        <v>0.0</v>
       </c>
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="B164" s="20">
-        <v>0.27</v>
-      </c>
-      <c r="C164" s="20">
-        <v>0.05</v>
-      </c>
-      <c r="D164" s="20">
-        <v>0.09</v>
-      </c>
-      <c r="E164" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="F164" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="G164" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="H164" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="I164" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J164" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K164" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="L164" s="20">
-        <v>0.09</v>
-      </c>
-      <c r="M164" s="20">
-        <v>0.09</v>
-      </c>
-      <c r="N164" s="20">
-        <v>0.09</v>
-      </c>
-      <c r="O164" s="20">
-        <v>0.09</v>
-      </c>
-      <c r="P164" s="20">
-        <v>0.1</v>
-      </c>
-      <c r="Q164" s="20">
-        <v>0.1</v>
-      </c>
-      <c r="R164" s="20">
-        <v>0.1</v>
-      </c>
-      <c r="S164" s="20">
-        <v>0.1</v>
-      </c>
-      <c r="T164" s="20">
-        <v>0.1</v>
-      </c>
-      <c r="U164" s="20">
-        <v>0.1</v>
-      </c>
-      <c r="V164" s="20">
-        <v>1.36</v>
-      </c>
-      <c r="W164" s="15">
-        <v>0.0</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="B164" s="16">
+        <v>4725.6</v>
+      </c>
+      <c r="C164" s="16">
+        <v>2353.39</v>
+      </c>
+      <c r="D164" s="16">
+        <v>2237.01</v>
+      </c>
+      <c r="E164" s="16">
+        <v>2096.85</v>
+      </c>
+      <c r="F164" s="16">
+        <v>2002.3</v>
+      </c>
+      <c r="G164" s="16">
+        <v>3142.86</v>
+      </c>
+      <c r="H164" s="15"/>
+      <c r="I164" s="15"/>
+      <c r="J164" s="15"/>
+      <c r="K164" s="15"/>
+      <c r="L164" s="15"/>
+      <c r="M164" s="15"/>
+      <c r="N164" s="15"/>
+      <c r="O164" s="15"/>
+      <c r="P164" s="15"/>
+      <c r="Q164" s="15"/>
+      <c r="R164" s="15"/>
+      <c r="S164" s="15"/>
+      <c r="T164" s="15"/>
+      <c r="U164" s="15"/>
+      <c r="V164" s="15"/>
+      <c r="W164" s="15"/>
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="B165" s="16">
-        <v>4725.6</v>
-      </c>
-      <c r="C165" s="16">
-        <v>2353.39</v>
-      </c>
-      <c r="D165" s="16">
-        <v>2237.01</v>
-      </c>
-      <c r="E165" s="16">
-        <v>2096.85</v>
-      </c>
-      <c r="F165" s="16">
-        <v>2002.3</v>
-      </c>
-      <c r="G165" s="16">
-        <v>3142.86</v>
+        <v>350</v>
+      </c>
+      <c r="B165" s="15"/>
+      <c r="C165" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="D165" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="E165" s="20">
+        <v>94.36</v>
+      </c>
+      <c r="F165" s="20">
+        <v>54.06</v>
+      </c>
+      <c r="G165" s="20">
+        <v>34.57</v>
       </c>
       <c r="H165" s="15"/>
       <c r="I165" s="15"/>
@@ -18617,25 +18627,29 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="B166" s="15"/>
-      <c r="C166" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="D166" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="E166" s="20">
-        <v>94.36</v>
-      </c>
-      <c r="F166" s="20">
-        <v>54.06</v>
-      </c>
-      <c r="G166" s="20">
-        <v>34.57</v>
-      </c>
-      <c r="H166" s="15"/>
+        <v>351</v>
+      </c>
+      <c r="B166" s="16">
+        <v>1370.42</v>
+      </c>
+      <c r="C166" s="16">
+        <v>1047.26</v>
+      </c>
+      <c r="D166" s="16">
+        <v>693.47</v>
+      </c>
+      <c r="E166" s="16">
+        <v>378.48</v>
+      </c>
+      <c r="F166" s="16">
+        <v>486.56</v>
+      </c>
+      <c r="G166" s="16">
+        <v>474.57</v>
+      </c>
+      <c r="H166" s="16">
+        <v>366.07</v>
+      </c>
       <c r="I166" s="15"/>
       <c r="J166" s="15"/>
       <c r="K166" s="15"/>
@@ -18654,97 +18668,109 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="B167" s="16">
-        <v>1370.42</v>
-      </c>
-      <c r="C167" s="16">
-        <v>1047.26</v>
-      </c>
-      <c r="D167" s="16">
-        <v>693.47</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="B167" s="15"/>
+      <c r="C167" s="15"/>
+      <c r="D167" s="15"/>
       <c r="E167" s="16">
-        <v>378.48</v>
+        <v>1658.61</v>
       </c>
       <c r="F167" s="16">
-        <v>486.56</v>
+        <v>1638.88</v>
       </c>
       <c r="G167" s="16">
-        <v>474.57</v>
+        <v>1752.67</v>
       </c>
       <c r="H167" s="16">
-        <v>366.07</v>
-      </c>
-      <c r="I167" s="15"/>
-      <c r="J167" s="15"/>
-      <c r="K167" s="15"/>
+        <v>2940.37</v>
+      </c>
+      <c r="I167" s="16">
+        <v>2740.46</v>
+      </c>
+      <c r="J167" s="16">
+        <v>3347.34</v>
+      </c>
+      <c r="K167" s="16">
+        <v>848.99</v>
+      </c>
       <c r="L167" s="15"/>
-      <c r="M167" s="15"/>
-      <c r="N167" s="15"/>
-      <c r="O167" s="15"/>
-      <c r="P167" s="15"/>
-      <c r="Q167" s="15"/>
-      <c r="R167" s="15"/>
-      <c r="S167" s="15"/>
-      <c r="T167" s="15"/>
+      <c r="M167" s="16">
+        <v>1952.53</v>
+      </c>
+      <c r="N167" s="16">
+        <v>2907.94</v>
+      </c>
+      <c r="O167" s="16">
+        <v>2347.38</v>
+      </c>
+      <c r="P167" s="16">
+        <v>4973.8</v>
+      </c>
+      <c r="Q167" s="16">
+        <v>4629.58</v>
+      </c>
+      <c r="R167" s="16">
+        <v>3226.74</v>
+      </c>
+      <c r="S167" s="16">
+        <v>3562.22</v>
+      </c>
+      <c r="T167" s="16">
+        <v>2711.6</v>
+      </c>
       <c r="U167" s="15"/>
       <c r="V167" s="15"/>
       <c r="W167" s="15"/>
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B168" s="15"/>
       <c r="C168" s="15"/>
       <c r="D168" s="15"/>
-      <c r="E168" s="16">
-        <v>1658.61</v>
-      </c>
-      <c r="F168" s="16">
-        <v>1638.88</v>
-      </c>
+      <c r="E168" s="15"/>
+      <c r="F168" s="15"/>
       <c r="G168" s="16">
-        <v>1752.67</v>
+        <v>133.05</v>
       </c>
       <c r="H168" s="16">
-        <v>2940.37</v>
-      </c>
-      <c r="I168" s="16">
-        <v>2740.46</v>
-      </c>
-      <c r="J168" s="16">
-        <v>3347.34</v>
-      </c>
-      <c r="K168" s="16">
-        <v>848.99</v>
+        <v>156.47</v>
+      </c>
+      <c r="I168" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="J168" s="20">
+        <v>79.75</v>
+      </c>
+      <c r="K168" s="20">
+        <v>65.38</v>
       </c>
       <c r="L168" s="15"/>
       <c r="M168" s="16">
-        <v>1952.53</v>
+        <v>317.59</v>
       </c>
       <c r="N168" s="16">
-        <v>2907.94</v>
+        <v>123.2</v>
       </c>
       <c r="O168" s="16">
-        <v>2347.38</v>
+        <v>101.49</v>
       </c>
       <c r="P168" s="16">
-        <v>4973.8</v>
-      </c>
-      <c r="Q168" s="16">
-        <v>4629.58</v>
+        <v>1067.84</v>
+      </c>
+      <c r="Q168" s="20">
+        <v>27.38</v>
       </c>
       <c r="R168" s="16">
-        <v>3226.74</v>
+        <v>677.81</v>
       </c>
       <c r="S168" s="16">
-        <v>3562.22</v>
+        <v>587.38</v>
       </c>
       <c r="T168" s="16">
-        <v>2711.6</v>
+        <v>135.97</v>
       </c>
       <c r="U168" s="15"/>
       <c r="V168" s="15"/>
@@ -18752,7 +18778,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
@@ -18760,44 +18786,44 @@
       <c r="E169" s="15"/>
       <c r="F169" s="15"/>
       <c r="G169" s="16">
-        <v>133.05</v>
+        <v>147.71</v>
       </c>
       <c r="H169" s="16">
-        <v>156.47</v>
-      </c>
-      <c r="I169" s="15">
-        <v>0.0</v>
+        <v>211.57</v>
+      </c>
+      <c r="I169" s="16">
+        <v>1014.55</v>
       </c>
       <c r="J169" s="20">
-        <v>79.75</v>
+        <v>80.73</v>
       </c>
       <c r="K169" s="20">
-        <v>65.38</v>
+        <v>69.92</v>
       </c>
       <c r="L169" s="15"/>
-      <c r="M169" s="16">
-        <v>317.59</v>
-      </c>
-      <c r="N169" s="16">
-        <v>123.2</v>
-      </c>
-      <c r="O169" s="16">
-        <v>101.49</v>
+      <c r="M169" s="20">
+        <v>67.62</v>
+      </c>
+      <c r="N169" s="20">
+        <v>61.82</v>
+      </c>
+      <c r="O169" s="20">
+        <v>54.24</v>
       </c>
       <c r="P169" s="16">
-        <v>1067.84</v>
-      </c>
-      <c r="Q169" s="20">
-        <v>27.38</v>
+        <v>2201.76</v>
+      </c>
+      <c r="Q169" s="16">
+        <v>2188.17</v>
       </c>
       <c r="R169" s="16">
-        <v>677.81</v>
-      </c>
-      <c r="S169" s="16">
-        <v>587.38</v>
+        <v>962.87</v>
+      </c>
+      <c r="S169" s="20">
+        <v>1.04</v>
       </c>
       <c r="T169" s="16">
-        <v>135.97</v>
+        <v>271.52</v>
       </c>
       <c r="U169" s="15"/>
       <c r="V169" s="15"/>
@@ -18805,52 +18831,62 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="B170" s="15"/>
-      <c r="C170" s="15"/>
-      <c r="D170" s="15"/>
-      <c r="E170" s="15"/>
-      <c r="F170" s="15"/>
-      <c r="G170" s="16">
-        <v>147.71</v>
+        <v>355</v>
+      </c>
+      <c r="B170" s="16">
+        <v>118.14</v>
+      </c>
+      <c r="C170" s="20">
+        <v>23.53</v>
+      </c>
+      <c r="D170" s="20">
+        <v>22.37</v>
+      </c>
+      <c r="E170" s="20">
+        <v>98.55</v>
+      </c>
+      <c r="F170" s="20">
+        <v>98.11</v>
+      </c>
+      <c r="G170" s="20">
+        <v>59.71</v>
       </c>
       <c r="H170" s="16">
-        <v>211.57</v>
-      </c>
-      <c r="I170" s="16">
-        <v>1014.55</v>
+        <v>154.5</v>
+      </c>
+      <c r="I170" s="20">
+        <v>81.24</v>
       </c>
       <c r="J170" s="20">
-        <v>80.73</v>
+        <v>70.88</v>
       </c>
       <c r="K170" s="20">
-        <v>69.92</v>
+        <v>95.34</v>
       </c>
       <c r="L170" s="15"/>
-      <c r="M170" s="20">
-        <v>67.62</v>
-      </c>
-      <c r="N170" s="20">
-        <v>61.82</v>
-      </c>
-      <c r="O170" s="20">
-        <v>54.24</v>
+      <c r="M170" s="16">
+        <v>325.97</v>
+      </c>
+      <c r="N170" s="16">
+        <v>536.85</v>
+      </c>
+      <c r="O170" s="16">
+        <v>1794.74</v>
       </c>
       <c r="P170" s="16">
-        <v>2201.76</v>
+        <v>1271.6</v>
       </c>
       <c r="Q170" s="16">
-        <v>2188.17</v>
+        <v>1000.23</v>
       </c>
       <c r="R170" s="16">
-        <v>962.87</v>
-      </c>
-      <c r="S170" s="20">
-        <v>1.04</v>
+        <v>1031.99</v>
+      </c>
+      <c r="S170" s="16">
+        <v>1846.54</v>
       </c>
       <c r="T170" s="16">
-        <v>271.52</v>
+        <v>1282.6</v>
       </c>
       <c r="U170" s="15"/>
       <c r="V170" s="15"/>
@@ -18858,62 +18894,62 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B171" s="16">
-        <v>118.14</v>
-      </c>
-      <c r="C171" s="20">
-        <v>23.53</v>
-      </c>
-      <c r="D171" s="20">
-        <v>22.37</v>
-      </c>
-      <c r="E171" s="20">
-        <v>98.55</v>
-      </c>
-      <c r="F171" s="20">
-        <v>98.11</v>
+        <v>354.42</v>
+      </c>
+      <c r="C171" s="16">
+        <v>305.94</v>
+      </c>
+      <c r="D171" s="16">
+        <v>246.07</v>
+      </c>
+      <c r="E171" s="16">
+        <v>289.37</v>
+      </c>
+      <c r="F171" s="16">
+        <v>267.31</v>
       </c>
       <c r="G171" s="20">
-        <v>59.71</v>
+        <v>76.48</v>
       </c>
       <c r="H171" s="16">
-        <v>154.5</v>
-      </c>
-      <c r="I171" s="20">
-        <v>81.24</v>
-      </c>
-      <c r="J171" s="20">
-        <v>70.88</v>
+        <v>620.94</v>
+      </c>
+      <c r="I171" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="J171" s="16">
+        <v>1690.41</v>
       </c>
       <c r="K171" s="20">
-        <v>95.34</v>
+        <v>68.1</v>
       </c>
       <c r="L171" s="15"/>
-      <c r="M171" s="16">
-        <v>325.97</v>
+      <c r="M171" s="20">
+        <v>67.5</v>
       </c>
       <c r="N171" s="16">
-        <v>536.85</v>
-      </c>
-      <c r="O171" s="16">
-        <v>1794.74</v>
-      </c>
-      <c r="P171" s="16">
-        <v>1271.6</v>
+        <v>1027.52</v>
+      </c>
+      <c r="O171" s="20">
+        <v>36.42</v>
+      </c>
+      <c r="P171" s="20">
+        <v>36.11</v>
       </c>
       <c r="Q171" s="16">
-        <v>1000.23</v>
-      </c>
-      <c r="R171" s="16">
-        <v>1031.99</v>
-      </c>
-      <c r="S171" s="16">
-        <v>1846.54</v>
+        <v>943.06</v>
+      </c>
+      <c r="R171" s="20">
+        <v>23.75</v>
+      </c>
+      <c r="S171" s="20">
+        <v>1.04</v>
       </c>
       <c r="T171" s="16">
-        <v>1282.6</v>
+        <v>135.97</v>
       </c>
       <c r="U171" s="15"/>
       <c r="V171" s="15"/>
@@ -18921,62 +18957,62 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B172" s="16">
-        <v>354.42</v>
+        <v>413.49</v>
       </c>
       <c r="C172" s="16">
-        <v>305.94</v>
+        <v>447.14</v>
       </c>
       <c r="D172" s="16">
-        <v>246.07</v>
+        <v>346.74</v>
       </c>
       <c r="E172" s="16">
-        <v>289.37</v>
+        <v>189.77</v>
       </c>
       <c r="F172" s="16">
-        <v>267.31</v>
-      </c>
-      <c r="G172" s="20">
-        <v>76.48</v>
+        <v>287.33</v>
+      </c>
+      <c r="G172" s="16">
+        <v>155.05</v>
       </c>
       <c r="H172" s="16">
-        <v>620.94</v>
+        <v>188.94</v>
       </c>
       <c r="I172" s="15">
         <v>0.0</v>
       </c>
-      <c r="J172" s="16">
-        <v>1690.41</v>
+      <c r="J172" s="20">
+        <v>98.45</v>
       </c>
       <c r="K172" s="20">
-        <v>68.1</v>
+        <v>69.01</v>
       </c>
       <c r="L172" s="15"/>
-      <c r="M172" s="20">
-        <v>67.5</v>
-      </c>
-      <c r="N172" s="16">
-        <v>1027.52</v>
+      <c r="M172" s="16">
+        <v>508.32</v>
+      </c>
+      <c r="N172" s="20">
+        <v>62.49</v>
       </c>
       <c r="O172" s="20">
-        <v>36.42</v>
+        <v>27.07</v>
       </c>
       <c r="P172" s="20">
-        <v>36.11</v>
-      </c>
-      <c r="Q172" s="16">
-        <v>943.06</v>
+        <v>27.68</v>
+      </c>
+      <c r="Q172" s="20">
+        <v>36.27</v>
       </c>
       <c r="R172" s="20">
-        <v>23.75</v>
-      </c>
-      <c r="S172" s="20">
-        <v>1.04</v>
-      </c>
-      <c r="T172" s="16">
-        <v>135.97</v>
+        <v>34.89</v>
+      </c>
+      <c r="S172" s="16">
+        <v>1089.29</v>
+      </c>
+      <c r="T172" s="20">
+        <v>0.74</v>
       </c>
       <c r="U172" s="15"/>
       <c r="V172" s="15"/>
@@ -18984,62 +19020,62 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B173" s="16">
-        <v>413.49</v>
+        <v>1016.0</v>
       </c>
       <c r="C173" s="16">
-        <v>447.14</v>
+        <v>1164.93</v>
       </c>
       <c r="D173" s="16">
-        <v>346.74</v>
+        <v>1331.02</v>
       </c>
       <c r="E173" s="16">
-        <v>189.77</v>
+        <v>1080.93</v>
       </c>
       <c r="F173" s="16">
-        <v>287.33</v>
+        <v>986.13</v>
       </c>
       <c r="G173" s="16">
-        <v>155.05</v>
+        <v>1180.67</v>
       </c>
       <c r="H173" s="16">
-        <v>188.94</v>
-      </c>
-      <c r="I173" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J173" s="20">
-        <v>98.45</v>
-      </c>
-      <c r="K173" s="20">
-        <v>69.01</v>
+        <v>1607.95</v>
+      </c>
+      <c r="I173" s="16">
+        <v>1644.67</v>
+      </c>
+      <c r="J173" s="16">
+        <v>1327.12</v>
+      </c>
+      <c r="K173" s="16">
+        <v>481.25</v>
       </c>
       <c r="L173" s="15"/>
       <c r="M173" s="16">
-        <v>508.32</v>
-      </c>
-      <c r="N173" s="20">
-        <v>62.49</v>
-      </c>
-      <c r="O173" s="20">
-        <v>27.07</v>
-      </c>
-      <c r="P173" s="20">
-        <v>27.68</v>
-      </c>
-      <c r="Q173" s="20">
-        <v>36.27</v>
-      </c>
-      <c r="R173" s="20">
-        <v>34.89</v>
-      </c>
-      <c r="S173" s="16">
-        <v>1089.29</v>
-      </c>
-      <c r="T173" s="20">
-        <v>0.74</v>
+        <v>665.53</v>
+      </c>
+      <c r="N173" s="16">
+        <v>1096.05</v>
+      </c>
+      <c r="O173" s="16">
+        <v>333.41</v>
+      </c>
+      <c r="P173" s="16">
+        <v>368.82</v>
+      </c>
+      <c r="Q173" s="16">
+        <v>434.48</v>
+      </c>
+      <c r="R173" s="16">
+        <v>495.43</v>
+      </c>
+      <c r="S173" s="20">
+        <v>36.92</v>
+      </c>
+      <c r="T173" s="16">
+        <v>884.79</v>
       </c>
       <c r="U173" s="15"/>
       <c r="V173" s="15"/>
@@ -19047,82 +19083,48 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="B174" s="16">
-        <v>1016.0</v>
-      </c>
-      <c r="C174" s="16">
-        <v>1164.93</v>
-      </c>
-      <c r="D174" s="16">
-        <v>1331.02</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="B174" s="15"/>
+      <c r="C174" s="15"/>
+      <c r="D174" s="15"/>
       <c r="E174" s="16">
-        <v>1080.93</v>
+        <v>394.21</v>
       </c>
       <c r="F174" s="16">
-        <v>986.13</v>
+        <v>502.58</v>
       </c>
       <c r="G174" s="16">
-        <v>1180.67</v>
-      </c>
-      <c r="H174" s="16">
-        <v>1607.95</v>
-      </c>
-      <c r="I174" s="16">
-        <v>1644.67</v>
-      </c>
-      <c r="J174" s="16">
-        <v>1327.12</v>
-      </c>
-      <c r="K174" s="16">
-        <v>481.25</v>
-      </c>
+        <v>482.95</v>
+      </c>
+      <c r="H174" s="15"/>
+      <c r="I174" s="15"/>
+      <c r="J174" s="15"/>
+      <c r="K174" s="15"/>
       <c r="L174" s="15"/>
-      <c r="M174" s="16">
-        <v>665.53</v>
-      </c>
-      <c r="N174" s="16">
-        <v>1096.05</v>
-      </c>
-      <c r="O174" s="16">
-        <v>333.41</v>
-      </c>
-      <c r="P174" s="16">
-        <v>368.82</v>
-      </c>
-      <c r="Q174" s="16">
-        <v>434.48</v>
-      </c>
-      <c r="R174" s="16">
-        <v>495.43</v>
-      </c>
-      <c r="S174" s="20">
-        <v>36.92</v>
-      </c>
-      <c r="T174" s="16">
-        <v>884.79</v>
-      </c>
+      <c r="M174" s="15"/>
+      <c r="N174" s="15"/>
+      <c r="O174" s="15"/>
+      <c r="P174" s="15"/>
+      <c r="Q174" s="15"/>
+      <c r="R174" s="15"/>
+      <c r="S174" s="15"/>
+      <c r="T174" s="15"/>
       <c r="U174" s="15"/>
       <c r="V174" s="15"/>
       <c r="W174" s="15"/>
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
       <c r="D175" s="15"/>
-      <c r="E175" s="16">
-        <v>394.21</v>
-      </c>
-      <c r="F175" s="16">
-        <v>502.58</v>
-      </c>
-      <c r="G175" s="16">
-        <v>482.95</v>
+      <c r="E175" s="15"/>
+      <c r="F175" s="15"/>
+      <c r="G175" s="20">
+        <v>70.19</v>
       </c>
       <c r="H175" s="15"/>
       <c r="I175" s="15"/>
@@ -19143,7 +19145,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -19151,7 +19153,7 @@
       <c r="E176" s="15"/>
       <c r="F176" s="15"/>
       <c r="G176" s="20">
-        <v>70.19</v>
+        <v>40.86</v>
       </c>
       <c r="H176" s="15"/>
       <c r="I176" s="15"/>
@@ -19172,15 +19174,25 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="B177" s="15"/>
-      <c r="C177" s="15"/>
-      <c r="D177" s="15"/>
-      <c r="E177" s="15"/>
-      <c r="F177" s="15"/>
+        <v>362</v>
+      </c>
+      <c r="B177" s="16">
+        <v>248.09</v>
+      </c>
+      <c r="C177" s="16">
+        <v>176.5</v>
+      </c>
+      <c r="D177" s="16">
+        <v>100.67</v>
+      </c>
+      <c r="E177" s="20">
+        <v>57.66</v>
+      </c>
+      <c r="F177" s="20">
+        <v>77.09</v>
+      </c>
       <c r="G177" s="20">
-        <v>40.86</v>
+        <v>74.38</v>
       </c>
       <c r="H177" s="15"/>
       <c r="I177" s="15"/>
@@ -19201,25 +19213,25 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B178" s="16">
-        <v>248.09</v>
+        <v>401.68</v>
       </c>
       <c r="C178" s="16">
-        <v>176.5</v>
+        <v>247.11</v>
       </c>
       <c r="D178" s="16">
-        <v>100.67</v>
+        <v>167.78</v>
       </c>
       <c r="E178" s="20">
-        <v>57.66</v>
-      </c>
-      <c r="F178" s="20">
-        <v>77.09</v>
+        <v>83.87</v>
+      </c>
+      <c r="F178" s="16">
+        <v>123.14</v>
       </c>
       <c r="G178" s="20">
-        <v>74.38</v>
+        <v>66.0</v>
       </c>
       <c r="H178" s="15"/>
       <c r="I178" s="15"/>
@@ -19240,25 +19252,25 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B179" s="16">
-        <v>401.68</v>
+        <v>271.72</v>
       </c>
       <c r="C179" s="16">
-        <v>247.11</v>
+        <v>188.27</v>
       </c>
       <c r="D179" s="16">
-        <v>167.78</v>
+        <v>123.04</v>
       </c>
       <c r="E179" s="20">
-        <v>83.87</v>
-      </c>
-      <c r="F179" s="16">
-        <v>123.14</v>
+        <v>62.91</v>
+      </c>
+      <c r="F179" s="20">
+        <v>79.09</v>
       </c>
       <c r="G179" s="20">
-        <v>66.0</v>
+        <v>28.29</v>
       </c>
       <c r="H179" s="15"/>
       <c r="I179" s="15"/>
@@ -19279,25 +19291,25 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B180" s="16">
-        <v>271.72</v>
+        <v>1358.61</v>
       </c>
       <c r="C180" s="16">
-        <v>188.27</v>
+        <v>964.89</v>
       </c>
       <c r="D180" s="16">
-        <v>123.04</v>
-      </c>
-      <c r="E180" s="20">
-        <v>62.91</v>
-      </c>
-      <c r="F180" s="20">
-        <v>79.09</v>
-      </c>
-      <c r="G180" s="20">
-        <v>28.29</v>
+        <v>693.47</v>
+      </c>
+      <c r="E180" s="16">
+        <v>189.77</v>
+      </c>
+      <c r="F180" s="16">
+        <v>223.26</v>
+      </c>
+      <c r="G180" s="16">
+        <v>203.24</v>
       </c>
       <c r="H180" s="15"/>
       <c r="I180" s="15"/>
@@ -19318,354 +19330,316 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="B181" s="16">
-        <v>1358.61</v>
-      </c>
-      <c r="C181" s="16">
-        <v>964.89</v>
-      </c>
-      <c r="D181" s="16">
-        <v>693.47</v>
-      </c>
-      <c r="E181" s="16">
-        <v>189.77</v>
-      </c>
-      <c r="F181" s="16">
-        <v>223.26</v>
-      </c>
-      <c r="G181" s="16">
-        <v>203.24</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="B181" s="15"/>
+      <c r="C181" s="15"/>
+      <c r="D181" s="15"/>
+      <c r="E181" s="15"/>
+      <c r="F181" s="15"/>
+      <c r="G181" s="15"/>
       <c r="H181" s="15"/>
       <c r="I181" s="15"/>
-      <c r="J181" s="15"/>
-      <c r="K181" s="15"/>
-      <c r="L181" s="15"/>
-      <c r="M181" s="15"/>
-      <c r="N181" s="15"/>
-      <c r="O181" s="15"/>
-      <c r="P181" s="15"/>
-      <c r="Q181" s="15"/>
-      <c r="R181" s="15"/>
-      <c r="S181" s="15"/>
-      <c r="T181" s="15"/>
-      <c r="U181" s="15"/>
-      <c r="V181" s="15"/>
-      <c r="W181" s="15"/>
+      <c r="J181" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="K181" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="L181" s="20">
+        <v>0.09</v>
+      </c>
+      <c r="M181" s="20">
+        <v>0.09</v>
+      </c>
+      <c r="N181" s="20">
+        <v>0.09</v>
+      </c>
+      <c r="O181" s="20">
+        <v>0.09</v>
+      </c>
+      <c r="P181" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="Q181" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="R181" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="S181" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="T181" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="U181" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="V181" s="20">
+        <v>1.36</v>
+      </c>
+      <c r="W181" s="15">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="B182" s="15"/>
-      <c r="C182" s="15"/>
-      <c r="D182" s="15"/>
-      <c r="E182" s="15"/>
-      <c r="F182" s="15"/>
-      <c r="G182" s="15"/>
-      <c r="H182" s="15"/>
-      <c r="I182" s="15"/>
-      <c r="J182" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="K182" s="15">
-        <v>0.0</v>
+        <v>367</v>
+      </c>
+      <c r="B182" s="20">
+        <v>53.45</v>
+      </c>
+      <c r="C182" s="20">
+        <v>53.67</v>
+      </c>
+      <c r="D182" s="20">
+        <v>53.63</v>
+      </c>
+      <c r="E182" s="20">
+        <v>46.81</v>
+      </c>
+      <c r="F182" s="20">
+        <v>46.81</v>
+      </c>
+      <c r="G182" s="20">
+        <v>46.81</v>
+      </c>
+      <c r="H182" s="20">
+        <v>33.63</v>
+      </c>
+      <c r="I182" s="20">
+        <v>33.46</v>
+      </c>
+      <c r="J182" s="20">
+        <v>33.46</v>
+      </c>
+      <c r="K182" s="20">
+        <v>33.11</v>
       </c>
       <c r="L182" s="20">
-        <v>0.09</v>
+        <v>29.74</v>
       </c>
       <c r="M182" s="20">
-        <v>0.09</v>
+        <v>29.43</v>
       </c>
       <c r="N182" s="20">
-        <v>0.09</v>
+        <v>29.43</v>
       </c>
       <c r="O182" s="20">
-        <v>0.09</v>
+        <v>29.37</v>
       </c>
       <c r="P182" s="20">
-        <v>0.1</v>
+        <v>29.19</v>
       </c>
       <c r="Q182" s="20">
-        <v>0.1</v>
+        <v>29.19</v>
       </c>
       <c r="R182" s="20">
-        <v>0.1</v>
+        <v>29.16</v>
       </c>
       <c r="S182" s="20">
-        <v>0.1</v>
+        <v>29.16</v>
       </c>
       <c r="T182" s="20">
-        <v>0.1</v>
+        <v>29.06</v>
       </c>
       <c r="U182" s="20">
-        <v>0.1</v>
+        <v>28.9</v>
       </c>
       <c r="V182" s="20">
-        <v>1.36</v>
-      </c>
-      <c r="W182" s="15">
-        <v>0.0</v>
+        <v>28.86</v>
+      </c>
+      <c r="W182" s="20">
+        <v>30.22</v>
       </c>
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B183" s="20">
-        <v>53.45</v>
+        <v>0.27</v>
       </c>
       <c r="C183" s="20">
-        <v>53.67</v>
+        <v>0.05</v>
       </c>
       <c r="D183" s="20">
-        <v>53.63</v>
+        <v>0.09</v>
       </c>
       <c r="E183" s="20">
-        <v>46.81</v>
-      </c>
-      <c r="F183" s="20">
-        <v>46.81</v>
-      </c>
-      <c r="G183" s="20">
-        <v>46.81</v>
-      </c>
-      <c r="H183" s="20">
-        <v>33.63</v>
-      </c>
-      <c r="I183" s="20">
-        <v>33.46</v>
-      </c>
-      <c r="J183" s="20">
-        <v>33.46</v>
-      </c>
-      <c r="K183" s="20">
-        <v>33.11</v>
-      </c>
-      <c r="L183" s="20">
-        <v>29.74</v>
-      </c>
-      <c r="M183" s="20">
-        <v>29.43</v>
-      </c>
-      <c r="N183" s="20">
-        <v>29.43</v>
-      </c>
-      <c r="O183" s="20">
-        <v>29.37</v>
-      </c>
-      <c r="P183" s="20">
-        <v>29.19</v>
-      </c>
-      <c r="Q183" s="20">
-        <v>29.19</v>
-      </c>
-      <c r="R183" s="20">
-        <v>29.16</v>
-      </c>
-      <c r="S183" s="20">
-        <v>29.16</v>
-      </c>
-      <c r="T183" s="20">
-        <v>29.06</v>
-      </c>
-      <c r="U183" s="20">
-        <v>28.9</v>
-      </c>
-      <c r="V183" s="20">
-        <v>28.86</v>
-      </c>
-      <c r="W183" s="20">
-        <v>30.22</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="F183" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="G183" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="H183" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="I183" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="J183" s="15"/>
+      <c r="K183" s="15"/>
+      <c r="L183" s="15"/>
+      <c r="M183" s="15"/>
+      <c r="N183" s="15"/>
+      <c r="O183" s="15"/>
+      <c r="P183" s="15"/>
+      <c r="Q183" s="15"/>
+      <c r="R183" s="15"/>
+      <c r="S183" s="15"/>
+      <c r="T183" s="15"/>
+      <c r="U183" s="15"/>
+      <c r="V183" s="15"/>
+      <c r="W183" s="15"/>
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="14" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B184" s="20">
-        <v>0.27</v>
+        <v>53.72</v>
       </c>
       <c r="C184" s="20">
-        <v>0.05</v>
+        <v>53.72</v>
       </c>
       <c r="D184" s="20">
-        <v>0.09</v>
+        <v>53.72</v>
       </c>
       <c r="E184" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="F184" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="G184" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="H184" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="I184" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="J184" s="15"/>
-      <c r="K184" s="15"/>
-      <c r="L184" s="15"/>
-      <c r="M184" s="15"/>
-      <c r="N184" s="15"/>
-      <c r="O184" s="15"/>
-      <c r="P184" s="15"/>
-      <c r="Q184" s="15"/>
-      <c r="R184" s="15"/>
-      <c r="S184" s="15"/>
-      <c r="T184" s="15"/>
-      <c r="U184" s="15"/>
-      <c r="V184" s="15"/>
-      <c r="W184" s="15"/>
+        <v>46.82</v>
+      </c>
+      <c r="F184" s="20">
+        <v>46.81</v>
+      </c>
+      <c r="G184" s="20">
+        <v>46.81</v>
+      </c>
+      <c r="H184" s="20">
+        <v>33.63</v>
+      </c>
+      <c r="I184" s="20">
+        <v>33.46</v>
+      </c>
+      <c r="J184" s="20">
+        <v>33.46</v>
+      </c>
+      <c r="K184" s="20">
+        <v>33.11</v>
+      </c>
+      <c r="L184" s="20">
+        <v>29.84</v>
+      </c>
+      <c r="M184" s="20">
+        <v>29.53</v>
+      </c>
+      <c r="N184" s="20">
+        <v>29.52</v>
+      </c>
+      <c r="O184" s="20">
+        <v>29.47</v>
+      </c>
+      <c r="P184" s="20">
+        <v>29.28</v>
+      </c>
+      <c r="Q184" s="20">
+        <v>29.28</v>
+      </c>
+      <c r="R184" s="20">
+        <v>29.26</v>
+      </c>
+      <c r="S184" s="20">
+        <v>29.26</v>
+      </c>
+      <c r="T184" s="20">
+        <v>29.16</v>
+      </c>
+      <c r="U184" s="20">
+        <v>28.99</v>
+      </c>
+      <c r="V184" s="20">
+        <v>30.22</v>
+      </c>
+      <c r="W184" s="20">
+        <v>30.22</v>
+      </c>
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B185" s="20">
-        <v>53.72</v>
+        <v>1.0</v>
       </c>
       <c r="C185" s="20">
-        <v>53.72</v>
+        <v>1.0</v>
       </c>
       <c r="D185" s="20">
-        <v>53.72</v>
+        <v>1.0</v>
       </c>
       <c r="E185" s="20">
-        <v>46.82</v>
+        <v>1.0</v>
       </c>
       <c r="F185" s="20">
-        <v>46.81</v>
+        <v>1.0</v>
       </c>
       <c r="G185" s="20">
-        <v>46.81</v>
+        <v>1.0</v>
       </c>
       <c r="H185" s="20">
-        <v>33.63</v>
+        <v>1.0</v>
       </c>
       <c r="I185" s="20">
-        <v>33.46</v>
+        <v>1.0</v>
       </c>
       <c r="J185" s="20">
-        <v>33.46</v>
+        <v>1.0</v>
       </c>
       <c r="K185" s="20">
-        <v>33.11</v>
+        <v>1.0</v>
       </c>
       <c r="L185" s="20">
-        <v>29.84</v>
+        <v>1.0</v>
       </c>
       <c r="M185" s="20">
-        <v>29.53</v>
+        <v>1.0</v>
       </c>
       <c r="N185" s="20">
-        <v>29.52</v>
+        <v>1.0</v>
       </c>
       <c r="O185" s="20">
-        <v>29.47</v>
+        <v>1.0</v>
       </c>
       <c r="P185" s="20">
-        <v>29.28</v>
+        <v>1.0</v>
       </c>
       <c r="Q185" s="20">
-        <v>29.28</v>
+        <v>1.0</v>
       </c>
       <c r="R185" s="20">
-        <v>29.26</v>
+        <v>1.0</v>
       </c>
       <c r="S185" s="20">
-        <v>29.26</v>
+        <v>1.0</v>
       </c>
       <c r="T185" s="20">
-        <v>29.16</v>
+        <v>1.0</v>
       </c>
       <c r="U185" s="20">
-        <v>28.99</v>
+        <v>1.0</v>
       </c>
       <c r="V185" s="20">
-        <v>30.22</v>
+        <v>1.0</v>
       </c>
       <c r="W185" s="20">
-        <v>30.22</v>
-      </c>
-    </row>
-    <row r="186" ht="15.0" customHeight="1">
-      <c r="A186" s="14" t="s">
-        <v>369</v>
-      </c>
-      <c r="B186" s="20">
         <v>1.0</v>
       </c>
-      <c r="C186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="D186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="E186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="F186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="G186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="H186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="I186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="J186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="K186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="L186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="M186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="N186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="O186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="P186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="Q186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="R186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="S186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="T186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="U186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="V186" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="W186" s="20">
-        <v>1.0</v>
-      </c>
-    </row>
+    </row>
+    <row r="186" ht="15.75" customHeight="1"/>
     <row r="187" ht="15.75" customHeight="1"/>
     <row r="188" ht="15.75" customHeight="1"/>
     <row r="189" ht="15.75" customHeight="1"/>
@@ -20479,7 +20453,6 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.5" right="0.5" top="1.0"/>

--- a/data/cox_xlsx/NKT.CO.xlsx
+++ b/data/cox_xlsx/NKT.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="501">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -982,6 +982,9 @@
   </si>
   <si>
     <t>Lease liabilities</t>
+  </si>
+  <si>
+    <t>Interest-bearing loans and borrowings - Balancing value LT</t>
   </si>
   <si>
     <t>Derivate financial instruments</t>
@@ -1644,7 +1647,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1722,6 +1725,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -16809,8 +16815,8 @@
       <c r="W130" s="15"/>
     </row>
     <row r="131" ht="15.0" customHeight="1">
-      <c r="A131" s="14" t="s">
-        <v>299</v>
+      <c r="A131" s="26" t="s">
+        <v>321</v>
       </c>
       <c r="B131" s="16">
         <v>1476.75</v>
@@ -16993,7 +16999,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B134" s="16">
         <v>129.95</v>
@@ -17026,7 +17032,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B135" s="16">
         <v>425.3</v>
@@ -17130,7 +17136,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B137" s="15"/>
       <c r="C137" s="15"/>
@@ -17159,7 +17165,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B138" s="15"/>
       <c r="C138" s="15"/>
@@ -17192,7 +17198,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B139" s="15"/>
       <c r="C139" s="15"/>
@@ -17225,7 +17231,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="17" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B140" s="18">
         <v>16858.59</v>
@@ -17296,7 +17302,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B141" s="18">
         <v>40191.25</v>
@@ -17367,7 +17373,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B142" s="16">
         <v>1701.22</v>
@@ -17438,7 +17444,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B143" s="15">
         <v>21714.14</v>
@@ -17471,7 +17477,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B144" s="16">
         <v>661.58</v>
@@ -17534,7 +17540,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B145" s="22">
         <v>-236.28</v>
@@ -17567,7 +17573,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B146" s="22">
         <v>-354.42</v>
@@ -17626,7 +17632,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B147" s="16">
         <v>1252.28</v>
@@ -17685,7 +17691,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B148" s="15"/>
       <c r="C148" s="15"/>
@@ -17714,7 +17720,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
@@ -17767,7 +17773,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -17832,7 +17838,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
@@ -17863,7 +17869,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -17920,7 +17926,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B153" s="16">
         <v>1831.17</v>
@@ -17963,7 +17969,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B154" s="18">
         <v>25908.12</v>
@@ -18034,7 +18040,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
@@ -18087,7 +18093,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="17" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B156" s="18"/>
       <c r="C156" s="18"/>
@@ -18140,7 +18146,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -18169,7 +18175,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B158" s="18">
         <v>25908.12</v>
@@ -18240,7 +18246,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="17" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B159" s="18"/>
       <c r="C159" s="18"/>
@@ -18301,7 +18307,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="17" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B160" s="18">
         <v>66099.37</v>
@@ -18338,7 +18344,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B161" s="20">
         <v>53.72</v>
@@ -18409,7 +18415,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B162" s="20">
         <v>53.45</v>
@@ -18480,7 +18486,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B163" s="20">
         <v>0.27</v>
@@ -18551,7 +18557,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B164" s="16">
         <v>4725.6</v>
@@ -18590,7 +18596,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B165" s="15"/>
       <c r="C165" s="15">
@@ -18627,7 +18633,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B166" s="16">
         <v>1370.42</v>
@@ -18668,7 +18674,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B167" s="15"/>
       <c r="C167" s="15"/>
@@ -18725,7 +18731,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B168" s="15"/>
       <c r="C168" s="15"/>
@@ -18778,7 +18784,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
@@ -18831,7 +18837,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B170" s="16">
         <v>118.14</v>
@@ -18894,7 +18900,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B171" s="16">
         <v>354.42</v>
@@ -18957,7 +18963,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B172" s="16">
         <v>413.49</v>
@@ -19020,7 +19026,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B173" s="16">
         <v>1016.0</v>
@@ -19083,7 +19089,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -19116,7 +19122,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -19145,7 +19151,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -19174,7 +19180,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B177" s="16">
         <v>248.09</v>
@@ -19213,7 +19219,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B178" s="16">
         <v>401.68</v>
@@ -19252,7 +19258,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B179" s="16">
         <v>271.72</v>
@@ -19291,7 +19297,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B180" s="16">
         <v>1358.61</v>
@@ -19330,7 +19336,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B181" s="15"/>
       <c r="C181" s="15"/>
@@ -19385,7 +19391,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B182" s="20">
         <v>53.45</v>
@@ -19456,7 +19462,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B183" s="20">
         <v>0.27</v>
@@ -19499,7 +19505,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B184" s="20">
         <v>53.72</v>
@@ -19570,7 +19576,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B185" s="20">
         <v>1.0</v>
@@ -20474,7 +20480,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -20860,70 +20866,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -20977,7 +20983,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -21075,7 +21081,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -21106,7 +21112,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -21137,7 +21143,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B22" s="16">
         <v>4564.0</v>
@@ -21204,7 +21210,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -21237,7 +21243,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B24" s="21">
         <v>-23.41</v>
@@ -21278,7 +21284,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B25" s="16">
         <v>1872.41</v>
@@ -21388,7 +21394,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B27" s="16">
         <v>2305.41</v>
@@ -21427,7 +21433,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B28" s="16">
         <v>152.13</v>
@@ -21466,7 +21472,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B29" s="22">
         <v>-117.03</v>
@@ -21505,7 +21511,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -21560,7 +21566,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -21589,7 +21595,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B32" s="16">
         <v>304.27</v>
@@ -21658,7 +21664,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B33" s="21">
         <v>-81.92</v>
@@ -21725,7 +21731,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -21754,7 +21760,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -21783,7 +21789,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B36" s="22">
         <v>-795.77</v>
@@ -21854,7 +21860,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15">
@@ -21891,7 +21897,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B38" s="19">
         <v>5839.58</v>
@@ -21962,7 +21968,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B39" s="15">
         <v>0.0</v>
@@ -22031,7 +22037,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -22078,7 +22084,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B41" s="22">
         <v>-8133.29</v>
@@ -22149,7 +22155,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -22180,7 +22186,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -22247,7 +22253,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B44" s="22">
         <v>-561.72</v>
@@ -22318,7 +22324,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15">
@@ -22349,7 +22355,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -22378,7 +22384,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="17" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B47" s="23">
         <v>-8695.01</v>
@@ -22449,7 +22455,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B48" s="22">
         <v>-175.54</v>
@@ -22520,7 +22526,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -22579,7 +22585,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B50" s="22">
         <v>-140.43</v>
@@ -22620,7 +22626,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B51" s="22">
         <v>-128.73</v>
@@ -22661,7 +22667,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -22692,7 +22698,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -22741,7 +22747,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -22772,7 +22778,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -22827,7 +22833,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -22866,7 +22872,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -22895,7 +22901,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15">
@@ -22928,7 +22934,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
@@ -22979,7 +22985,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -23016,7 +23022,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B61" s="22">
         <v>-234.05</v>
@@ -23059,7 +23065,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -23088,7 +23094,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B63" s="23">
         <v>-678.75</v>
@@ -23159,7 +23165,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B64" s="15">
         <v>0.0</v>
@@ -23202,7 +23208,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B65" s="18">
         <v>0.0</v>
@@ -23245,7 +23251,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15">
@@ -23278,7 +23284,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B67" s="21">
         <v>-23.41</v>
@@ -23349,7 +23355,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B68" s="16">
         <v>3534.18</v>
@@ -23404,7 +23410,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B69" s="15">
         <v>17933.66</v>
@@ -23475,7 +23481,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B70" s="15">
         <v>14342.2</v>
@@ -23546,7 +23552,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B71" s="23">
         <v>-3557.58</v>
@@ -23617,7 +23623,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B72" s="22">
         <v>-2855.43</v>
@@ -24603,7 +24609,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -24782,37 +24788,37 @@
         <v>39</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG11" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AH11" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -25216,16 +25222,16 @@
         <v>45</v>
       </c>
       <c r="AD15" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AF15" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AH15" s="10" t="s">
         <v>45</v>
@@ -25293,7 +25299,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -25400,4052 +25406,4052 @@
         <v>70</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AF19" s="13" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG19" s="13" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AH19" s="13" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="26" t="s">
-        <v>449</v>
-      </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="27"/>
-      <c r="AA20" s="27"/>
-      <c r="AB20" s="27"/>
-      <c r="AC20" s="27"/>
-      <c r="AD20" s="27"/>
-      <c r="AE20" s="27"/>
-      <c r="AF20" s="27"/>
-      <c r="AG20" s="27"/>
-      <c r="AH20" s="27"/>
+      <c r="A20" s="27" t="s">
+        <v>450</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="28"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="28"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="28"/>
+      <c r="AC20" s="28"/>
+      <c r="AD20" s="28"/>
+      <c r="AE20" s="28"/>
+      <c r="AF20" s="28"/>
+      <c r="AG20" s="28"/>
+      <c r="AH20" s="28"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>449</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="29" t="s">
+        <v>450</v>
+      </c>
+      <c r="B21" s="30">
         <v>56479.25</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>28555.0</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>29770.04</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>23064.0</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>18396.88</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>16139.72</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="31">
         <v>8160.34</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
         <v>5662.6</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="30">
         <v>13073.13</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="31">
         <v>7466.47</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="31">
         <v>6217.78</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="31">
         <v>6058.46</v>
       </c>
-      <c r="N21" s="30">
+      <c r="N21" s="31">
         <v>5871.31</v>
       </c>
-      <c r="O21" s="30">
+      <c r="O21" s="31">
         <v>4253.44</v>
       </c>
-      <c r="P21" s="30">
+      <c r="P21" s="31">
         <v>6918.83</v>
       </c>
-      <c r="Q21" s="30">
+      <c r="Q21" s="31">
         <v>7860.37</v>
       </c>
-      <c r="R21" s="30">
+      <c r="R21" s="31">
         <v>6598.44</v>
       </c>
-      <c r="S21" s="30">
+      <c r="S21" s="31">
         <v>4400.68</v>
       </c>
-      <c r="T21" s="30">
+      <c r="T21" s="31">
         <v>7642.39</v>
       </c>
-      <c r="U21" s="30">
+      <c r="U21" s="31">
         <v>7317.87</v>
       </c>
-      <c r="V21" s="30">
+      <c r="V21" s="31">
         <v>4627.18</v>
       </c>
-      <c r="W21" s="30">
+      <c r="W21" s="31">
         <v>2448.91</v>
       </c>
-      <c r="X21" s="30">
+      <c r="X21" s="31">
         <v>1077.17</v>
       </c>
-      <c r="Y21" s="30">
+      <c r="Y21" s="31">
         <v>557.81</v>
       </c>
-      <c r="Z21" s="30">
+      <c r="Z21" s="31">
         <v>1477.26</v>
       </c>
-      <c r="AA21" s="30">
+      <c r="AA21" s="31">
         <v>2443.8</v>
       </c>
-      <c r="AB21" s="30">
+      <c r="AB21" s="31">
         <v>682.03</v>
       </c>
-      <c r="AC21" s="30">
+      <c r="AC21" s="31">
         <v>4290.3</v>
       </c>
-      <c r="AD21" s="30">
+      <c r="AD21" s="31">
         <v>3829.48</v>
       </c>
-      <c r="AE21" s="30">
+      <c r="AE21" s="31">
         <v>1918.2</v>
       </c>
-      <c r="AF21" s="30">
+      <c r="AF21" s="31">
         <v>1954.31</v>
       </c>
-      <c r="AG21" s="30">
+      <c r="AG21" s="31">
         <v>1734.47</v>
       </c>
-      <c r="AH21" s="30">
+      <c r="AH21" s="31">
         <v>1666.84</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>450</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="A22" s="29" t="s">
+        <v>451</v>
+      </c>
+      <c r="B22" s="30">
         <v>32858.19</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>25102.11</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>20287.21</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>14633.62</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>12227.73</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="30">
         <v>10668.04</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="31">
         <v>8263.42</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="31">
         <v>8004.71</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="31">
         <v>8215.31</v>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="31">
         <v>6217.87</v>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="31">
         <v>6712.13</v>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="31">
         <v>6973.54</v>
       </c>
-      <c r="N22" s="30">
+      <c r="N22" s="31">
         <v>6641.87</v>
       </c>
-      <c r="O22" s="30">
+      <c r="O22" s="31">
         <v>5478.42</v>
       </c>
-      <c r="P22" s="30">
+      <c r="P22" s="31">
         <v>6369.43</v>
       </c>
-      <c r="Q22" s="30">
+      <c r="Q22" s="31">
         <v>6404.45</v>
       </c>
-      <c r="R22" s="30">
+      <c r="R22" s="31">
         <v>6107.65</v>
       </c>
-      <c r="S22" s="30">
+      <c r="S22" s="31">
         <v>6181.63</v>
       </c>
-      <c r="T22" s="30">
+      <c r="T22" s="31">
         <v>4533.23</v>
       </c>
-      <c r="U22" s="30">
+      <c r="U22" s="31">
         <v>3243.14</v>
       </c>
-      <c r="V22" s="30">
+      <c r="V22" s="31">
         <v>2023.71</v>
       </c>
-      <c r="W22" s="30">
+      <c r="W22" s="31">
         <v>1620.5</v>
       </c>
-      <c r="X22" s="30">
+      <c r="X22" s="31">
         <v>1294.02</v>
       </c>
-      <c r="Y22" s="30">
+      <c r="Y22" s="31">
         <v>1632.18</v>
       </c>
-      <c r="Z22" s="30">
+      <c r="Z22" s="31">
         <v>2418.73</v>
       </c>
-      <c r="AA22" s="30">
+      <c r="AA22" s="31">
         <v>2594.8</v>
       </c>
-      <c r="AB22" s="30">
+      <c r="AB22" s="31">
         <v>2446.98</v>
       </c>
-      <c r="AC22" s="30">
+      <c r="AC22" s="31">
         <v>2934.26</v>
       </c>
-      <c r="AD22" s="30">
+      <c r="AD22" s="31">
         <v>2202.73</v>
       </c>
-      <c r="AE22" s="29"/>
-      <c r="AF22" s="29"/>
-      <c r="AG22" s="29"/>
-      <c r="AH22" s="29"/>
+      <c r="AE22" s="30"/>
+      <c r="AF22" s="30"/>
+      <c r="AG22" s="30"/>
+      <c r="AH22" s="30"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="26" t="s">
-        <v>451</v>
-      </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="27"/>
-      <c r="AC23" s="27"/>
-      <c r="AD23" s="27"/>
-      <c r="AE23" s="27"/>
-      <c r="AF23" s="27"/>
-      <c r="AG23" s="27"/>
-      <c r="AH23" s="27"/>
+      <c r="A23" s="27" t="s">
+        <v>452</v>
+      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="28"/>
+      <c r="W23" s="28"/>
+      <c r="X23" s="28"/>
+      <c r="Y23" s="28"/>
+      <c r="Z23" s="28"/>
+      <c r="AA23" s="28"/>
+      <c r="AB23" s="28"/>
+      <c r="AC23" s="28"/>
+      <c r="AD23" s="28"/>
+      <c r="AE23" s="28"/>
+      <c r="AF23" s="28"/>
+      <c r="AG23" s="28"/>
+      <c r="AH23" s="28"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>451</v>
-      </c>
-      <c r="B24" s="29">
+      <c r="A24" s="29" t="s">
+        <v>452</v>
+      </c>
+      <c r="B24" s="30">
         <v>67856.14</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>43616.7</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>37387.05</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <v>23721.36</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>18262.73</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <v>16410.0</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="31">
         <v>5775.97</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <v>3201.54</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="30">
         <v>10165.86</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="31">
         <v>7777.92</v>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="31">
         <v>5276.02</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="31">
         <v>4576.73</v>
       </c>
-      <c r="N24" s="30">
+      <c r="N24" s="31">
         <v>3401.5</v>
       </c>
-      <c r="O24" s="30">
+      <c r="O24" s="31">
         <v>2273.73</v>
       </c>
-      <c r="P24" s="30">
+      <c r="P24" s="31">
         <v>2239.53</v>
       </c>
-      <c r="Q24" s="30">
+      <c r="Q24" s="31">
         <v>3503.47</v>
       </c>
-      <c r="R24" s="30">
+      <c r="R24" s="31">
         <v>3655.98</v>
       </c>
-      <c r="S24" s="30">
+      <c r="S24" s="31">
         <v>1554.87</v>
       </c>
-      <c r="T24" s="30">
+      <c r="T24" s="31">
         <v>5484.79</v>
       </c>
-      <c r="U24" s="30">
+      <c r="U24" s="31">
         <v>6155.21</v>
       </c>
-      <c r="V24" s="30">
+      <c r="V24" s="31">
         <v>3602.59</v>
       </c>
-      <c r="W24" s="30">
+      <c r="W24" s="31">
         <v>2057.79</v>
       </c>
-      <c r="X24" s="30">
+      <c r="X24" s="31">
         <v>1435.33</v>
       </c>
-      <c r="Y24" s="30">
+      <c r="Y24" s="31">
         <v>861.4</v>
       </c>
-      <c r="Z24" s="30">
+      <c r="Z24" s="31">
         <v>1368.88</v>
       </c>
-      <c r="AA24" s="30">
+      <c r="AA24" s="31">
         <v>5261.19</v>
       </c>
-      <c r="AB24" s="30">
+      <c r="AB24" s="31">
         <v>1597.76</v>
       </c>
-      <c r="AC24" s="30">
+      <c r="AC24" s="31">
         <v>1704.37</v>
       </c>
-      <c r="AD24" s="30">
+      <c r="AD24" s="31">
         <v>2089.76</v>
       </c>
-      <c r="AE24" s="30">
+      <c r="AE24" s="31">
         <v>1361.42</v>
       </c>
-      <c r="AF24" s="30">
+      <c r="AF24" s="31">
         <v>1054.84</v>
       </c>
-      <c r="AG24" s="30">
+      <c r="AG24" s="31">
         <v>1297.74</v>
       </c>
-      <c r="AH24" s="30">
+      <c r="AH24" s="31">
         <v>1059.41</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="29" t="s">
+        <v>453</v>
+      </c>
+      <c r="B25" s="30">
         <v>39883.5</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>29893.85</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>21436.58</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <v>13762.16</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <v>10678.76</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="31">
         <v>9147.1</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="31">
         <v>6590.91</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="31">
         <v>6476.1</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="31">
         <v>6602.21</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="31">
         <v>4776.57</v>
       </c>
-      <c r="L25" s="30">
+      <c r="L25" s="31">
         <v>3961.2</v>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="31">
         <v>3549.39</v>
       </c>
-      <c r="N25" s="30">
+      <c r="N25" s="31">
         <v>3164.92</v>
       </c>
-      <c r="O25" s="30">
+      <c r="O25" s="31">
         <v>2422.26</v>
       </c>
-      <c r="P25" s="30">
+      <c r="P25" s="31">
         <v>3144.3</v>
       </c>
-      <c r="Q25" s="30">
+      <c r="Q25" s="31">
         <v>3879.87</v>
       </c>
-      <c r="R25" s="30">
+      <c r="R25" s="31">
         <v>4134.17</v>
       </c>
-      <c r="S25" s="30">
+      <c r="S25" s="31">
         <v>4468.28</v>
       </c>
-      <c r="T25" s="30">
+      <c r="T25" s="31">
         <v>3666.44</v>
       </c>
-      <c r="U25" s="30">
+      <c r="U25" s="31">
         <v>2860.28</v>
       </c>
-      <c r="V25" s="30">
+      <c r="V25" s="31">
         <v>1856.05</v>
       </c>
-      <c r="W25" s="30">
+      <c r="W25" s="31">
         <v>2220.81</v>
       </c>
-      <c r="X25" s="30">
+      <c r="X25" s="31">
         <v>2175.89</v>
       </c>
-      <c r="Y25" s="30">
+      <c r="Y25" s="31">
         <v>1913.57</v>
       </c>
-      <c r="Z25" s="30">
+      <c r="Z25" s="31">
         <v>2318.28</v>
       </c>
-      <c r="AA25" s="30">
+      <c r="AA25" s="31">
         <v>2399.14</v>
       </c>
-      <c r="AB25" s="30">
+      <c r="AB25" s="31">
         <v>1526.09</v>
       </c>
-      <c r="AC25" s="30">
+      <c r="AC25" s="31">
         <v>1616.76</v>
       </c>
-      <c r="AD25" s="30">
+      <c r="AD25" s="31">
         <v>1360.43</v>
       </c>
-      <c r="AE25" s="29"/>
-      <c r="AF25" s="29"/>
-      <c r="AG25" s="29"/>
-      <c r="AH25" s="29"/>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="30"/>
+      <c r="AG25" s="30"/>
+      <c r="AH25" s="30"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="26" t="s">
-        <v>453</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-      <c r="W26" s="27"/>
-      <c r="X26" s="27"/>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="27"/>
-      <c r="AA26" s="27"/>
-      <c r="AB26" s="27"/>
-      <c r="AC26" s="27"/>
-      <c r="AD26" s="27"/>
-      <c r="AE26" s="27"/>
-      <c r="AF26" s="27"/>
-      <c r="AG26" s="27"/>
-      <c r="AH26" s="27"/>
+      <c r="A26" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="28"/>
+      <c r="X26" s="28"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
+      <c r="AC26" s="28"/>
+      <c r="AD26" s="28"/>
+      <c r="AE26" s="28"/>
+      <c r="AF26" s="28"/>
+      <c r="AG26" s="28"/>
+      <c r="AH26" s="28"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>454</v>
-      </c>
-      <c r="B27" s="30">
+      <c r="A27" s="29" t="s">
+        <v>455</v>
+      </c>
+      <c r="B27" s="31">
         <v>1263.14</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>811.93</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>695.96</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>506.8</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>390.18</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="31">
         <v>350.59</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="31">
         <v>171.75</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="32">
         <v>95.67</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="31">
         <v>303.78</v>
       </c>
-      <c r="K27" s="30">
+      <c r="K27" s="31">
         <v>234.94</v>
       </c>
-      <c r="L27" s="30">
+      <c r="L27" s="31">
         <v>176.82</v>
       </c>
-      <c r="M27" s="30">
+      <c r="M27" s="31">
         <v>155.0</v>
       </c>
-      <c r="N27" s="30">
+      <c r="N27" s="31">
         <v>115.22</v>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="32">
         <v>77.15</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="32">
         <v>76.47</v>
       </c>
-      <c r="Q27" s="30">
+      <c r="Q27" s="31">
         <v>119.63</v>
       </c>
-      <c r="R27" s="30">
+      <c r="R27" s="31">
         <v>124.95</v>
       </c>
-      <c r="S27" s="31">
+      <c r="S27" s="32">
         <v>53.14</v>
       </c>
-      <c r="T27" s="30">
+      <c r="T27" s="31">
         <v>188.09</v>
       </c>
-      <c r="U27" s="30">
+      <c r="U27" s="31">
         <v>212.31</v>
       </c>
-      <c r="V27" s="30">
+      <c r="V27" s="31">
         <v>119.19</v>
       </c>
-      <c r="W27" s="31">
+      <c r="W27" s="32">
         <v>68.08</v>
       </c>
-      <c r="X27" s="31">
+      <c r="X27" s="32">
         <v>46.54</v>
       </c>
-      <c r="Y27" s="31">
+      <c r="Y27" s="32">
         <v>27.93</v>
       </c>
-      <c r="Z27" s="31">
+      <c r="Z27" s="32">
         <v>44.38</v>
       </c>
-      <c r="AA27" s="30">
+      <c r="AA27" s="31">
         <v>158.07</v>
       </c>
-      <c r="AB27" s="31">
+      <c r="AB27" s="32">
         <v>34.5</v>
       </c>
-      <c r="AC27" s="31">
+      <c r="AC27" s="32">
         <v>36.8</v>
       </c>
-      <c r="AD27" s="31">
+      <c r="AD27" s="32">
         <v>45.23</v>
       </c>
-      <c r="AE27" s="31">
+      <c r="AE27" s="32">
         <v>29.47</v>
       </c>
-      <c r="AF27" s="31">
+      <c r="AF27" s="32">
         <v>22.83</v>
       </c>
-      <c r="AG27" s="31">
+      <c r="AG27" s="32">
         <v>28.09</v>
       </c>
-      <c r="AH27" s="31">
+      <c r="AH27" s="32">
         <v>22.93</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="28" t="s">
-        <v>455</v>
-      </c>
-      <c r="B28" s="30">
+      <c r="A28" s="29" t="s">
+        <v>456</v>
+      </c>
+      <c r="B28" s="31">
         <v>768.98</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="31">
         <v>593.06</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="31">
         <v>448.42</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="31">
         <v>310.1</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="31">
         <v>261.11</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="31">
         <v>245.78</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="31">
         <v>201.26</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="31">
         <v>202.02</v>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="31">
         <v>208.95</v>
       </c>
-      <c r="K28" s="30">
+      <c r="K28" s="31">
         <v>155.76</v>
       </c>
-      <c r="L28" s="30">
+      <c r="L28" s="31">
         <v>133.98</v>
       </c>
-      <c r="M28" s="30">
+      <c r="M28" s="31">
         <v>120.62</v>
       </c>
-      <c r="N28" s="30">
+      <c r="N28" s="31">
         <v>107.8</v>
       </c>
-      <c r="O28" s="31">
+      <c r="O28" s="32">
         <v>82.64</v>
       </c>
-      <c r="P28" s="30">
+      <c r="P28" s="31">
         <v>107.55</v>
       </c>
-      <c r="Q28" s="30">
+      <c r="Q28" s="31">
         <v>133.07</v>
       </c>
-      <c r="R28" s="30">
+      <c r="R28" s="31">
         <v>141.0</v>
       </c>
-      <c r="S28" s="30">
+      <c r="S28" s="31">
         <v>151.84</v>
       </c>
-      <c r="T28" s="30">
+      <c r="T28" s="31">
         <v>124.12</v>
       </c>
-      <c r="U28" s="31">
+      <c r="U28" s="32">
         <v>96.05</v>
       </c>
-      <c r="V28" s="31">
+      <c r="V28" s="32">
         <v>60.92</v>
       </c>
-      <c r="W28" s="31">
+      <c r="W28" s="32">
         <v>69.78</v>
       </c>
-      <c r="X28" s="31">
+      <c r="X28" s="32">
         <v>64.41</v>
       </c>
-      <c r="Y28" s="31">
+      <c r="Y28" s="32">
         <v>53.72</v>
       </c>
-      <c r="Z28" s="31">
+      <c r="Z28" s="32">
         <v>61.62</v>
       </c>
-      <c r="AA28" s="31">
+      <c r="AA28" s="32">
         <v>60.73</v>
       </c>
-      <c r="AB28" s="31">
+      <c r="AB28" s="32">
         <v>33.0</v>
       </c>
-      <c r="AC28" s="31">
+      <c r="AC28" s="32">
         <v>34.98</v>
       </c>
-      <c r="AD28" s="31">
+      <c r="AD28" s="32">
         <v>29.45</v>
       </c>
-      <c r="AE28" s="29"/>
-      <c r="AF28" s="29"/>
-      <c r="AG28" s="29"/>
-      <c r="AH28" s="29"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="30"/>
+      <c r="AG28" s="30"/>
+      <c r="AH28" s="30"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="26" t="s">
-        <v>456</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="27"/>
-      <c r="W29" s="27"/>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="27"/>
-      <c r="Z29" s="27"/>
-      <c r="AA29" s="27"/>
-      <c r="AB29" s="27"/>
-      <c r="AC29" s="27"/>
-      <c r="AD29" s="27"/>
-      <c r="AE29" s="27"/>
-      <c r="AF29" s="27"/>
-      <c r="AG29" s="27"/>
-      <c r="AH29" s="27"/>
+      <c r="A29" s="27" t="s">
+        <v>457</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="28"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+      <c r="AC29" s="28"/>
+      <c r="AD29" s="28"/>
+      <c r="AE29" s="28"/>
+      <c r="AF29" s="28"/>
+      <c r="AG29" s="28"/>
+      <c r="AH29" s="28"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>457</v>
-      </c>
-      <c r="B30" s="32">
+      <c r="A30" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="B30" s="33">
         <v>-4.45</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <v>14.36</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>9.45</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <v>4.39</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="33">
         <v>-0.7</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <v>1.81</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="34">
         <v>7.99</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="33">
         <v>-34.04</v>
       </c>
-      <c r="J30" s="32">
+      <c r="J30" s="33">
         <v>-0.64</v>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="34">
         <v>9.67</v>
       </c>
-      <c r="L30" s="33">
+      <c r="L30" s="34">
         <v>19.08</v>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="34">
         <v>29.76</v>
       </c>
-      <c r="N30" s="33">
+      <c r="N30" s="34">
         <v>2.11</v>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="34">
         <v>24.04</v>
       </c>
-      <c r="P30" s="32">
+      <c r="P30" s="33">
         <v>-1.36</v>
       </c>
-      <c r="Q30" s="32">
+      <c r="Q30" s="33">
         <v>-35.66</v>
       </c>
-      <c r="R30" s="32">
+      <c r="R30" s="33">
         <v>-13.89</v>
       </c>
-      <c r="S30" s="33">
+      <c r="S30" s="34">
         <v>0.61</v>
       </c>
-      <c r="T30" s="33">
+      <c r="T30" s="34">
         <v>12.19</v>
       </c>
-      <c r="U30" s="32">
+      <c r="U30" s="33">
         <v>-0.44</v>
       </c>
-      <c r="V30" s="32">
+      <c r="V30" s="33">
         <v>-7.48</v>
       </c>
-      <c r="W30" s="33">
+      <c r="W30" s="34">
         <v>3.86</v>
       </c>
-      <c r="X30" s="33">
+      <c r="X30" s="34">
         <v>5.81</v>
       </c>
-      <c r="Y30" s="33">
+      <c r="Y30" s="34">
         <v>22.2</v>
       </c>
-      <c r="Z30" s="33">
+      <c r="Z30" s="34">
         <v>13.15</v>
       </c>
-      <c r="AA30" s="32">
+      <c r="AA30" s="33">
         <v>-9.54</v>
       </c>
-      <c r="AB30" s="32">
+      <c r="AB30" s="33">
         <v>-30.12</v>
       </c>
-      <c r="AC30" s="32">
+      <c r="AC30" s="33">
         <v>-35.59</v>
       </c>
-      <c r="AD30" s="32">
+      <c r="AD30" s="33">
         <v>-8.05</v>
       </c>
-      <c r="AE30" s="33">
+      <c r="AE30" s="34">
         <v>20.44</v>
       </c>
-      <c r="AF30" s="32">
+      <c r="AF30" s="33">
         <v>-29.18</v>
       </c>
-      <c r="AG30" s="33">
+      <c r="AG30" s="34">
         <v>12.33</v>
       </c>
-      <c r="AH30" s="33">
+      <c r="AH30" s="34">
         <v>28.92</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="B31" s="33">
+      <c r="A31" s="29" t="s">
+        <v>459</v>
+      </c>
+      <c r="B31" s="34">
         <v>3.96</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <v>7.24</v>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="34">
         <v>4.86</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="34">
         <v>0.38</v>
       </c>
-      <c r="F31" s="32">
+      <c r="F31" s="33">
         <v>-1.34</v>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="34">
         <v>0.87</v>
       </c>
-      <c r="H31" s="33">
+      <c r="H31" s="34">
         <v>3.84</v>
       </c>
-      <c r="I31" s="33">
+      <c r="I31" s="34">
         <v>7.49</v>
       </c>
-      <c r="J31" s="33">
+      <c r="J31" s="34">
         <v>10.57</v>
       </c>
-      <c r="K31" s="33">
+      <c r="K31" s="34">
         <v>16.25</v>
       </c>
-      <c r="L31" s="33">
+      <c r="L31" s="34">
         <v>16.2</v>
       </c>
-      <c r="M31" s="33">
+      <c r="M31" s="34">
         <v>3.46</v>
       </c>
-      <c r="N31" s="32">
+      <c r="N31" s="33">
         <v>-7.56</v>
       </c>
-      <c r="O31" s="32">
+      <c r="O31" s="33">
         <v>-9.14</v>
       </c>
-      <c r="P31" s="32">
+      <c r="P31" s="33">
         <v>-6.87</v>
       </c>
-      <c r="Q31" s="32">
+      <c r="Q31" s="33">
         <v>-5.57</v>
       </c>
-      <c r="R31" s="32">
+      <c r="R31" s="33">
         <v>-0.47</v>
       </c>
-      <c r="S31" s="33">
+      <c r="S31" s="34">
         <v>2.58</v>
       </c>
-      <c r="T31" s="33">
+      <c r="T31" s="34">
         <v>2.94</v>
       </c>
-      <c r="U31" s="33">
+      <c r="U31" s="34">
         <v>0.45</v>
       </c>
-      <c r="V31" s="33">
+      <c r="V31" s="34">
         <v>2.91</v>
       </c>
-      <c r="W31" s="33">
+      <c r="W31" s="34">
         <v>0.95</v>
       </c>
-      <c r="X31" s="32">
+      <c r="X31" s="33">
         <v>-3.14</v>
       </c>
-      <c r="Y31" s="32">
+      <c r="Y31" s="33">
         <v>-8.1</v>
       </c>
-      <c r="Z31" s="32">
+      <c r="Z31" s="33">
         <v>-11.1</v>
       </c>
-      <c r="AA31" s="32">
+      <c r="AA31" s="33">
         <v>-11.65</v>
       </c>
-      <c r="AB31" s="32">
+      <c r="AB31" s="33">
         <v>-16.03</v>
       </c>
-      <c r="AC31" s="32">
+      <c r="AC31" s="33">
         <v>-8.04</v>
       </c>
-      <c r="AD31" s="33">
+      <c r="AD31" s="34">
         <v>3.76</v>
       </c>
-      <c r="AE31" s="33"/>
-      <c r="AF31" s="33"/>
-      <c r="AG31" s="33"/>
-      <c r="AH31" s="33"/>
+      <c r="AE31" s="34"/>
+      <c r="AF31" s="34"/>
+      <c r="AG31" s="34"/>
+      <c r="AH31" s="34"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="26" t="s">
-        <v>459</v>
-      </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-      <c r="W32" s="27"/>
-      <c r="X32" s="27"/>
-      <c r="Y32" s="27"/>
-      <c r="Z32" s="27"/>
-      <c r="AA32" s="27"/>
-      <c r="AB32" s="27"/>
-      <c r="AC32" s="27"/>
-      <c r="AD32" s="27"/>
-      <c r="AE32" s="27"/>
-      <c r="AF32" s="27"/>
-      <c r="AG32" s="27"/>
-      <c r="AH32" s="27"/>
+      <c r="A32" s="27" t="s">
+        <v>460</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="28"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
+      <c r="AC32" s="28"/>
+      <c r="AD32" s="28"/>
+      <c r="AE32" s="28"/>
+      <c r="AF32" s="28"/>
+      <c r="AG32" s="28"/>
+      <c r="AH32" s="28"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="28" t="s">
-        <v>460</v>
-      </c>
-      <c r="B33" s="33">
+      <c r="A33" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="B33" s="34">
         <v>0.0</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="34">
         <v>0.0</v>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="34">
         <v>0.0</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="34">
         <v>0.0</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="34">
         <v>0.0</v>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="34">
         <v>0.0</v>
       </c>
-      <c r="H33" s="33">
+      <c r="H33" s="34">
         <v>0.0</v>
       </c>
-      <c r="I33" s="33">
+      <c r="I33" s="34">
         <v>0.0</v>
       </c>
-      <c r="J33" s="33">
+      <c r="J33" s="34">
         <v>0.0</v>
       </c>
-      <c r="K33" s="33">
+      <c r="K33" s="34">
         <v>0.0</v>
       </c>
-      <c r="L33" s="33">
+      <c r="L33" s="34">
         <v>2.36</v>
       </c>
-      <c r="M33" s="33">
+      <c r="M33" s="34">
         <v>2.22</v>
       </c>
-      <c r="N33" s="33">
+      <c r="N33" s="34">
         <v>6.29</v>
       </c>
-      <c r="O33" s="33">
+      <c r="O33" s="34">
         <v>2.07</v>
       </c>
-      <c r="P33" s="33">
+      <c r="P33" s="34">
         <v>1.59</v>
       </c>
-      <c r="Q33" s="33">
+      <c r="Q33" s="34">
         <v>1.79</v>
       </c>
-      <c r="R33" s="33">
+      <c r="R33" s="34">
         <v>0.0</v>
       </c>
-      <c r="S33" s="33">
+      <c r="S33" s="34">
         <v>15.74</v>
       </c>
-      <c r="T33" s="33">
+      <c r="T33" s="34">
         <v>3.3</v>
       </c>
-      <c r="U33" s="33">
+      <c r="U33" s="34">
         <v>3.64</v>
       </c>
-      <c r="V33" s="33">
+      <c r="V33" s="34">
         <v>4.2</v>
       </c>
-      <c r="W33" s="33">
+      <c r="W33" s="34">
         <v>7.6</v>
       </c>
-      <c r="X33" s="33">
+      <c r="X33" s="34">
         <v>5.67</v>
       </c>
-      <c r="Y33" s="33">
+      <c r="Y33" s="34">
         <v>8.18</v>
       </c>
-      <c r="Z33" s="33">
+      <c r="Z33" s="34">
         <v>0.0</v>
       </c>
-      <c r="AA33" s="33">
+      <c r="AA33" s="34">
         <v>3.34</v>
       </c>
-      <c r="AB33" s="33">
+      <c r="AB33" s="34">
         <v>7.65</v>
       </c>
-      <c r="AC33" s="33">
+      <c r="AC33" s="34">
         <v>5.51</v>
       </c>
-      <c r="AD33" s="33">
+      <c r="AD33" s="34">
         <v>3.5</v>
       </c>
-      <c r="AE33" s="33">
+      <c r="AE33" s="34">
         <v>5.51</v>
       </c>
-      <c r="AF33" s="33">
+      <c r="AF33" s="34">
         <v>6.68</v>
       </c>
-      <c r="AG33" s="33">
+      <c r="AG33" s="34">
         <v>4.46</v>
       </c>
-      <c r="AH33" s="33">
+      <c r="AH33" s="34">
         <v>5.48</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="28" t="s">
-        <v>461</v>
-      </c>
-      <c r="B34" s="33">
+      <c r="A34" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="B34" s="34">
         <v>0.0</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="34">
         <v>0.0</v>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="34">
         <v>0.0</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="34">
         <v>0.0</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="34">
         <v>0.0</v>
       </c>
-      <c r="G34" s="33">
+      <c r="G34" s="34">
         <v>0.0</v>
       </c>
-      <c r="H34" s="33">
+      <c r="H34" s="34">
         <v>0.85</v>
       </c>
-      <c r="I34" s="33">
+      <c r="I34" s="34">
         <v>1.23</v>
       </c>
-      <c r="J34" s="33">
+      <c r="J34" s="34">
         <v>2.0</v>
       </c>
-      <c r="K34" s="33">
+      <c r="K34" s="34">
         <v>2.73</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <v>2.95</v>
       </c>
-      <c r="M34" s="33">
+      <c r="M34" s="34">
         <v>2.85</v>
       </c>
-      <c r="N34" s="33">
+      <c r="N34" s="34">
         <v>2.35</v>
       </c>
-      <c r="O34" s="33">
+      <c r="O34" s="34">
         <v>2.68</v>
       </c>
-      <c r="P34" s="33">
+      <c r="P34" s="34">
         <v>2.99</v>
       </c>
-      <c r="Q34" s="33">
+      <c r="Q34" s="34">
         <v>3.35</v>
       </c>
-      <c r="R34" s="33">
+      <c r="R34" s="34">
         <v>3.78</v>
       </c>
-      <c r="S34" s="33">
+      <c r="S34" s="34">
         <v>4.91</v>
       </c>
-      <c r="T34" s="33">
+      <c r="T34" s="34">
         <v>4.21</v>
       </c>
-      <c r="U34" s="33">
+      <c r="U34" s="34">
         <v>4.83</v>
       </c>
-      <c r="V34" s="33">
+      <c r="V34" s="34">
         <v>4.94</v>
       </c>
-      <c r="W34" s="33">
+      <c r="W34" s="34">
         <v>4.48</v>
       </c>
-      <c r="X34" s="33">
+      <c r="X34" s="34">
         <v>4.16</v>
       </c>
-      <c r="Y34" s="33">
+      <c r="Y34" s="34">
         <v>4.08</v>
       </c>
-      <c r="Z34" s="33">
+      <c r="Z34" s="34">
         <v>3.59</v>
       </c>
-      <c r="AA34" s="33">
+      <c r="AA34" s="34">
         <v>4.33</v>
       </c>
-      <c r="AB34" s="33">
+      <c r="AB34" s="34">
         <v>5.57</v>
       </c>
-      <c r="AC34" s="33">
+      <c r="AC34" s="34">
         <v>4.92</v>
       </c>
-      <c r="AD34" s="33">
+      <c r="AD34" s="34">
         <v>4.87</v>
       </c>
-      <c r="AE34" s="33"/>
-      <c r="AF34" s="33"/>
-      <c r="AG34" s="33"/>
-      <c r="AH34" s="33"/>
+      <c r="AE34" s="34"/>
+      <c r="AF34" s="34"/>
+      <c r="AG34" s="34"/>
+      <c r="AH34" s="34"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>462</v>
-      </c>
-      <c r="B35" s="33">
+      <c r="A35" s="29" t="s">
+        <v>463</v>
+      </c>
+      <c r="B35" s="34">
         <v>0.0</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="34">
         <v>0.0</v>
       </c>
-      <c r="D35" s="33">
+      <c r="D35" s="34">
         <v>0.0</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="34">
         <v>0.0</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="34">
         <v>0.0</v>
       </c>
-      <c r="G35" s="33">
+      <c r="G35" s="34">
         <v>0.0</v>
       </c>
-      <c r="H35" s="33">
+      <c r="H35" s="34">
         <v>0.0</v>
       </c>
-      <c r="I35" s="33">
+      <c r="I35" s="34">
         <v>0.0</v>
       </c>
-      <c r="J35" s="33">
+      <c r="J35" s="34">
         <v>0.0</v>
       </c>
-      <c r="K35" s="33">
+      <c r="K35" s="34">
         <v>0.0</v>
       </c>
-      <c r="L35" s="33">
+      <c r="L35" s="34">
         <v>2.36</v>
       </c>
-      <c r="M35" s="33">
+      <c r="M35" s="34">
         <v>2.22</v>
       </c>
-      <c r="N35" s="33">
+      <c r="N35" s="34">
         <v>6.29</v>
       </c>
-      <c r="O35" s="33">
+      <c r="O35" s="34">
         <v>2.07</v>
       </c>
-      <c r="P35" s="33">
+      <c r="P35" s="34">
         <v>2.2</v>
       </c>
-      <c r="Q35" s="33">
+      <c r="Q35" s="34">
         <v>2.48</v>
       </c>
-      <c r="R35" s="33">
+      <c r="R35" s="34">
         <v>0.0</v>
       </c>
-      <c r="S35" s="33">
+      <c r="S35" s="34">
         <v>21.86</v>
       </c>
-      <c r="T35" s="33">
+      <c r="T35" s="34">
         <v>4.59</v>
       </c>
-      <c r="U35" s="33">
+      <c r="U35" s="34">
         <v>5.05</v>
       </c>
-      <c r="V35" s="33">
+      <c r="V35" s="34">
         <v>5.83</v>
       </c>
-      <c r="W35" s="33">
+      <c r="W35" s="34">
         <v>10.55</v>
       </c>
-      <c r="X35" s="33">
+      <c r="X35" s="34">
         <v>7.87</v>
       </c>
-      <c r="Y35" s="33">
+      <c r="Y35" s="34">
         <v>11.37</v>
       </c>
-      <c r="Z35" s="33">
+      <c r="Z35" s="34">
         <v>0.0</v>
       </c>
-      <c r="AA35" s="33">
+      <c r="AA35" s="34">
         <v>4.55</v>
       </c>
-      <c r="AB35" s="33">
+      <c r="AB35" s="34">
         <v>10.2</v>
       </c>
-      <c r="AC35" s="33">
+      <c r="AC35" s="34">
         <v>7.34</v>
       </c>
-      <c r="AD35" s="33">
+      <c r="AD35" s="34">
         <v>4.67</v>
       </c>
-      <c r="AE35" s="33">
+      <c r="AE35" s="34">
         <v>7.35</v>
       </c>
-      <c r="AF35" s="33">
+      <c r="AF35" s="34">
         <v>9.54</v>
       </c>
-      <c r="AG35" s="33">
+      <c r="AG35" s="34">
         <v>6.37</v>
       </c>
-      <c r="AH35" s="33">
+      <c r="AH35" s="34">
         <v>7.83</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="28" t="s">
-        <v>463</v>
-      </c>
-      <c r="B36" s="33">
+      <c r="A36" s="29" t="s">
+        <v>464</v>
+      </c>
+      <c r="B36" s="34">
         <v>0.0</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="34">
         <v>0.0</v>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="34">
         <v>0.0</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="34">
         <v>0.0</v>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="34">
         <v>0.0</v>
       </c>
-      <c r="G36" s="33">
+      <c r="G36" s="34">
         <v>0.0</v>
       </c>
-      <c r="H36" s="33">
+      <c r="H36" s="34">
         <v>0.43</v>
       </c>
-      <c r="I36" s="33">
+      <c r="I36" s="34">
         <v>0.8</v>
       </c>
-      <c r="J36" s="33">
+      <c r="J36" s="34">
         <v>1.59</v>
       </c>
-      <c r="K36" s="33">
+      <c r="K36" s="34">
         <v>2.22</v>
       </c>
-      <c r="L36" s="33">
+      <c r="L36" s="34">
         <v>3.04</v>
       </c>
-      <c r="M36" s="33">
+      <c r="M36" s="34">
         <v>3.1</v>
       </c>
-      <c r="N36" s="33">
+      <c r="N36" s="34">
         <v>2.61</v>
       </c>
-      <c r="O36" s="33">
+      <c r="O36" s="34">
         <v>3.58</v>
       </c>
-      <c r="P36" s="33">
+      <c r="P36" s="34">
         <v>4.15</v>
       </c>
-      <c r="Q36" s="33">
+      <c r="Q36" s="34">
         <v>4.65</v>
       </c>
-      <c r="R36" s="33">
+      <c r="R36" s="34">
         <v>5.25</v>
       </c>
-      <c r="S36" s="33">
+      <c r="S36" s="34">
         <v>6.82</v>
       </c>
-      <c r="T36" s="33">
+      <c r="T36" s="34">
         <v>5.84</v>
       </c>
-      <c r="U36" s="33">
+      <c r="U36" s="34">
         <v>6.71</v>
       </c>
-      <c r="V36" s="33">
+      <c r="V36" s="34">
         <v>6.86</v>
       </c>
-      <c r="W36" s="33">
+      <c r="W36" s="34">
         <v>6.17</v>
       </c>
-      <c r="X36" s="33">
+      <c r="X36" s="34">
         <v>5.68</v>
       </c>
-      <c r="Y36" s="33">
+      <c r="Y36" s="34">
         <v>5.54</v>
       </c>
-      <c r="Z36" s="33">
+      <c r="Z36" s="34">
         <v>4.83</v>
       </c>
-      <c r="AA36" s="33">
+      <c r="AA36" s="34">
         <v>5.82</v>
       </c>
-      <c r="AB36" s="33">
+      <c r="AB36" s="34">
         <v>7.52</v>
       </c>
-      <c r="AC36" s="33">
+      <c r="AC36" s="34">
         <v>6.73</v>
       </c>
-      <c r="AD36" s="33">
+      <c r="AD36" s="34">
         <v>6.76</v>
       </c>
-      <c r="AE36" s="33"/>
-      <c r="AF36" s="33"/>
-      <c r="AG36" s="33"/>
-      <c r="AH36" s="33"/>
+      <c r="AE36" s="34"/>
+      <c r="AF36" s="34"/>
+      <c r="AG36" s="34"/>
+      <c r="AH36" s="34"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="26" t="s">
-        <v>464</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-      <c r="W37" s="27"/>
-      <c r="X37" s="27"/>
-      <c r="Y37" s="27"/>
-      <c r="Z37" s="27"/>
-      <c r="AA37" s="27"/>
-      <c r="AB37" s="27"/>
-      <c r="AC37" s="27"/>
-      <c r="AD37" s="27"/>
-      <c r="AE37" s="27"/>
-      <c r="AF37" s="27"/>
-      <c r="AG37" s="27"/>
-      <c r="AH37" s="27"/>
+      <c r="A37" s="27" t="s">
+        <v>465</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="28"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
+      <c r="AC37" s="28"/>
+      <c r="AD37" s="28"/>
+      <c r="AE37" s="28"/>
+      <c r="AF37" s="28"/>
+      <c r="AG37" s="28"/>
+      <c r="AH37" s="28"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>465</v>
-      </c>
-      <c r="B38" s="31">
+      <c r="A38" s="29" t="s">
+        <v>466</v>
+      </c>
+      <c r="B38" s="32">
         <v>2.8</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <v>2.18</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <v>2.35</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <v>2.28</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <v>1.81</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="32">
         <v>1.7</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="32">
         <v>0.9</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="32">
         <v>0.43</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="32">
         <v>1.26</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="32">
         <v>0.9</v>
       </c>
-      <c r="L38" s="31">
+      <c r="L38" s="32">
         <v>0.68</v>
       </c>
-      <c r="M38" s="31">
+      <c r="M38" s="32">
         <v>0.63</v>
       </c>
-      <c r="N38" s="31">
+      <c r="N38" s="32">
         <v>0.54</v>
       </c>
-      <c r="O38" s="31">
+      <c r="O38" s="32">
         <v>0.4</v>
       </c>
-      <c r="P38" s="31">
+      <c r="P38" s="32">
         <v>0.53</v>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="32">
         <v>0.81</v>
       </c>
-      <c r="R38" s="31">
+      <c r="R38" s="32">
         <v>0.88</v>
       </c>
-      <c r="S38" s="31">
+      <c r="S38" s="32">
         <v>0.35</v>
       </c>
-      <c r="T38" s="31">
+      <c r="T38" s="32">
         <v>1.58</v>
       </c>
-      <c r="U38" s="31">
+      <c r="U38" s="32">
         <v>1.99</v>
       </c>
-      <c r="V38" s="31">
+      <c r="V38" s="32">
         <v>1.2</v>
       </c>
-      <c r="W38" s="31">
+      <c r="W38" s="32">
         <v>0.69</v>
       </c>
-      <c r="X38" s="31">
+      <c r="X38" s="32">
         <v>0.42</v>
       </c>
-      <c r="Y38" s="31">
+      <c r="Y38" s="32">
         <v>0.28</v>
       </c>
-      <c r="Z38" s="31">
+      <c r="Z38" s="32">
         <v>0.33</v>
       </c>
-      <c r="AA38" s="31">
+      <c r="AA38" s="32">
         <v>1.14</v>
       </c>
-      <c r="AB38" s="31">
+      <c r="AB38" s="32">
         <v>0.34</v>
       </c>
-      <c r="AC38" s="31">
+      <c r="AC38" s="32">
         <v>0.52</v>
       </c>
-      <c r="AD38" s="31">
+      <c r="AD38" s="32">
         <v>0.73</v>
       </c>
-      <c r="AE38" s="31">
+      <c r="AE38" s="32">
         <v>0.5</v>
       </c>
-      <c r="AF38" s="31">
+      <c r="AF38" s="32">
         <v>0.38</v>
       </c>
-      <c r="AG38" s="31">
+      <c r="AG38" s="32">
         <v>0.48</v>
       </c>
-      <c r="AH38" s="31">
+      <c r="AH38" s="32">
         <v>0.44</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="28" t="s">
-        <v>466</v>
-      </c>
-      <c r="B39" s="31">
+      <c r="A39" s="29" t="s">
+        <v>467</v>
+      </c>
+      <c r="B39" s="32">
         <v>2.34</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <v>2.09</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="32">
         <v>1.85</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="32">
         <v>1.42</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="32">
         <v>1.22</v>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="32">
         <v>1.02</v>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="32">
         <v>0.84</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="32">
         <v>0.79</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="32">
         <v>0.8</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="32">
         <v>0.63</v>
       </c>
-      <c r="L39" s="31">
+      <c r="L39" s="32">
         <v>0.56</v>
       </c>
-      <c r="M39" s="31">
+      <c r="M39" s="32">
         <v>0.57</v>
       </c>
-      <c r="N39" s="31">
+      <c r="N39" s="32">
         <v>0.61</v>
       </c>
-      <c r="O39" s="31">
+      <c r="O39" s="32">
         <v>0.58</v>
       </c>
-      <c r="P39" s="31">
+      <c r="P39" s="32">
         <v>0.81</v>
       </c>
-      <c r="Q39" s="31">
+      <c r="Q39" s="32">
         <v>1.07</v>
       </c>
-      <c r="R39" s="31">
+      <c r="R39" s="32">
         <v>1.16</v>
       </c>
-      <c r="S39" s="31">
+      <c r="S39" s="32">
         <v>1.15</v>
       </c>
-      <c r="T39" s="31">
+      <c r="T39" s="32">
         <v>1.2</v>
       </c>
-      <c r="U39" s="31">
+      <c r="U39" s="32">
         <v>0.91</v>
       </c>
-      <c r="V39" s="31">
+      <c r="V39" s="32">
         <v>0.56</v>
       </c>
-      <c r="W39" s="31">
+      <c r="W39" s="32">
         <v>0.59</v>
       </c>
-      <c r="X39" s="31">
+      <c r="X39" s="32">
         <v>0.53</v>
       </c>
-      <c r="Y39" s="31">
+      <c r="Y39" s="32">
         <v>0.55</v>
       </c>
-      <c r="Z39" s="31">
+      <c r="Z39" s="32">
         <v>0.63</v>
       </c>
-      <c r="AA39" s="31">
+      <c r="AA39" s="32">
         <v>0.7</v>
       </c>
-      <c r="AB39" s="31">
+      <c r="AB39" s="32">
         <v>0.48</v>
       </c>
-      <c r="AC39" s="31">
+      <c r="AC39" s="32">
         <v>0.52</v>
       </c>
-      <c r="AD39" s="31">
+      <c r="AD39" s="32">
         <v>0.51</v>
       </c>
-      <c r="AE39" s="29"/>
-      <c r="AF39" s="29"/>
-      <c r="AG39" s="29"/>
-      <c r="AH39" s="29"/>
+      <c r="AE39" s="30"/>
+      <c r="AF39" s="30"/>
+      <c r="AG39" s="30"/>
+      <c r="AH39" s="30"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="26" t="s">
-        <v>467</v>
-      </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="27"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-      <c r="W40" s="27"/>
-      <c r="X40" s="27"/>
-      <c r="Y40" s="27"/>
-      <c r="Z40" s="27"/>
-      <c r="AA40" s="27"/>
-      <c r="AB40" s="27"/>
-      <c r="AC40" s="27"/>
-      <c r="AD40" s="27"/>
-      <c r="AE40" s="27"/>
-      <c r="AF40" s="27"/>
-      <c r="AG40" s="27"/>
-      <c r="AH40" s="27"/>
+      <c r="A40" s="27" t="s">
+        <v>468</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="28"/>
+      <c r="W40" s="28"/>
+      <c r="X40" s="28"/>
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="28"/>
+      <c r="AA40" s="28"/>
+      <c r="AB40" s="28"/>
+      <c r="AC40" s="28"/>
+      <c r="AD40" s="28"/>
+      <c r="AE40" s="28"/>
+      <c r="AF40" s="28"/>
+      <c r="AG40" s="28"/>
+      <c r="AH40" s="28"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>468</v>
-      </c>
-      <c r="B41" s="31">
+      <c r="A41" s="29" t="s">
+        <v>469</v>
+      </c>
+      <c r="B41" s="32">
         <v>4.26</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <v>3.52</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <v>3.81</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="32">
         <v>4.9</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="32">
         <v>4.73</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="32">
         <v>5.27</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="32">
         <v>10.23</v>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="32">
         <v>2.1</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="32">
         <v>4.72</v>
       </c>
-      <c r="K41" s="31">
+      <c r="K41" s="32">
         <v>0.98</v>
       </c>
-      <c r="L41" s="31">
+      <c r="L41" s="32">
         <v>1.15</v>
       </c>
-      <c r="M41" s="31">
+      <c r="M41" s="32">
         <v>0.99</v>
       </c>
-      <c r="N41" s="31">
+      <c r="N41" s="32">
         <v>0.83</v>
       </c>
-      <c r="O41" s="31">
+      <c r="O41" s="32">
         <v>0.62</v>
       </c>
-      <c r="P41" s="31">
+      <c r="P41" s="32">
         <v>1.04</v>
       </c>
-      <c r="Q41" s="31">
+      <c r="Q41" s="32">
         <v>1.43</v>
       </c>
-      <c r="R41" s="31">
+      <c r="R41" s="32">
         <v>1.56</v>
       </c>
-      <c r="S41" s="31">
+      <c r="S41" s="32">
         <v>0.78</v>
       </c>
-      <c r="T41" s="31">
+      <c r="T41" s="32">
         <v>3.18</v>
       </c>
-      <c r="U41" s="31">
+      <c r="U41" s="32">
         <v>2.88</v>
       </c>
-      <c r="V41" s="31">
+      <c r="V41" s="32">
         <v>1.93</v>
       </c>
-      <c r="W41" s="31">
+      <c r="W41" s="32">
         <v>2.01</v>
       </c>
-      <c r="X41" s="31">
+      <c r="X41" s="32">
         <v>0.54</v>
       </c>
-      <c r="Y41" s="31">
+      <c r="Y41" s="32">
         <v>0.37</v>
       </c>
-      <c r="Z41" s="31">
+      <c r="Z41" s="32">
         <v>0.42</v>
       </c>
-      <c r="AA41" s="31">
+      <c r="AA41" s="32">
         <v>1.48</v>
       </c>
-      <c r="AB41" s="31">
+      <c r="AB41" s="32">
         <v>0.53</v>
       </c>
-      <c r="AC41" s="31">
+      <c r="AC41" s="32">
         <v>1.03</v>
       </c>
-      <c r="AD41" s="31">
+      <c r="AD41" s="32">
         <v>1.26</v>
       </c>
-      <c r="AE41" s="31">
+      <c r="AE41" s="32">
         <v>0.61</v>
       </c>
-      <c r="AF41" s="31">
+      <c r="AF41" s="32">
         <v>0.46</v>
       </c>
-      <c r="AG41" s="31">
+      <c r="AG41" s="32">
         <v>0.59</v>
       </c>
-      <c r="AH41" s="31">
+      <c r="AH41" s="32">
         <v>0.44</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="28" t="s">
-        <v>469</v>
-      </c>
-      <c r="B42" s="31">
+      <c r="A42" s="29" t="s">
+        <v>470</v>
+      </c>
+      <c r="B42" s="32">
         <v>4.11</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="32">
         <v>4.17</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="32">
         <v>4.72</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="32">
         <v>4.81</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="32">
         <v>4.75</v>
       </c>
-      <c r="G42" s="31">
+      <c r="G42" s="32">
         <v>2.57</v>
       </c>
-      <c r="H42" s="31">
+      <c r="H42" s="32">
         <v>1.85</v>
       </c>
-      <c r="I42" s="31">
+      <c r="I42" s="32">
         <v>1.44</v>
       </c>
-      <c r="J42" s="31">
+      <c r="J42" s="32">
         <v>1.28</v>
       </c>
-      <c r="K42" s="31">
+      <c r="K42" s="32">
         <v>0.92</v>
       </c>
-      <c r="L42" s="31">
+      <c r="L42" s="32">
         <v>0.91</v>
       </c>
-      <c r="M42" s="31">
+      <c r="M42" s="32">
         <v>0.94</v>
       </c>
-      <c r="N42" s="31">
+      <c r="N42" s="32">
         <v>1.02</v>
       </c>
-      <c r="O42" s="31">
+      <c r="O42" s="32">
         <v>1.04</v>
       </c>
-      <c r="P42" s="31">
+      <c r="P42" s="32">
         <v>1.56</v>
       </c>
-      <c r="Q42" s="31">
+      <c r="Q42" s="32">
         <v>1.95</v>
       </c>
-      <c r="R42" s="31">
+      <c r="R42" s="32">
         <v>2.08</v>
       </c>
-      <c r="S42" s="31">
+      <c r="S42" s="32">
         <v>2.22</v>
       </c>
-      <c r="T42" s="31">
+      <c r="T42" s="32">
         <v>2.03</v>
       </c>
-      <c r="U42" s="31">
+      <c r="U42" s="32">
         <v>1.41</v>
       </c>
-      <c r="V42" s="31">
+      <c r="V42" s="32">
         <v>0.84</v>
       </c>
-      <c r="W42" s="31">
+      <c r="W42" s="32">
         <v>0.83</v>
       </c>
-      <c r="X42" s="31">
+      <c r="X42" s="32">
         <v>0.7</v>
       </c>
-      <c r="Y42" s="31">
+      <c r="Y42" s="32">
         <v>0.76</v>
       </c>
-      <c r="Z42" s="31">
+      <c r="Z42" s="32">
         <v>0.91</v>
       </c>
-      <c r="AA42" s="31">
+      <c r="AA42" s="32">
         <v>1.03</v>
       </c>
-      <c r="AB42" s="31">
+      <c r="AB42" s="32">
         <v>0.71</v>
       </c>
-      <c r="AC42" s="31">
+      <c r="AC42" s="32">
         <v>0.74</v>
       </c>
-      <c r="AD42" s="31">
+      <c r="AD42" s="32">
         <v>0.64</v>
       </c>
-      <c r="AE42" s="29"/>
-      <c r="AF42" s="29"/>
-      <c r="AG42" s="29"/>
-      <c r="AH42" s="29"/>
+      <c r="AE42" s="30"/>
+      <c r="AF42" s="30"/>
+      <c r="AG42" s="30"/>
+      <c r="AH42" s="30"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="26" t="s">
-        <v>470</v>
-      </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="27"/>
-      <c r="S43" s="27"/>
-      <c r="T43" s="27"/>
-      <c r="U43" s="27"/>
-      <c r="V43" s="27"/>
-      <c r="W43" s="27"/>
-      <c r="X43" s="27"/>
-      <c r="Y43" s="27"/>
-      <c r="Z43" s="27"/>
-      <c r="AA43" s="27"/>
-      <c r="AB43" s="27"/>
-      <c r="AC43" s="27"/>
-      <c r="AD43" s="27"/>
-      <c r="AE43" s="27"/>
-      <c r="AF43" s="27"/>
-      <c r="AG43" s="27"/>
-      <c r="AH43" s="27"/>
+      <c r="A43" s="27" t="s">
+        <v>471</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="28"/>
+      <c r="W43" s="28"/>
+      <c r="X43" s="28"/>
+      <c r="Y43" s="28"/>
+      <c r="Z43" s="28"/>
+      <c r="AA43" s="28"/>
+      <c r="AB43" s="28"/>
+      <c r="AC43" s="28"/>
+      <c r="AD43" s="28"/>
+      <c r="AE43" s="28"/>
+      <c r="AF43" s="28"/>
+      <c r="AG43" s="28"/>
+      <c r="AH43" s="28"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="28" t="s">
-        <v>471</v>
-      </c>
-      <c r="B44" s="31">
+      <c r="A44" s="29" t="s">
+        <v>472</v>
+      </c>
+      <c r="B44" s="32">
         <v>1.61</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <v>1.14</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <v>1.22</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <v>1.09</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <v>1.0</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <v>0.76</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="32">
         <v>0.44</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="32">
         <v>0.2</v>
       </c>
-      <c r="J44" s="31">
+      <c r="J44" s="32">
         <v>0.7</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="32">
         <v>0.74</v>
       </c>
-      <c r="L44" s="31">
+      <c r="L44" s="32">
         <v>0.44</v>
       </c>
-      <c r="M44" s="31">
+      <c r="M44" s="32">
         <v>0.24</v>
       </c>
-      <c r="N44" s="31">
+      <c r="N44" s="32">
         <v>0.19</v>
       </c>
-      <c r="O44" s="31">
+      <c r="O44" s="32">
         <v>0.15</v>
       </c>
-      <c r="P44" s="31">
+      <c r="P44" s="32">
         <v>0.14</v>
       </c>
-      <c r="Q44" s="31">
+      <c r="Q44" s="32">
         <v>0.23</v>
       </c>
-      <c r="R44" s="31">
+      <c r="R44" s="32">
         <v>0.28</v>
       </c>
-      <c r="S44" s="31">
+      <c r="S44" s="32">
         <v>0.09</v>
       </c>
-      <c r="T44" s="31">
+      <c r="T44" s="32">
         <v>0.38</v>
       </c>
-      <c r="U44" s="31">
+      <c r="U44" s="32">
         <v>0.52</v>
       </c>
-      <c r="V44" s="31">
+      <c r="V44" s="32">
         <v>0.38</v>
       </c>
-      <c r="W44" s="31">
+      <c r="W44" s="32">
         <v>0.25</v>
       </c>
-      <c r="X44" s="31">
+      <c r="X44" s="32">
         <v>0.21</v>
       </c>
-      <c r="Y44" s="31">
+      <c r="Y44" s="32">
         <v>0.15</v>
       </c>
-      <c r="Z44" s="31">
+      <c r="Z44" s="32">
         <v>0.19</v>
       </c>
-      <c r="AA44" s="31">
+      <c r="AA44" s="32">
         <v>2.81</v>
       </c>
-      <c r="AB44" s="31">
+      <c r="AB44" s="32">
         <v>0.17</v>
       </c>
-      <c r="AC44" s="31">
+      <c r="AC44" s="32">
         <v>0.22</v>
       </c>
-      <c r="AD44" s="31">
+      <c r="AD44" s="32">
         <v>0.34</v>
       </c>
-      <c r="AE44" s="31">
+      <c r="AE44" s="32">
         <v>0.26</v>
       </c>
-      <c r="AF44" s="31">
+      <c r="AF44" s="32">
         <v>0.2</v>
       </c>
-      <c r="AG44" s="31">
+      <c r="AG44" s="32">
         <v>0.23</v>
       </c>
-      <c r="AH44" s="31">
+      <c r="AH44" s="32">
         <v>0.2</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="28" t="s">
-        <v>472</v>
-      </c>
-      <c r="B45" s="31">
+      <c r="A45" s="29" t="s">
+        <v>473</v>
+      </c>
+      <c r="B45" s="32">
         <v>1.25</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="32">
         <v>1.06</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="32">
         <v>0.92</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="32">
         <v>0.69</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="32">
         <v>0.61</v>
       </c>
-      <c r="G45" s="31">
+      <c r="G45" s="32">
         <v>0.56</v>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="32">
         <v>0.49</v>
       </c>
-      <c r="I45" s="31">
+      <c r="I45" s="32">
         <v>0.42</v>
       </c>
-      <c r="J45" s="31">
+      <c r="J45" s="32">
         <v>0.4</v>
       </c>
-      <c r="K45" s="31">
+      <c r="K45" s="32">
         <v>0.29</v>
       </c>
-      <c r="L45" s="31">
+      <c r="L45" s="32">
         <v>0.21</v>
       </c>
-      <c r="M45" s="31">
+      <c r="M45" s="32">
         <v>0.19</v>
       </c>
-      <c r="N45" s="31">
+      <c r="N45" s="32">
         <v>0.19</v>
       </c>
-      <c r="O45" s="31">
+      <c r="O45" s="32">
         <v>0.17</v>
       </c>
-      <c r="P45" s="31">
+      <c r="P45" s="32">
         <v>0.22</v>
       </c>
-      <c r="Q45" s="31">
+      <c r="Q45" s="32">
         <v>0.29</v>
       </c>
-      <c r="R45" s="31">
+      <c r="R45" s="32">
         <v>0.32</v>
       </c>
-      <c r="S45" s="31">
+      <c r="S45" s="32">
         <v>0.32</v>
       </c>
-      <c r="T45" s="31">
+      <c r="T45" s="32">
         <v>0.37</v>
       </c>
-      <c r="U45" s="31">
+      <c r="U45" s="32">
         <v>0.34</v>
       </c>
-      <c r="V45" s="31">
+      <c r="V45" s="32">
         <v>0.25</v>
       </c>
-      <c r="W45" s="31">
+      <c r="W45" s="32">
         <v>0.35</v>
       </c>
-      <c r="X45" s="31">
+      <c r="X45" s="32">
         <v>0.34</v>
       </c>
-      <c r="Y45" s="31">
+      <c r="Y45" s="32">
         <v>0.35</v>
       </c>
-      <c r="Z45" s="31">
+      <c r="Z45" s="32">
         <v>0.41</v>
       </c>
-      <c r="AA45" s="31">
+      <c r="AA45" s="32">
         <v>0.46</v>
       </c>
-      <c r="AB45" s="31">
+      <c r="AB45" s="32">
         <v>0.23</v>
       </c>
-      <c r="AC45" s="31">
+      <c r="AC45" s="32">
         <v>0.25</v>
       </c>
-      <c r="AD45" s="31">
+      <c r="AD45" s="32">
         <v>0.25</v>
       </c>
-      <c r="AE45" s="29"/>
-      <c r="AF45" s="29"/>
-      <c r="AG45" s="29"/>
-      <c r="AH45" s="29"/>
+      <c r="AE45" s="30"/>
+      <c r="AF45" s="30"/>
+      <c r="AG45" s="30"/>
+      <c r="AH45" s="30"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="26" t="s">
-        <v>473</v>
-      </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="27"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="27"/>
-      <c r="W46" s="27"/>
-      <c r="X46" s="27"/>
-      <c r="Y46" s="27"/>
-      <c r="Z46" s="27"/>
-      <c r="AA46" s="27"/>
-      <c r="AB46" s="27"/>
-      <c r="AC46" s="27"/>
-      <c r="AD46" s="27"/>
-      <c r="AE46" s="27"/>
-      <c r="AF46" s="27"/>
-      <c r="AG46" s="27"/>
-      <c r="AH46" s="27"/>
+      <c r="A46" s="27" t="s">
+        <v>474</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+      <c r="T46" s="28"/>
+      <c r="U46" s="28"/>
+      <c r="V46" s="28"/>
+      <c r="W46" s="28"/>
+      <c r="X46" s="28"/>
+      <c r="Y46" s="28"/>
+      <c r="Z46" s="28"/>
+      <c r="AA46" s="28"/>
+      <c r="AB46" s="28"/>
+      <c r="AC46" s="28"/>
+      <c r="AD46" s="28"/>
+      <c r="AE46" s="28"/>
+      <c r="AF46" s="28"/>
+      <c r="AG46" s="28"/>
+      <c r="AH46" s="28"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="28" t="s">
-        <v>474</v>
-      </c>
-      <c r="B47" s="29"/>
-      <c r="C47" s="31">
+      <c r="A47" s="29" t="s">
+        <v>475</v>
+      </c>
+      <c r="B47" s="30"/>
+      <c r="C47" s="32">
         <v>6.96</v>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="32">
         <v>10.58</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="32">
         <v>22.76</v>
       </c>
-      <c r="F47" s="29"/>
-      <c r="G47" s="31">
+      <c r="F47" s="30"/>
+      <c r="G47" s="32">
         <v>55.11</v>
       </c>
-      <c r="H47" s="31">
+      <c r="H47" s="32">
         <v>12.51</v>
       </c>
-      <c r="I47" s="29"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="31">
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="32">
         <v>10.34</v>
       </c>
-      <c r="L47" s="31">
+      <c r="L47" s="32">
         <v>5.24</v>
       </c>
-      <c r="M47" s="31">
+      <c r="M47" s="32">
         <v>3.36</v>
       </c>
-      <c r="N47" s="31">
+      <c r="N47" s="32">
         <v>47.29</v>
       </c>
-      <c r="O47" s="31">
+      <c r="O47" s="32">
         <v>4.16</v>
       </c>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="29"/>
-      <c r="R47" s="29"/>
-      <c r="S47" s="30">
+      <c r="P47" s="30"/>
+      <c r="Q47" s="30"/>
+      <c r="R47" s="30"/>
+      <c r="S47" s="31">
         <v>162.86</v>
       </c>
-      <c r="T47" s="31">
+      <c r="T47" s="32">
         <v>8.2</v>
       </c>
-      <c r="U47" s="29"/>
-      <c r="V47" s="29"/>
-      <c r="W47" s="31">
+      <c r="U47" s="30"/>
+      <c r="V47" s="30"/>
+      <c r="W47" s="32">
         <v>25.94</v>
       </c>
-      <c r="X47" s="31">
+      <c r="X47" s="32">
         <v>17.22</v>
       </c>
-      <c r="Y47" s="31">
+      <c r="Y47" s="32">
         <v>4.51</v>
       </c>
-      <c r="Z47" s="31">
+      <c r="Z47" s="32">
         <v>7.61</v>
       </c>
-      <c r="AA47" s="29"/>
-      <c r="AB47" s="29"/>
-      <c r="AC47" s="29"/>
-      <c r="AD47" s="29"/>
-      <c r="AE47" s="31">
+      <c r="AA47" s="30"/>
+      <c r="AB47" s="30"/>
+      <c r="AC47" s="30"/>
+      <c r="AD47" s="30"/>
+      <c r="AE47" s="32">
         <v>4.89</v>
       </c>
-      <c r="AF47" s="29"/>
-      <c r="AG47" s="31">
+      <c r="AF47" s="30"/>
+      <c r="AG47" s="32">
         <v>8.11</v>
       </c>
-      <c r="AH47" s="31">
+      <c r="AH47" s="32">
         <v>3.46</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>475</v>
-      </c>
-      <c r="B48" s="31">
+      <c r="A48" s="29" t="s">
+        <v>476</v>
+      </c>
+      <c r="B48" s="32">
         <v>25.25</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="32">
         <v>13.81</v>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="32">
         <v>20.59</v>
       </c>
-      <c r="E48" s="30">
+      <c r="E48" s="31">
         <v>260.28</v>
       </c>
-      <c r="F48" s="29"/>
-      <c r="G48" s="30">
+      <c r="F48" s="30"/>
+      <c r="G48" s="31">
         <v>115.02</v>
       </c>
-      <c r="H48" s="31">
+      <c r="H48" s="32">
         <v>26.05</v>
       </c>
-      <c r="I48" s="31">
+      <c r="I48" s="32">
         <v>13.35</v>
       </c>
-      <c r="J48" s="31">
+      <c r="J48" s="32">
         <v>9.46</v>
       </c>
-      <c r="K48" s="31">
+      <c r="K48" s="32">
         <v>6.15</v>
       </c>
-      <c r="L48" s="31">
+      <c r="L48" s="32">
         <v>6.17</v>
       </c>
-      <c r="M48" s="31">
+      <c r="M48" s="32">
         <v>28.86</v>
       </c>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="31">
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="30"/>
+      <c r="S48" s="32">
         <v>38.83</v>
       </c>
-      <c r="T48" s="31">
+      <c r="T48" s="32">
         <v>34.0</v>
       </c>
-      <c r="U48" s="30">
+      <c r="U48" s="31">
         <v>222.24</v>
       </c>
-      <c r="V48" s="31">
+      <c r="V48" s="32">
         <v>34.38</v>
       </c>
-      <c r="W48" s="30">
+      <c r="W48" s="31">
         <v>105.79</v>
       </c>
-      <c r="X48" s="29"/>
-      <c r="Y48" s="29"/>
-      <c r="Z48" s="29"/>
-      <c r="AA48" s="29"/>
-      <c r="AB48" s="29"/>
-      <c r="AC48" s="29"/>
-      <c r="AD48" s="31">
+      <c r="X48" s="30"/>
+      <c r="Y48" s="30"/>
+      <c r="Z48" s="30"/>
+      <c r="AA48" s="30"/>
+      <c r="AB48" s="30"/>
+      <c r="AC48" s="30"/>
+      <c r="AD48" s="32">
         <v>26.61</v>
       </c>
-      <c r="AE48" s="29"/>
-      <c r="AF48" s="29"/>
-      <c r="AG48" s="29"/>
-      <c r="AH48" s="29"/>
+      <c r="AE48" s="30"/>
+      <c r="AF48" s="30"/>
+      <c r="AG48" s="30"/>
+      <c r="AH48" s="30"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="26" t="s">
-        <v>476</v>
-      </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
-      <c r="Q49" s="27"/>
-      <c r="R49" s="27"/>
-      <c r="S49" s="27"/>
-      <c r="T49" s="27"/>
-      <c r="U49" s="27"/>
-      <c r="V49" s="27"/>
-      <c r="W49" s="27"/>
-      <c r="X49" s="27"/>
-      <c r="Y49" s="27"/>
-      <c r="Z49" s="27"/>
-      <c r="AA49" s="27"/>
-      <c r="AB49" s="27"/>
-      <c r="AC49" s="27"/>
-      <c r="AD49" s="27"/>
-      <c r="AE49" s="27"/>
-      <c r="AF49" s="27"/>
-      <c r="AG49" s="27"/>
-      <c r="AH49" s="27"/>
+      <c r="A49" s="27" t="s">
+        <v>477</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="28"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="28"/>
+      <c r="X49" s="28"/>
+      <c r="Y49" s="28"/>
+      <c r="Z49" s="28"/>
+      <c r="AA49" s="28"/>
+      <c r="AB49" s="28"/>
+      <c r="AC49" s="28"/>
+      <c r="AD49" s="28"/>
+      <c r="AE49" s="28"/>
+      <c r="AF49" s="28"/>
+      <c r="AG49" s="28"/>
+      <c r="AH49" s="28"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="B50" s="31">
+      <c r="A50" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="B50" s="32">
         <v>14.13</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="32">
         <v>10.98</v>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="32">
         <v>14.96</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="32">
         <v>16.15</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="32">
         <v>17.14</v>
       </c>
-      <c r="G50" s="31">
+      <c r="G50" s="32">
         <v>49.31</v>
       </c>
-      <c r="H50" s="31">
+      <c r="H50" s="32">
         <v>23.66</v>
       </c>
-      <c r="I50" s="31">
+      <c r="I50" s="32">
         <v>7.47</v>
       </c>
-      <c r="J50" s="31">
+      <c r="J50" s="32">
         <v>13.69</v>
       </c>
-      <c r="K50" s="31">
+      <c r="K50" s="32">
         <v>32.05</v>
       </c>
-      <c r="L50" s="30">
+      <c r="L50" s="31">
         <v>202.9</v>
       </c>
-      <c r="M50" s="31">
+      <c r="M50" s="32">
         <v>3.15</v>
       </c>
-      <c r="N50" s="31">
+      <c r="N50" s="32">
         <v>2.52</v>
       </c>
-      <c r="O50" s="31">
+      <c r="O50" s="32">
         <v>2.1</v>
       </c>
-      <c r="P50" s="31">
+      <c r="P50" s="32">
         <v>4.32</v>
       </c>
-      <c r="Q50" s="31">
+      <c r="Q50" s="32">
         <v>6.32</v>
       </c>
-      <c r="R50" s="31">
+      <c r="R50" s="32">
         <v>5.43</v>
       </c>
-      <c r="S50" s="31">
+      <c r="S50" s="32">
         <v>1.48</v>
       </c>
-      <c r="T50" s="31">
+      <c r="T50" s="32">
         <v>4.6</v>
       </c>
-      <c r="U50" s="31">
+      <c r="U50" s="32">
         <v>6.59</v>
       </c>
-      <c r="V50" s="31">
+      <c r="V50" s="32">
         <v>5.77</v>
       </c>
-      <c r="W50" s="31">
+      <c r="W50" s="32">
         <v>3.96</v>
       </c>
-      <c r="X50" s="31">
+      <c r="X50" s="32">
         <v>3.35</v>
       </c>
-      <c r="Y50" s="31">
+      <c r="Y50" s="32">
         <v>7.29</v>
       </c>
-      <c r="Z50" s="31">
+      <c r="Z50" s="32">
         <v>5.75</v>
       </c>
-      <c r="AA50" s="31">
+      <c r="AA50" s="32">
         <v>12.29</v>
       </c>
-      <c r="AB50" s="31">
+      <c r="AB50" s="32">
         <v>0.36</v>
       </c>
-      <c r="AC50" s="31">
+      <c r="AC50" s="32">
         <v>2.25</v>
       </c>
-      <c r="AD50" s="31">
+      <c r="AD50" s="32">
         <v>4.34</v>
       </c>
-      <c r="AE50" s="31">
+      <c r="AE50" s="32">
         <v>3.8</v>
       </c>
-      <c r="AF50" s="31">
+      <c r="AF50" s="32">
         <v>3.01</v>
       </c>
-      <c r="AG50" s="31">
+      <c r="AG50" s="32">
         <v>1.72</v>
       </c>
-      <c r="AH50" s="31">
+      <c r="AH50" s="32">
         <v>2.95</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>478</v>
-      </c>
-      <c r="B51" s="31">
+      <c r="A51" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="B51" s="32">
         <v>13.98</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="32">
         <v>15.38</v>
       </c>
-      <c r="D51" s="31">
+      <c r="D51" s="32">
         <v>18.49</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="32">
         <v>18.54</v>
       </c>
-      <c r="F51" s="31">
+      <c r="F51" s="32">
         <v>18.02</v>
       </c>
-      <c r="G51" s="31">
+      <c r="G51" s="32">
         <v>20.33</v>
       </c>
-      <c r="H51" s="31">
+      <c r="H51" s="32">
         <v>19.73</v>
       </c>
-      <c r="I51" s="31">
+      <c r="I51" s="32">
         <v>10.31</v>
       </c>
-      <c r="J51" s="31">
+      <c r="J51" s="32">
         <v>7.54</v>
       </c>
-      <c r="K51" s="31">
+      <c r="K51" s="32">
         <v>5.1</v>
       </c>
-      <c r="L51" s="31">
+      <c r="L51" s="32">
         <v>3.81</v>
       </c>
-      <c r="M51" s="31">
+      <c r="M51" s="32">
         <v>3.23</v>
       </c>
-      <c r="N51" s="31">
+      <c r="N51" s="32">
         <v>3.6</v>
       </c>
-      <c r="O51" s="31">
+      <c r="O51" s="32">
         <v>3.48</v>
       </c>
-      <c r="P51" s="31">
+      <c r="P51" s="32">
         <v>4.25</v>
       </c>
-      <c r="Q51" s="31">
+      <c r="Q51" s="32">
         <v>4.75</v>
       </c>
-      <c r="R51" s="31">
+      <c r="R51" s="32">
         <v>4.68</v>
       </c>
-      <c r="S51" s="31">
+      <c r="S51" s="32">
         <v>4.48</v>
       </c>
-      <c r="T51" s="31">
+      <c r="T51" s="32">
         <v>5.08</v>
       </c>
-      <c r="U51" s="31">
+      <c r="U51" s="32">
         <v>5.42</v>
       </c>
-      <c r="V51" s="31">
+      <c r="V51" s="32">
         <v>4.88</v>
       </c>
-      <c r="W51" s="31">
+      <c r="W51" s="32">
         <v>6.24</v>
       </c>
-      <c r="X51" s="31">
+      <c r="X51" s="32">
         <v>2.29</v>
       </c>
-      <c r="Y51" s="31">
+      <c r="Y51" s="32">
         <v>2.18</v>
       </c>
-      <c r="Z51" s="31">
+      <c r="Z51" s="32">
         <v>2.19</v>
       </c>
-      <c r="AA51" s="31">
+      <c r="AA51" s="32">
         <v>2.08</v>
       </c>
-      <c r="AB51" s="31">
+      <c r="AB51" s="32">
         <v>1.2</v>
       </c>
-      <c r="AC51" s="31">
+      <c r="AC51" s="32">
         <v>2.8</v>
       </c>
-      <c r="AD51" s="31">
+      <c r="AD51" s="32">
         <v>2.99</v>
       </c>
-      <c r="AE51" s="29"/>
-      <c r="AF51" s="29"/>
-      <c r="AG51" s="29"/>
-      <c r="AH51" s="29"/>
+      <c r="AE51" s="30"/>
+      <c r="AF51" s="30"/>
+      <c r="AG51" s="30"/>
+      <c r="AH51" s="30"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="26" t="s">
-        <v>479</v>
-      </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
-      <c r="N52" s="27"/>
-      <c r="O52" s="27"/>
-      <c r="P52" s="27"/>
-      <c r="Q52" s="27"/>
-      <c r="R52" s="27"/>
-      <c r="S52" s="27"/>
-      <c r="T52" s="27"/>
-      <c r="U52" s="27"/>
-      <c r="V52" s="27"/>
-      <c r="W52" s="27"/>
-      <c r="X52" s="27"/>
-      <c r="Y52" s="27"/>
-      <c r="Z52" s="27"/>
-      <c r="AA52" s="27"/>
-      <c r="AB52" s="27"/>
-      <c r="AC52" s="27"/>
-      <c r="AD52" s="27"/>
-      <c r="AE52" s="27"/>
-      <c r="AF52" s="27"/>
-      <c r="AG52" s="27"/>
-      <c r="AH52" s="27"/>
+      <c r="A52" s="27" t="s">
+        <v>480</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="28"/>
+      <c r="T52" s="28"/>
+      <c r="U52" s="28"/>
+      <c r="V52" s="28"/>
+      <c r="W52" s="28"/>
+      <c r="X52" s="28"/>
+      <c r="Y52" s="28"/>
+      <c r="Z52" s="28"/>
+      <c r="AA52" s="28"/>
+      <c r="AB52" s="28"/>
+      <c r="AC52" s="28"/>
+      <c r="AD52" s="28"/>
+      <c r="AE52" s="28"/>
+      <c r="AF52" s="28"/>
+      <c r="AG52" s="28"/>
+      <c r="AH52" s="28"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="28" t="s">
-        <v>480</v>
-      </c>
-      <c r="B53" s="31">
+      <c r="A53" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="B53" s="32">
         <v>21.72</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="32">
         <v>16.5</v>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="32">
         <v>28.97</v>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="32">
         <v>48.79</v>
       </c>
-      <c r="F53" s="30">
+      <c r="F53" s="31">
         <v>480.02</v>
       </c>
-      <c r="G53" s="29"/>
-      <c r="H53" s="29"/>
-      <c r="I53" s="29"/>
-      <c r="J53" s="29"/>
-      <c r="K53" s="29"/>
-      <c r="L53" s="29"/>
-      <c r="M53" s="31">
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="32">
         <v>13.45</v>
       </c>
-      <c r="N53" s="31">
+      <c r="N53" s="32">
         <v>12.02</v>
       </c>
-      <c r="O53" s="31">
+      <c r="O53" s="32">
         <v>11.77</v>
       </c>
-      <c r="P53" s="30">
+      <c r="P53" s="31">
         <v>302.75</v>
       </c>
-      <c r="Q53" s="31">
+      <c r="Q53" s="32">
         <v>12.59</v>
       </c>
-      <c r="R53" s="31">
+      <c r="R53" s="32">
         <v>13.66</v>
       </c>
-      <c r="S53" s="31">
+      <c r="S53" s="32">
         <v>2.96</v>
       </c>
-      <c r="T53" s="31">
+      <c r="T53" s="32">
         <v>6.4</v>
       </c>
-      <c r="U53" s="31">
+      <c r="U53" s="32">
         <v>9.62</v>
       </c>
-      <c r="V53" s="31">
+      <c r="V53" s="32">
         <v>9.44</v>
       </c>
-      <c r="W53" s="31">
+      <c r="W53" s="32">
         <v>9.02</v>
       </c>
-      <c r="X53" s="31">
+      <c r="X53" s="32">
         <v>14.66</v>
       </c>
-      <c r="Y53" s="29"/>
-      <c r="Z53" s="29"/>
-      <c r="AA53" s="29"/>
-      <c r="AB53" s="31">
+      <c r="Y53" s="30"/>
+      <c r="Z53" s="30"/>
+      <c r="AA53" s="30"/>
+      <c r="AB53" s="32">
         <v>0.44</v>
       </c>
-      <c r="AC53" s="31">
+      <c r="AC53" s="32">
         <v>3.95</v>
       </c>
-      <c r="AD53" s="31">
+      <c r="AD53" s="32">
         <v>9.45</v>
       </c>
-      <c r="AE53" s="31">
+      <c r="AE53" s="32">
         <v>11.29</v>
       </c>
-      <c r="AF53" s="31">
+      <c r="AF53" s="32">
         <v>23.21</v>
       </c>
-      <c r="AG53" s="31">
+      <c r="AG53" s="32">
         <v>3.22</v>
       </c>
-      <c r="AH53" s="31">
+      <c r="AH53" s="32">
         <v>14.16</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="28" t="s">
-        <v>481</v>
-      </c>
-      <c r="B54" s="31">
+      <c r="A54" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="B54" s="32">
         <v>26.41</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="32">
         <v>50.98</v>
       </c>
-      <c r="D54" s="29"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="29"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
-      <c r="I54" s="29"/>
-      <c r="J54" s="30">
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="31">
         <v>287.76</v>
       </c>
-      <c r="K54" s="31">
+      <c r="K54" s="32">
         <v>62.89</v>
       </c>
-      <c r="L54" s="31">
+      <c r="L54" s="32">
         <v>35.2</v>
       </c>
-      <c r="M54" s="31">
+      <c r="M54" s="32">
         <v>14.6</v>
       </c>
-      <c r="N54" s="31">
+      <c r="N54" s="32">
         <v>14.69</v>
       </c>
-      <c r="O54" s="31">
+      <c r="O54" s="32">
         <v>11.05</v>
       </c>
-      <c r="P54" s="31">
+      <c r="P54" s="32">
         <v>8.79</v>
       </c>
-      <c r="Q54" s="31">
+      <c r="Q54" s="32">
         <v>8.09</v>
       </c>
-      <c r="R54" s="31">
+      <c r="R54" s="32">
         <v>7.78</v>
       </c>
-      <c r="S54" s="31">
+      <c r="S54" s="32">
         <v>7.29</v>
       </c>
-      <c r="T54" s="31">
+      <c r="T54" s="32">
         <v>8.45</v>
       </c>
-      <c r="U54" s="31">
+      <c r="U54" s="32">
         <v>23.77</v>
       </c>
-      <c r="V54" s="29"/>
-      <c r="W54" s="29"/>
-      <c r="X54" s="31">
+      <c r="V54" s="30"/>
+      <c r="W54" s="30"/>
+      <c r="X54" s="32">
         <v>8.16</v>
       </c>
-      <c r="Y54" s="31">
+      <c r="Y54" s="32">
         <v>6.88</v>
       </c>
-      <c r="Z54" s="31">
+      <c r="Z54" s="32">
         <v>4.27</v>
       </c>
-      <c r="AA54" s="31">
+      <c r="AA54" s="32">
         <v>3.86</v>
       </c>
-      <c r="AB54" s="31">
+      <c r="AB54" s="32">
         <v>1.72</v>
       </c>
-      <c r="AC54" s="31">
+      <c r="AC54" s="32">
         <v>6.25</v>
       </c>
-      <c r="AD54" s="31">
+      <c r="AD54" s="32">
         <v>7.98</v>
       </c>
-      <c r="AE54" s="29"/>
-      <c r="AF54" s="29"/>
-      <c r="AG54" s="29"/>
-      <c r="AH54" s="29"/>
+      <c r="AE54" s="30"/>
+      <c r="AF54" s="30"/>
+      <c r="AG54" s="30"/>
+      <c r="AH54" s="30"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="26" t="s">
-        <v>482</v>
-      </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
-      <c r="N55" s="27"/>
-      <c r="O55" s="27"/>
-      <c r="P55" s="27"/>
-      <c r="Q55" s="27"/>
-      <c r="R55" s="27"/>
-      <c r="S55" s="27"/>
-      <c r="T55" s="27"/>
-      <c r="U55" s="27"/>
-      <c r="V55" s="27"/>
-      <c r="W55" s="27"/>
-      <c r="X55" s="27"/>
-      <c r="Y55" s="27"/>
-      <c r="Z55" s="27"/>
-      <c r="AA55" s="27"/>
-      <c r="AB55" s="27"/>
-      <c r="AC55" s="27"/>
-      <c r="AD55" s="27"/>
-      <c r="AE55" s="27"/>
-      <c r="AF55" s="27"/>
-      <c r="AG55" s="27"/>
-      <c r="AH55" s="27"/>
+      <c r="A55" s="27" t="s">
+        <v>483</v>
+      </c>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="28"/>
+      <c r="N55" s="28"/>
+      <c r="O55" s="28"/>
+      <c r="P55" s="28"/>
+      <c r="Q55" s="28"/>
+      <c r="R55" s="28"/>
+      <c r="S55" s="28"/>
+      <c r="T55" s="28"/>
+      <c r="U55" s="28"/>
+      <c r="V55" s="28"/>
+      <c r="W55" s="28"/>
+      <c r="X55" s="28"/>
+      <c r="Y55" s="28"/>
+      <c r="Z55" s="28"/>
+      <c r="AA55" s="28"/>
+      <c r="AB55" s="28"/>
+      <c r="AC55" s="28"/>
+      <c r="AD55" s="28"/>
+      <c r="AE55" s="28"/>
+      <c r="AF55" s="28"/>
+      <c r="AG55" s="28"/>
+      <c r="AH55" s="28"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="28" t="s">
-        <v>483</v>
-      </c>
-      <c r="B56" s="31">
+      <c r="A56" s="29" t="s">
+        <v>484</v>
+      </c>
+      <c r="B56" s="32">
         <v>26.19</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="32">
         <v>15.86</v>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="32">
         <v>25.17</v>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="32">
         <v>47.86</v>
       </c>
-      <c r="F56" s="30">
+      <c r="F56" s="31">
         <v>200.46</v>
       </c>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29"/>
-      <c r="I56" s="29"/>
-      <c r="J56" s="31">
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="32">
         <v>24.08</v>
       </c>
-      <c r="K56" s="31">
+      <c r="K56" s="32">
         <v>21.7</v>
       </c>
-      <c r="L56" s="30">
+      <c r="L56" s="31">
         <v>202.9</v>
       </c>
-      <c r="M56" s="31">
+      <c r="M56" s="32">
         <v>9.5</v>
       </c>
-      <c r="N56" s="31">
+      <c r="N56" s="32">
         <v>10.89</v>
       </c>
-      <c r="O56" s="31">
+      <c r="O56" s="32">
         <v>10.67</v>
       </c>
-      <c r="P56" s="31">
+      <c r="P56" s="32">
         <v>14.53</v>
       </c>
-      <c r="Q56" s="31">
+      <c r="Q56" s="32">
         <v>17.38</v>
       </c>
-      <c r="R56" s="31">
+      <c r="R56" s="32">
         <v>13.66</v>
       </c>
-      <c r="S56" s="31">
+      <c r="S56" s="32">
         <v>2.96</v>
       </c>
-      <c r="T56" s="31">
+      <c r="T56" s="32">
         <v>6.4</v>
       </c>
-      <c r="U56" s="31">
+      <c r="U56" s="32">
         <v>8.96</v>
       </c>
-      <c r="V56" s="31">
+      <c r="V56" s="32">
         <v>9.28</v>
       </c>
-      <c r="W56" s="31">
+      <c r="W56" s="32">
         <v>9.02</v>
       </c>
-      <c r="X56" s="31">
+      <c r="X56" s="32">
         <v>8.96</v>
       </c>
-      <c r="Y56" s="29"/>
-      <c r="Z56" s="29"/>
-      <c r="AA56" s="29"/>
-      <c r="AB56" s="29"/>
-      <c r="AC56" s="31">
+      <c r="Y56" s="30"/>
+      <c r="Z56" s="30"/>
+      <c r="AA56" s="30"/>
+      <c r="AB56" s="30"/>
+      <c r="AC56" s="32">
         <v>11.99</v>
       </c>
-      <c r="AD56" s="31">
+      <c r="AD56" s="32">
         <v>21.52</v>
       </c>
-      <c r="AE56" s="31">
+      <c r="AE56" s="32">
         <v>17.38</v>
       </c>
-      <c r="AF56" s="31">
+      <c r="AF56" s="32">
         <v>7.49</v>
       </c>
-      <c r="AG56" s="29"/>
-      <c r="AH56" s="31">
+      <c r="AG56" s="30"/>
+      <c r="AH56" s="32">
         <v>16.74</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="28" t="s">
-        <v>484</v>
-      </c>
-      <c r="B57" s="31">
+      <c r="A57" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="B57" s="32">
         <v>2.34</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="32">
         <v>2.09</v>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="32">
         <v>1.85</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="32">
         <v>1.42</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F57" s="32">
         <v>1.22</v>
       </c>
-      <c r="G57" s="31">
+      <c r="G57" s="32">
         <v>1.02</v>
       </c>
-      <c r="H57" s="31">
+      <c r="H57" s="32">
         <v>0.84</v>
       </c>
-      <c r="I57" s="31">
+      <c r="I57" s="32">
         <v>0.79</v>
       </c>
-      <c r="J57" s="31">
+      <c r="J57" s="32">
         <v>0.8</v>
       </c>
-      <c r="K57" s="31">
+      <c r="K57" s="32">
         <v>0.63</v>
       </c>
-      <c r="L57" s="31">
+      <c r="L57" s="32">
         <v>0.56</v>
       </c>
-      <c r="M57" s="31">
+      <c r="M57" s="32">
         <v>0.57</v>
       </c>
-      <c r="N57" s="31">
+      <c r="N57" s="32">
         <v>0.61</v>
       </c>
-      <c r="O57" s="31">
+      <c r="O57" s="32">
         <v>0.58</v>
       </c>
-      <c r="P57" s="31">
+      <c r="P57" s="32">
         <v>0.81</v>
       </c>
-      <c r="Q57" s="31">
+      <c r="Q57" s="32">
         <v>1.07</v>
       </c>
-      <c r="R57" s="31">
+      <c r="R57" s="32">
         <v>1.16</v>
       </c>
-      <c r="S57" s="31">
+      <c r="S57" s="32">
         <v>1.15</v>
       </c>
-      <c r="T57" s="31">
+      <c r="T57" s="32">
         <v>1.2</v>
       </c>
-      <c r="U57" s="31">
+      <c r="U57" s="32">
         <v>0.91</v>
       </c>
-      <c r="V57" s="31">
+      <c r="V57" s="32">
         <v>0.56</v>
       </c>
-      <c r="W57" s="31">
+      <c r="W57" s="32">
         <v>0.59</v>
       </c>
-      <c r="X57" s="31">
+      <c r="X57" s="32">
         <v>0.53</v>
       </c>
-      <c r="Y57" s="31">
+      <c r="Y57" s="32">
         <v>0.55</v>
       </c>
-      <c r="Z57" s="31">
+      <c r="Z57" s="32">
         <v>0.63</v>
       </c>
-      <c r="AA57" s="31">
+      <c r="AA57" s="32">
         <v>0.7</v>
       </c>
-      <c r="AB57" s="31">
+      <c r="AB57" s="32">
         <v>0.48</v>
       </c>
-      <c r="AC57" s="31">
+      <c r="AC57" s="32">
         <v>0.52</v>
       </c>
-      <c r="AD57" s="31">
+      <c r="AD57" s="32">
         <v>0.51</v>
       </c>
-      <c r="AE57" s="29"/>
-      <c r="AF57" s="29"/>
-      <c r="AG57" s="29"/>
-      <c r="AH57" s="29"/>
+      <c r="AE57" s="30"/>
+      <c r="AF57" s="30"/>
+      <c r="AG57" s="30"/>
+      <c r="AH57" s="30"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="26" t="s">
-        <v>485</v>
-      </c>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="27"/>
-      <c r="L58" s="27"/>
-      <c r="M58" s="27"/>
-      <c r="N58" s="27"/>
-      <c r="O58" s="27"/>
-      <c r="P58" s="27"/>
-      <c r="Q58" s="27"/>
-      <c r="R58" s="27"/>
-      <c r="S58" s="27"/>
-      <c r="T58" s="27"/>
-      <c r="U58" s="27"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="27"/>
-      <c r="X58" s="27"/>
-      <c r="Y58" s="27"/>
-      <c r="Z58" s="27"/>
-      <c r="AA58" s="27"/>
-      <c r="AB58" s="27"/>
-      <c r="AC58" s="27"/>
-      <c r="AD58" s="27"/>
-      <c r="AE58" s="27"/>
-      <c r="AF58" s="27"/>
-      <c r="AG58" s="27"/>
-      <c r="AH58" s="27"/>
+      <c r="A58" s="27" t="s">
+        <v>486</v>
+      </c>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
+      <c r="N58" s="28"/>
+      <c r="O58" s="28"/>
+      <c r="P58" s="28"/>
+      <c r="Q58" s="28"/>
+      <c r="R58" s="28"/>
+      <c r="S58" s="28"/>
+      <c r="T58" s="28"/>
+      <c r="U58" s="28"/>
+      <c r="V58" s="28"/>
+      <c r="W58" s="28"/>
+      <c r="X58" s="28"/>
+      <c r="Y58" s="28"/>
+      <c r="Z58" s="28"/>
+      <c r="AA58" s="28"/>
+      <c r="AB58" s="28"/>
+      <c r="AC58" s="28"/>
+      <c r="AD58" s="28"/>
+      <c r="AE58" s="28"/>
+      <c r="AF58" s="28"/>
+      <c r="AG58" s="28"/>
+      <c r="AH58" s="28"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="28" t="s">
-        <v>486</v>
-      </c>
-      <c r="B59" s="31">
+      <c r="A59" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="B59" s="32">
         <v>1.23</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C59" s="32">
         <v>0.17</v>
       </c>
-      <c r="D59" s="31">
+      <c r="D59" s="32">
         <v>0.25</v>
       </c>
-      <c r="E59" s="31">
+      <c r="E59" s="32">
         <v>0.04</v>
       </c>
-      <c r="F59" s="31">
+      <c r="F59" s="32">
         <v>4.65</v>
       </c>
-      <c r="G59" s="29"/>
-      <c r="H59" s="29"/>
-      <c r="I59" s="29"/>
-      <c r="J59" s="29"/>
-      <c r="K59" s="29"/>
-      <c r="L59" s="29"/>
-      <c r="M59" s="31">
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="32">
         <v>1.24</v>
       </c>
-      <c r="N59" s="31">
+      <c r="N59" s="32">
         <v>0.42</v>
       </c>
-      <c r="O59" s="29">
+      <c r="O59" s="30">
         <v>0.0</v>
       </c>
-      <c r="P59" s="34">
+      <c r="P59" s="35">
         <v>-3.11</v>
       </c>
-      <c r="Q59" s="31">
+      <c r="Q59" s="32">
         <v>1.18</v>
       </c>
-      <c r="R59" s="34">
+      <c r="R59" s="35">
         <v>-0.34</v>
       </c>
-      <c r="S59" s="34">
+      <c r="S59" s="35">
         <v>-0.06</v>
       </c>
-      <c r="T59" s="31">
+      <c r="T59" s="32">
         <v>0.17</v>
       </c>
-      <c r="U59" s="31">
+      <c r="U59" s="32">
         <v>0.14</v>
       </c>
-      <c r="V59" s="31">
+      <c r="V59" s="32">
         <v>0.13</v>
       </c>
-      <c r="W59" s="31">
+      <c r="W59" s="32">
         <v>0.06</v>
       </c>
-      <c r="X59" s="31">
+      <c r="X59" s="32">
         <v>0.13</v>
       </c>
-      <c r="Y59" s="29"/>
-      <c r="Z59" s="29"/>
-      <c r="AA59" s="29"/>
-      <c r="AB59" s="29">
+      <c r="Y59" s="30"/>
+      <c r="Z59" s="30"/>
+      <c r="AA59" s="30"/>
+      <c r="AB59" s="30">
         <v>0.0</v>
       </c>
-      <c r="AC59" s="31">
+      <c r="AC59" s="32">
         <v>0.05</v>
       </c>
-      <c r="AD59" s="31">
+      <c r="AD59" s="32">
         <v>0.11</v>
       </c>
-      <c r="AE59" s="31">
+      <c r="AE59" s="32">
         <v>0.07</v>
       </c>
-      <c r="AF59" s="34">
+      <c r="AF59" s="35">
         <v>-0.26</v>
       </c>
-      <c r="AG59" s="31">
+      <c r="AG59" s="32">
         <v>0.01</v>
       </c>
-      <c r="AH59" s="29"/>
+      <c r="AH59" s="30"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="28" t="s">
-        <v>487</v>
-      </c>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
-      <c r="K60" s="29"/>
-      <c r="L60" s="29"/>
-      <c r="M60" s="31">
+      <c r="A60" s="29" t="s">
+        <v>488</v>
+      </c>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
+      <c r="M60" s="32">
         <v>4.95</v>
       </c>
-      <c r="N60" s="34">
+      <c r="N60" s="35">
         <v>-1.63</v>
       </c>
-      <c r="O60" s="34">
+      <c r="O60" s="35">
         <v>-0.45</v>
       </c>
-      <c r="P60" s="34">
+      <c r="P60" s="35">
         <v>-0.15</v>
       </c>
-      <c r="Q60" s="34">
+      <c r="Q60" s="35">
         <v>-1.6</v>
       </c>
-      <c r="R60" s="31">
+      <c r="R60" s="32">
         <v>2.06</v>
       </c>
-      <c r="S60" s="31">
+      <c r="S60" s="32">
         <v>0.2</v>
       </c>
-      <c r="T60" s="29"/>
-      <c r="U60" s="29"/>
-      <c r="V60" s="29"/>
-      <c r="W60" s="29"/>
-      <c r="X60" s="34">
+      <c r="T60" s="30"/>
+      <c r="U60" s="30"/>
+      <c r="V60" s="30"/>
+      <c r="W60" s="30"/>
+      <c r="X60" s="35">
         <v>-0.44</v>
       </c>
-      <c r="Y60" s="29"/>
-      <c r="Z60" s="29"/>
-      <c r="AA60" s="29"/>
-      <c r="AB60" s="31">
+      <c r="Y60" s="30"/>
+      <c r="Z60" s="30"/>
+      <c r="AA60" s="30"/>
+      <c r="AB60" s="32">
         <v>0.03</v>
       </c>
-      <c r="AC60" s="31">
+      <c r="AC60" s="32">
         <v>0.16</v>
       </c>
-      <c r="AD60" s="29"/>
-      <c r="AE60" s="29"/>
-      <c r="AF60" s="29"/>
-      <c r="AG60" s="29"/>
-      <c r="AH60" s="29"/>
+      <c r="AD60" s="30"/>
+      <c r="AE60" s="30"/>
+      <c r="AF60" s="30"/>
+      <c r="AG60" s="30"/>
+      <c r="AH60" s="30"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="26" t="s">
-        <v>488</v>
-      </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="27"/>
-      <c r="Q61" s="27"/>
-      <c r="R61" s="27"/>
-      <c r="S61" s="27"/>
-      <c r="T61" s="27"/>
-      <c r="U61" s="27"/>
-      <c r="V61" s="27"/>
-      <c r="W61" s="27"/>
-      <c r="X61" s="27"/>
-      <c r="Y61" s="27"/>
-      <c r="Z61" s="27"/>
-      <c r="AA61" s="27"/>
-      <c r="AB61" s="27"/>
-      <c r="AC61" s="27"/>
-      <c r="AD61" s="27"/>
-      <c r="AE61" s="27"/>
-      <c r="AF61" s="27"/>
-      <c r="AG61" s="27"/>
-      <c r="AH61" s="27"/>
+      <c r="A61" s="27" t="s">
+        <v>489</v>
+      </c>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="28"/>
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="28"/>
+      <c r="N61" s="28"/>
+      <c r="O61" s="28"/>
+      <c r="P61" s="28"/>
+      <c r="Q61" s="28"/>
+      <c r="R61" s="28"/>
+      <c r="S61" s="28"/>
+      <c r="T61" s="28"/>
+      <c r="U61" s="28"/>
+      <c r="V61" s="28"/>
+      <c r="W61" s="28"/>
+      <c r="X61" s="28"/>
+      <c r="Y61" s="28"/>
+      <c r="Z61" s="28"/>
+      <c r="AA61" s="28"/>
+      <c r="AB61" s="28"/>
+      <c r="AC61" s="28"/>
+      <c r="AD61" s="28"/>
+      <c r="AE61" s="28"/>
+      <c r="AF61" s="28"/>
+      <c r="AG61" s="28"/>
+      <c r="AH61" s="28"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="28" t="s">
-        <v>489</v>
-      </c>
-      <c r="B62" s="31">
+      <c r="A62" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="B62" s="32">
         <v>1.34</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="32">
         <v>0.75</v>
       </c>
-      <c r="D62" s="31">
+      <c r="D62" s="32">
         <v>1.04</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="32">
         <v>1.06</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F62" s="32">
         <v>1.01</v>
       </c>
-      <c r="G62" s="31">
+      <c r="G62" s="32">
         <v>1.05</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H62" s="32">
         <v>0.62</v>
       </c>
-      <c r="I62" s="31">
+      <c r="I62" s="32">
         <v>0.38</v>
       </c>
-      <c r="J62" s="31">
+      <c r="J62" s="32">
         <v>0.9</v>
       </c>
-      <c r="K62" s="31">
+      <c r="K62" s="32">
         <v>0.79</v>
       </c>
-      <c r="L62" s="31">
+      <c r="L62" s="32">
         <v>0.52</v>
       </c>
-      <c r="M62" s="31">
+      <c r="M62" s="32">
         <v>0.31</v>
       </c>
-      <c r="N62" s="31">
+      <c r="N62" s="32">
         <v>0.33</v>
       </c>
-      <c r="O62" s="31">
+      <c r="O62" s="32">
         <v>0.28</v>
       </c>
-      <c r="P62" s="31">
+      <c r="P62" s="32">
         <v>0.43</v>
       </c>
-      <c r="Q62" s="31">
+      <c r="Q62" s="32">
         <v>0.52</v>
       </c>
-      <c r="R62" s="31">
+      <c r="R62" s="32">
         <v>0.51</v>
       </c>
-      <c r="S62" s="31">
+      <c r="S62" s="32">
         <v>0.24</v>
       </c>
-      <c r="T62" s="31">
+      <c r="T62" s="32">
         <v>0.53</v>
       </c>
-      <c r="U62" s="31">
+      <c r="U62" s="32">
         <v>0.61</v>
       </c>
-      <c r="V62" s="31">
+      <c r="V62" s="32">
         <v>0.49</v>
       </c>
-      <c r="W62" s="31">
+      <c r="W62" s="32">
         <v>0.3</v>
       </c>
-      <c r="X62" s="31">
+      <c r="X62" s="32">
         <v>0.16</v>
       </c>
-      <c r="Y62" s="31">
+      <c r="Y62" s="32">
         <v>0.1</v>
       </c>
-      <c r="Z62" s="31">
+      <c r="Z62" s="32">
         <v>0.22</v>
       </c>
-      <c r="AA62" s="31">
+      <c r="AA62" s="32">
         <v>1.3</v>
       </c>
-      <c r="AB62" s="31">
+      <c r="AB62" s="32">
         <v>0.1</v>
       </c>
-      <c r="AC62" s="31">
+      <c r="AC62" s="32">
         <v>0.56</v>
       </c>
-      <c r="AD62" s="31">
+      <c r="AD62" s="32">
         <v>0.63</v>
       </c>
-      <c r="AE62" s="31">
+      <c r="AE62" s="32">
         <v>0.36</v>
       </c>
-      <c r="AF62" s="31">
+      <c r="AF62" s="32">
         <v>0.38</v>
       </c>
-      <c r="AG62" s="31">
+      <c r="AG62" s="32">
         <v>0.31</v>
       </c>
-      <c r="AH62" s="31">
+      <c r="AH62" s="32">
         <v>0.31</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="28" t="s">
-        <v>490</v>
-      </c>
-      <c r="B63" s="31">
+      <c r="A63" s="29" t="s">
+        <v>491</v>
+      </c>
+      <c r="B63" s="32">
         <v>1.05</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="32">
         <v>0.95</v>
       </c>
-      <c r="D63" s="31">
+      <c r="D63" s="32">
         <v>0.98</v>
       </c>
-      <c r="E63" s="31">
+      <c r="E63" s="32">
         <v>0.85</v>
       </c>
-      <c r="F63" s="31">
+      <c r="F63" s="32">
         <v>0.8</v>
       </c>
-      <c r="G63" s="31">
+      <c r="G63" s="32">
         <v>0.74</v>
       </c>
-      <c r="H63" s="31">
+      <c r="H63" s="32">
         <v>0.63</v>
       </c>
-      <c r="I63" s="31">
+      <c r="I63" s="32">
         <v>0.55</v>
       </c>
-      <c r="J63" s="31">
+      <c r="J63" s="32">
         <v>0.52</v>
       </c>
-      <c r="K63" s="31">
+      <c r="K63" s="32">
         <v>0.4</v>
       </c>
-      <c r="L63" s="31">
+      <c r="L63" s="32">
         <v>0.36</v>
       </c>
-      <c r="M63" s="31">
+      <c r="M63" s="32">
         <v>0.37</v>
       </c>
-      <c r="N63" s="31">
+      <c r="N63" s="32">
         <v>0.41</v>
       </c>
-      <c r="O63" s="31">
+      <c r="O63" s="32">
         <v>0.39</v>
       </c>
-      <c r="P63" s="31">
+      <c r="P63" s="32">
         <v>0.44</v>
       </c>
-      <c r="Q63" s="31">
+      <c r="Q63" s="32">
         <v>0.48</v>
       </c>
-      <c r="R63" s="31">
+      <c r="R63" s="32">
         <v>0.47</v>
       </c>
-      <c r="S63" s="31">
+      <c r="S63" s="32">
         <v>0.44</v>
       </c>
-      <c r="T63" s="31">
+      <c r="T63" s="32">
         <v>0.46</v>
       </c>
-      <c r="U63" s="31">
+      <c r="U63" s="32">
         <v>0.38</v>
       </c>
-      <c r="V63" s="31">
+      <c r="V63" s="32">
         <v>0.28</v>
       </c>
-      <c r="W63" s="31">
+      <c r="W63" s="32">
         <v>0.27</v>
       </c>
-      <c r="X63" s="31">
+      <c r="X63" s="32">
         <v>0.22</v>
       </c>
-      <c r="Y63" s="31">
+      <c r="Y63" s="32">
         <v>0.32</v>
       </c>
-      <c r="Z63" s="31">
+      <c r="Z63" s="32">
         <v>0.43</v>
       </c>
-      <c r="AA63" s="31">
+      <c r="AA63" s="32">
         <v>0.48</v>
       </c>
-      <c r="AB63" s="31">
+      <c r="AB63" s="32">
         <v>0.41</v>
       </c>
-      <c r="AC63" s="31">
+      <c r="AC63" s="32">
         <v>0.46</v>
       </c>
-      <c r="AD63" s="31">
+      <c r="AD63" s="32">
         <v>0.4</v>
       </c>
-      <c r="AE63" s="29"/>
-      <c r="AF63" s="29"/>
-      <c r="AG63" s="29"/>
-      <c r="AH63" s="29"/>
+      <c r="AE63" s="30"/>
+      <c r="AF63" s="30"/>
+      <c r="AG63" s="30"/>
+      <c r="AH63" s="30"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="26" t="s">
-        <v>491</v>
-      </c>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="27"/>
-      <c r="K64" s="27"/>
-      <c r="L64" s="27"/>
-      <c r="M64" s="27"/>
-      <c r="N64" s="27"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
-      <c r="Q64" s="27"/>
-      <c r="R64" s="27"/>
-      <c r="S64" s="27"/>
-      <c r="T64" s="27"/>
-      <c r="U64" s="27"/>
-      <c r="V64" s="27"/>
-      <c r="W64" s="27"/>
-      <c r="X64" s="27"/>
-      <c r="Y64" s="27"/>
-      <c r="Z64" s="27"/>
-      <c r="AA64" s="27"/>
-      <c r="AB64" s="27"/>
-      <c r="AC64" s="27"/>
-      <c r="AD64" s="27"/>
-      <c r="AE64" s="27"/>
-      <c r="AF64" s="27"/>
-      <c r="AG64" s="27"/>
-      <c r="AH64" s="27"/>
+      <c r="A64" s="27" t="s">
+        <v>492</v>
+      </c>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="28"/>
+      <c r="K64" s="28"/>
+      <c r="L64" s="28"/>
+      <c r="M64" s="28"/>
+      <c r="N64" s="28"/>
+      <c r="O64" s="28"/>
+      <c r="P64" s="28"/>
+      <c r="Q64" s="28"/>
+      <c r="R64" s="28"/>
+      <c r="S64" s="28"/>
+      <c r="T64" s="28"/>
+      <c r="U64" s="28"/>
+      <c r="V64" s="28"/>
+      <c r="W64" s="28"/>
+      <c r="X64" s="28"/>
+      <c r="Y64" s="28"/>
+      <c r="Z64" s="28"/>
+      <c r="AA64" s="28"/>
+      <c r="AB64" s="28"/>
+      <c r="AC64" s="28"/>
+      <c r="AD64" s="28"/>
+      <c r="AE64" s="28"/>
+      <c r="AF64" s="28"/>
+      <c r="AG64" s="28"/>
+      <c r="AH64" s="28"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="28" t="s">
-        <v>492</v>
-      </c>
-      <c r="B65" s="31">
+      <c r="A65" s="29" t="s">
+        <v>493</v>
+      </c>
+      <c r="B65" s="32">
         <v>12.26</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="32">
         <v>7.05</v>
       </c>
-      <c r="D65" s="31">
+      <c r="D65" s="32">
         <v>10.43</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="32">
         <v>12.69</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="32">
         <v>15.52</v>
       </c>
-      <c r="G65" s="31">
+      <c r="G65" s="32">
         <v>25.98</v>
       </c>
-      <c r="H65" s="31">
+      <c r="H65" s="32">
         <v>27.92</v>
       </c>
-      <c r="I65" s="31">
+      <c r="I65" s="32">
         <v>7.21</v>
       </c>
-      <c r="J65" s="31">
+      <c r="J65" s="32">
         <v>9.36</v>
       </c>
-      <c r="K65" s="31">
+      <c r="K65" s="32">
         <v>11.07</v>
       </c>
-      <c r="L65" s="31">
+      <c r="L65" s="32">
         <v>11.99</v>
       </c>
-      <c r="M65" s="31">
+      <c r="M65" s="32">
         <v>3.5</v>
       </c>
-      <c r="N65" s="31">
+      <c r="N65" s="32">
         <v>3.48</v>
       </c>
-      <c r="O65" s="31">
+      <c r="O65" s="32">
         <v>3.1</v>
       </c>
-      <c r="P65" s="31">
+      <c r="P65" s="32">
         <v>7.76</v>
       </c>
-      <c r="Q65" s="31">
+      <c r="Q65" s="32">
         <v>9.61</v>
       </c>
-      <c r="R65" s="31">
+      <c r="R65" s="32">
         <v>9.32</v>
       </c>
-      <c r="S65" s="31">
+      <c r="S65" s="32">
         <v>3.42</v>
       </c>
-      <c r="T65" s="31">
+      <c r="T65" s="32">
         <v>5.51</v>
       </c>
-      <c r="U65" s="31">
+      <c r="U65" s="32">
         <v>6.91</v>
       </c>
-      <c r="V65" s="31">
+      <c r="V65" s="32">
         <v>6.18</v>
       </c>
-      <c r="W65" s="31">
+      <c r="W65" s="32">
         <v>4.8</v>
       </c>
-      <c r="X65" s="31">
+      <c r="X65" s="32">
         <v>2.19</v>
       </c>
-      <c r="Y65" s="31">
+      <c r="Y65" s="32">
         <v>11.3</v>
       </c>
-      <c r="Z65" s="31">
+      <c r="Z65" s="32">
         <v>5.73</v>
       </c>
-      <c r="AA65" s="31">
+      <c r="AA65" s="32">
         <v>7.28</v>
       </c>
-      <c r="AB65" s="29"/>
-      <c r="AC65" s="31">
+      <c r="AB65" s="30"/>
+      <c r="AC65" s="32">
         <v>4.09</v>
       </c>
-      <c r="AD65" s="31">
+      <c r="AD65" s="32">
         <v>4.84</v>
       </c>
-      <c r="AE65" s="31">
+      <c r="AE65" s="32">
         <v>2.71</v>
       </c>
-      <c r="AF65" s="31">
+      <c r="AF65" s="32">
         <v>3.32</v>
       </c>
-      <c r="AG65" s="31">
+      <c r="AG65" s="32">
         <v>22.75</v>
       </c>
-      <c r="AH65" s="31">
+      <c r="AH65" s="32">
         <v>4.03</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="28" t="s">
-        <v>493</v>
-      </c>
-      <c r="B66" s="31">
+      <c r="A66" s="29" t="s">
+        <v>494</v>
+      </c>
+      <c r="B66" s="32">
         <v>10.86</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="32">
         <v>11.23</v>
       </c>
-      <c r="D66" s="31">
+      <c r="D66" s="32">
         <v>14.26</v>
       </c>
-      <c r="E66" s="31">
+      <c r="E66" s="32">
         <v>15.17</v>
       </c>
-      <c r="F66" s="31">
+      <c r="F66" s="32">
         <v>14.25</v>
       </c>
-      <c r="G66" s="31">
+      <c r="G66" s="32">
         <v>13.24</v>
       </c>
-      <c r="H66" s="31">
+      <c r="H66" s="32">
         <v>11.07</v>
       </c>
-      <c r="I66" s="31">
+      <c r="I66" s="32">
         <v>7.47</v>
       </c>
-      <c r="J66" s="31">
+      <c r="J66" s="32">
         <v>6.29</v>
       </c>
-      <c r="K66" s="31">
+      <c r="K66" s="32">
         <v>4.83</v>
       </c>
-      <c r="L66" s="31">
+      <c r="L66" s="32">
         <v>4.66</v>
       </c>
-      <c r="M66" s="31">
+      <c r="M66" s="32">
         <v>4.82</v>
       </c>
-      <c r="N66" s="31">
+      <c r="N66" s="32">
         <v>5.73</v>
       </c>
-      <c r="O66" s="31">
+      <c r="O66" s="32">
         <v>5.97</v>
       </c>
-      <c r="P66" s="31">
+      <c r="P66" s="32">
         <v>6.71</v>
       </c>
-      <c r="Q66" s="31">
+      <c r="Q66" s="32">
         <v>6.56</v>
       </c>
-      <c r="R66" s="31">
+      <c r="R66" s="32">
         <v>5.98</v>
       </c>
-      <c r="S66" s="31">
+      <c r="S66" s="32">
         <v>5.38</v>
       </c>
-      <c r="T66" s="31">
+      <c r="T66" s="32">
         <v>5.52</v>
       </c>
-      <c r="U66" s="31">
+      <c r="U66" s="32">
         <v>5.64</v>
       </c>
-      <c r="V66" s="31">
+      <c r="V66" s="32">
         <v>5.0</v>
       </c>
-      <c r="W66" s="31">
+      <c r="W66" s="32">
         <v>4.91</v>
       </c>
-      <c r="X66" s="29"/>
-      <c r="Y66" s="29"/>
-      <c r="Z66" s="29"/>
-      <c r="AA66" s="29"/>
-      <c r="AB66" s="29"/>
-      <c r="AC66" s="31">
+      <c r="X66" s="30"/>
+      <c r="Y66" s="30"/>
+      <c r="Z66" s="30"/>
+      <c r="AA66" s="30"/>
+      <c r="AB66" s="30"/>
+      <c r="AC66" s="32">
         <v>4.27</v>
       </c>
-      <c r="AD66" s="31">
+      <c r="AD66" s="32">
         <v>4.3</v>
       </c>
-      <c r="AE66" s="29"/>
-      <c r="AF66" s="29"/>
-      <c r="AG66" s="29"/>
-      <c r="AH66" s="29"/>
+      <c r="AE66" s="30"/>
+      <c r="AF66" s="30"/>
+      <c r="AG66" s="30"/>
+      <c r="AH66" s="30"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="26" t="s">
-        <v>494</v>
-      </c>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
-      <c r="N67" s="27"/>
-      <c r="O67" s="27"/>
-      <c r="P67" s="27"/>
-      <c r="Q67" s="27"/>
-      <c r="R67" s="27"/>
-      <c r="S67" s="27"/>
-      <c r="T67" s="27"/>
-      <c r="U67" s="27"/>
-      <c r="V67" s="27"/>
-      <c r="W67" s="27"/>
-      <c r="X67" s="27"/>
-      <c r="Y67" s="27"/>
-      <c r="Z67" s="27"/>
-      <c r="AA67" s="27"/>
-      <c r="AB67" s="27"/>
-      <c r="AC67" s="27"/>
-      <c r="AD67" s="27"/>
-      <c r="AE67" s="27"/>
-      <c r="AF67" s="27"/>
-      <c r="AG67" s="27"/>
-      <c r="AH67" s="27"/>
+      <c r="A67" s="27" t="s">
+        <v>495</v>
+      </c>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="28"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="28"/>
+      <c r="M67" s="28"/>
+      <c r="N67" s="28"/>
+      <c r="O67" s="28"/>
+      <c r="P67" s="28"/>
+      <c r="Q67" s="28"/>
+      <c r="R67" s="28"/>
+      <c r="S67" s="28"/>
+      <c r="T67" s="28"/>
+      <c r="U67" s="28"/>
+      <c r="V67" s="28"/>
+      <c r="W67" s="28"/>
+      <c r="X67" s="28"/>
+      <c r="Y67" s="28"/>
+      <c r="Z67" s="28"/>
+      <c r="AA67" s="28"/>
+      <c r="AB67" s="28"/>
+      <c r="AC67" s="28"/>
+      <c r="AD67" s="28"/>
+      <c r="AE67" s="28"/>
+      <c r="AF67" s="28"/>
+      <c r="AG67" s="28"/>
+      <c r="AH67" s="28"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="28" t="s">
-        <v>495</v>
-      </c>
-      <c r="B68" s="31">
+      <c r="A68" s="29" t="s">
+        <v>496</v>
+      </c>
+      <c r="B68" s="32">
         <v>9.8</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="32">
         <v>2.36</v>
       </c>
-      <c r="D68" s="31">
+      <c r="D68" s="32">
         <v>4.99</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="32">
         <v>7.56</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="32">
         <v>9.16</v>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="32">
         <v>12.02</v>
       </c>
-      <c r="H68" s="31">
+      <c r="H68" s="32">
         <v>7.09</v>
       </c>
-      <c r="I68" s="29"/>
-      <c r="J68" s="31">
+      <c r="I68" s="30"/>
+      <c r="J68" s="32">
         <v>15.12</v>
       </c>
-      <c r="K68" s="31">
+      <c r="K68" s="32">
         <v>5.34</v>
       </c>
-      <c r="L68" s="31">
+      <c r="L68" s="32">
         <v>3.74</v>
       </c>
-      <c r="M68" s="31">
+      <c r="M68" s="32">
         <v>3.16</v>
       </c>
-      <c r="N68" s="31">
+      <c r="N68" s="32">
         <v>9.64</v>
       </c>
-      <c r="O68" s="31">
+      <c r="O68" s="32">
         <v>3.84</v>
       </c>
-      <c r="P68" s="31">
+      <c r="P68" s="32">
         <v>11.64</v>
       </c>
-      <c r="Q68" s="29"/>
-      <c r="R68" s="31">
+      <c r="Q68" s="30"/>
+      <c r="R68" s="32">
         <v>10.17</v>
       </c>
-      <c r="S68" s="31">
+      <c r="S68" s="32">
         <v>4.43</v>
       </c>
-      <c r="T68" s="31">
+      <c r="T68" s="32">
         <v>6.18</v>
       </c>
-      <c r="U68" s="31">
+      <c r="U68" s="32">
         <v>25.04</v>
       </c>
-      <c r="V68" s="30">
+      <c r="V68" s="31">
         <v>104.78</v>
       </c>
-      <c r="W68" s="31">
+      <c r="W68" s="32">
         <v>7.75</v>
       </c>
-      <c r="X68" s="31">
+      <c r="X68" s="32">
         <v>4.05</v>
       </c>
-      <c r="Y68" s="31">
+      <c r="Y68" s="32">
         <v>1.61</v>
       </c>
-      <c r="Z68" s="31">
+      <c r="Z68" s="32">
         <v>3.1</v>
       </c>
-      <c r="AA68" s="29"/>
-      <c r="AB68" s="29"/>
-      <c r="AC68" s="31">
+      <c r="AA68" s="30"/>
+      <c r="AB68" s="30"/>
+      <c r="AC68" s="32">
         <v>36.07</v>
       </c>
-      <c r="AD68" s="31">
+      <c r="AD68" s="32">
         <v>7.02</v>
       </c>
-      <c r="AE68" s="31">
+      <c r="AE68" s="32">
         <v>2.66</v>
       </c>
-      <c r="AF68" s="31">
+      <c r="AF68" s="32">
         <v>6.74</v>
       </c>
-      <c r="AG68" s="31">
+      <c r="AG68" s="32">
         <v>3.29</v>
       </c>
-      <c r="AH68" s="31">
+      <c r="AH68" s="32">
         <v>5.44</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="28" t="s">
-        <v>496</v>
-      </c>
-      <c r="B69" s="31">
+      <c r="A69" s="29" t="s">
+        <v>497</v>
+      </c>
+      <c r="B69" s="32">
         <v>5.47</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="32">
         <v>4.89</v>
       </c>
-      <c r="D69" s="31">
+      <c r="D69" s="32">
         <v>7.14</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="32">
         <v>10.05</v>
       </c>
-      <c r="F69" s="31">
+      <c r="F69" s="32">
         <v>12.43</v>
       </c>
-      <c r="G69" s="31">
+      <c r="G69" s="32">
         <v>11.45</v>
       </c>
-      <c r="H69" s="31">
+      <c r="H69" s="32">
         <v>8.58</v>
       </c>
-      <c r="I69" s="31">
+      <c r="I69" s="32">
         <v>6.9</v>
       </c>
-      <c r="J69" s="31">
+      <c r="J69" s="32">
         <v>5.96</v>
       </c>
-      <c r="K69" s="31">
+      <c r="K69" s="32">
         <v>4.49</v>
       </c>
-      <c r="L69" s="31">
+      <c r="L69" s="32">
         <v>5.09</v>
       </c>
-      <c r="M69" s="31">
+      <c r="M69" s="32">
         <v>8.33</v>
       </c>
-      <c r="N69" s="31">
+      <c r="N69" s="32">
         <v>12.12</v>
       </c>
-      <c r="O69" s="31">
+      <c r="O69" s="32">
         <v>10.43</v>
       </c>
-      <c r="P69" s="31">
+      <c r="P69" s="32">
         <v>11.33</v>
       </c>
-      <c r="Q69" s="31">
+      <c r="Q69" s="32">
         <v>12.77</v>
       </c>
-      <c r="R69" s="31">
+      <c r="R69" s="32">
         <v>9.75</v>
       </c>
-      <c r="S69" s="31">
+      <c r="S69" s="32">
         <v>9.42</v>
       </c>
-      <c r="T69" s="31">
+      <c r="T69" s="32">
         <v>10.7</v>
       </c>
-      <c r="U69" s="31">
+      <c r="U69" s="32">
         <v>12.42</v>
       </c>
-      <c r="V69" s="31">
+      <c r="V69" s="32">
         <v>6.92</v>
       </c>
-      <c r="W69" s="31">
+      <c r="W69" s="32">
         <v>6.05</v>
       </c>
-      <c r="X69" s="31">
+      <c r="X69" s="32">
         <v>6.32</v>
       </c>
-      <c r="Y69" s="31">
+      <c r="Y69" s="32">
         <v>10.83</v>
       </c>
-      <c r="Z69" s="31">
+      <c r="Z69" s="32">
         <v>12.31</v>
       </c>
-      <c r="AA69" s="31">
+      <c r="AA69" s="32">
         <v>10.28</v>
       </c>
-      <c r="AB69" s="31">
+      <c r="AB69" s="32">
         <v>7.45</v>
       </c>
-      <c r="AC69" s="31">
+      <c r="AC69" s="32">
         <v>6.09</v>
       </c>
-      <c r="AD69" s="31">
+      <c r="AD69" s="32">
         <v>4.65</v>
       </c>
-      <c r="AE69" s="29"/>
-      <c r="AF69" s="29"/>
-      <c r="AG69" s="29"/>
-      <c r="AH69" s="29"/>
+      <c r="AE69" s="30"/>
+      <c r="AF69" s="30"/>
+      <c r="AG69" s="30"/>
+      <c r="AH69" s="30"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27"/>
-      <c r="K70" s="27"/>
-      <c r="L70" s="27"/>
-      <c r="M70" s="27"/>
-      <c r="N70" s="27"/>
-      <c r="O70" s="27"/>
-      <c r="P70" s="27"/>
-      <c r="Q70" s="27"/>
-      <c r="R70" s="27"/>
-      <c r="S70" s="27"/>
-      <c r="T70" s="27"/>
-      <c r="U70" s="27"/>
-      <c r="V70" s="27"/>
-      <c r="W70" s="27"/>
-      <c r="X70" s="27"/>
-      <c r="Y70" s="27"/>
-      <c r="Z70" s="27"/>
-      <c r="AA70" s="27"/>
-      <c r="AB70" s="27"/>
-      <c r="AC70" s="27"/>
-      <c r="AD70" s="27"/>
-      <c r="AE70" s="27"/>
-      <c r="AF70" s="27"/>
-      <c r="AG70" s="27"/>
-      <c r="AH70" s="27"/>
+      <c r="A70" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+      <c r="J70" s="28"/>
+      <c r="K70" s="28"/>
+      <c r="L70" s="28"/>
+      <c r="M70" s="28"/>
+      <c r="N70" s="28"/>
+      <c r="O70" s="28"/>
+      <c r="P70" s="28"/>
+      <c r="Q70" s="28"/>
+      <c r="R70" s="28"/>
+      <c r="S70" s="28"/>
+      <c r="T70" s="28"/>
+      <c r="U70" s="28"/>
+      <c r="V70" s="28"/>
+      <c r="W70" s="28"/>
+      <c r="X70" s="28"/>
+      <c r="Y70" s="28"/>
+      <c r="Z70" s="28"/>
+      <c r="AA70" s="28"/>
+      <c r="AB70" s="28"/>
+      <c r="AC70" s="28"/>
+      <c r="AD70" s="28"/>
+      <c r="AE70" s="28"/>
+      <c r="AF70" s="28"/>
+      <c r="AG70" s="28"/>
+      <c r="AH70" s="28"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="28" t="s">
-        <v>498</v>
-      </c>
-      <c r="B71" s="29"/>
-      <c r="C71" s="31">
+      <c r="A71" s="29" t="s">
+        <v>499</v>
+      </c>
+      <c r="B71" s="30"/>
+      <c r="C71" s="32">
         <v>4.55</v>
       </c>
-      <c r="D71" s="31">
+      <c r="D71" s="32">
         <v>9.02</v>
       </c>
-      <c r="E71" s="31">
+      <c r="E71" s="32">
         <v>22.06</v>
       </c>
-      <c r="F71" s="29"/>
-      <c r="G71" s="31">
+      <c r="F71" s="30"/>
+      <c r="G71" s="32">
         <v>75.52</v>
       </c>
-      <c r="H71" s="31">
+      <c r="H71" s="32">
         <v>17.76</v>
       </c>
-      <c r="I71" s="29"/>
-      <c r="J71" s="29"/>
-      <c r="K71" s="31">
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="32">
         <v>11.01</v>
       </c>
-      <c r="L71" s="31">
+      <c r="L71" s="32">
         <v>6.2</v>
       </c>
-      <c r="M71" s="31">
+      <c r="M71" s="32">
         <v>4.46</v>
       </c>
-      <c r="N71" s="31">
+      <c r="N71" s="32">
         <v>81.9</v>
       </c>
-      <c r="O71" s="31">
+      <c r="O71" s="32">
         <v>7.81</v>
       </c>
-      <c r="P71" s="29"/>
-      <c r="Q71" s="29"/>
-      <c r="R71" s="29"/>
-      <c r="S71" s="30">
+      <c r="P71" s="30"/>
+      <c r="Q71" s="30"/>
+      <c r="R71" s="30"/>
+      <c r="S71" s="31">
         <v>462.84</v>
       </c>
-      <c r="T71" s="31">
+      <c r="T71" s="32">
         <v>11.43</v>
       </c>
-      <c r="U71" s="29"/>
-      <c r="V71" s="29"/>
-      <c r="W71" s="31">
+      <c r="U71" s="30"/>
+      <c r="V71" s="30"/>
+      <c r="W71" s="32">
         <v>30.75</v>
       </c>
-      <c r="X71" s="31">
+      <c r="X71" s="32">
         <v>13.18</v>
       </c>
-      <c r="Y71" s="31">
+      <c r="Y71" s="32">
         <v>2.98</v>
       </c>
-      <c r="Z71" s="31">
+      <c r="Z71" s="32">
         <v>8.42</v>
       </c>
-      <c r="AA71" s="29"/>
-      <c r="AB71" s="29"/>
-      <c r="AC71" s="29"/>
-      <c r="AD71" s="29"/>
-      <c r="AE71" s="31">
+      <c r="AA71" s="30"/>
+      <c r="AB71" s="30"/>
+      <c r="AC71" s="30"/>
+      <c r="AD71" s="30"/>
+      <c r="AE71" s="32">
         <v>6.92</v>
       </c>
-      <c r="AF71" s="29"/>
-      <c r="AG71" s="31">
+      <c r="AF71" s="30"/>
+      <c r="AG71" s="32">
         <v>10.84</v>
       </c>
-      <c r="AH71" s="31">
+      <c r="AH71" s="32">
         <v>5.44</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="28" t="s">
-        <v>499</v>
-      </c>
-      <c r="B72" s="31">
+      <c r="A72" s="29" t="s">
+        <v>500</v>
+      </c>
+      <c r="B72" s="32">
         <v>21.06</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="32">
         <v>11.4</v>
       </c>
-      <c r="D72" s="31">
+      <c r="D72" s="32">
         <v>20.18</v>
       </c>
-      <c r="E72" s="30">
+      <c r="E72" s="31">
         <v>140.14</v>
       </c>
-      <c r="F72" s="29"/>
-      <c r="G72" s="30">
+      <c r="F72" s="30"/>
+      <c r="G72" s="31">
         <v>164.78</v>
       </c>
-      <c r="H72" s="31">
+      <c r="H72" s="32">
         <v>36.51</v>
       </c>
-      <c r="I72" s="31">
+      <c r="I72" s="32">
         <v>18.49</v>
       </c>
-      <c r="J72" s="31">
+      <c r="J72" s="32">
         <v>12.59</v>
       </c>
-      <c r="K72" s="31">
+      <c r="K72" s="32">
         <v>8.31</v>
       </c>
-      <c r="L72" s="31">
+      <c r="L72" s="32">
         <v>10.48</v>
       </c>
-      <c r="M72" s="31">
+      <c r="M72" s="32">
         <v>56.29</v>
       </c>
-      <c r="N72" s="29"/>
-      <c r="O72" s="29"/>
-      <c r="P72" s="29"/>
-      <c r="Q72" s="29"/>
-      <c r="R72" s="29"/>
-      <c r="S72" s="31">
+      <c r="N72" s="30"/>
+      <c r="O72" s="30"/>
+      <c r="P72" s="30"/>
+      <c r="Q72" s="30"/>
+      <c r="R72" s="30"/>
+      <c r="S72" s="32">
         <v>54.93</v>
       </c>
-      <c r="T72" s="31">
+      <c r="T72" s="32">
         <v>42.85</v>
       </c>
-      <c r="U72" s="30">
+      <c r="U72" s="31">
         <v>241.22</v>
       </c>
-      <c r="V72" s="31">
+      <c r="V72" s="32">
         <v>37.8</v>
       </c>
-      <c r="W72" s="30">
+      <c r="W72" s="31">
         <v>152.74</v>
       </c>
-      <c r="X72" s="29"/>
-      <c r="Y72" s="29"/>
-      <c r="Z72" s="29"/>
-      <c r="AA72" s="29"/>
-      <c r="AB72" s="29"/>
-      <c r="AC72" s="29"/>
-      <c r="AD72" s="31">
+      <c r="X72" s="30"/>
+      <c r="Y72" s="30"/>
+      <c r="Z72" s="30"/>
+      <c r="AA72" s="30"/>
+      <c r="AB72" s="30"/>
+      <c r="AC72" s="30"/>
+      <c r="AD72" s="32">
         <v>43.14</v>
       </c>
-      <c r="AE72" s="29"/>
-      <c r="AF72" s="29"/>
-      <c r="AG72" s="29"/>
-      <c r="AH72" s="29"/>
+      <c r="AE72" s="30"/>
+      <c r="AF72" s="30"/>
+      <c r="AG72" s="30"/>
+      <c r="AH72" s="30"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
